--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="F14" t="n">
-        <v>8.76</v>
+        <v>9.65</v>
       </c>
       <c r="G14" t="n">
-        <v>120.2</v>
+        <v>123.8</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-64.53</v>
+        <v>-58.79</v>
       </c>
       <c r="K14" t="n">
-        <v>-106.14</v>
+        <v>-14.18</v>
       </c>
       <c r="L14" t="n">
-        <v>124.21</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:24:03</t>
+          <t>06:23:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="F15" t="n">
-        <v>9.26</v>
+        <v>8.76</v>
       </c>
       <c r="G15" t="n">
-        <v>127.9</v>
+        <v>133.7</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>19.53</v>
+        <v>-30.37</v>
       </c>
       <c r="K15" t="n">
-        <v>-145.46</v>
+        <v>-107.92</v>
       </c>
       <c r="L15" t="n">
-        <v>146.76</v>
+        <v>112.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:25:30</t>
+          <t>06:25:10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.27</v>
+        <v>2.72</v>
       </c>
       <c r="F16" t="n">
-        <v>9.18</v>
+        <v>9.42</v>
       </c>
       <c r="G16" t="n">
-        <v>132.8</v>
+        <v>121.8</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>30.86</v>
+        <v>-136.22</v>
       </c>
       <c r="K16" t="n">
-        <v>57.55</v>
+        <v>37.57</v>
       </c>
       <c r="L16" t="n">
-        <v>65.3</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:30:51</t>
+          <t>06:31:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="F17" t="n">
-        <v>9.68</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>124.1</v>
+        <v>121.5</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>127.81</v>
+        <v>-144.91</v>
       </c>
       <c r="K17" t="n">
-        <v>-44.32</v>
+        <v>-145.65</v>
       </c>
       <c r="L17" t="n">
-        <v>135.28</v>
+        <v>205.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:32:58</t>
+          <t>06:33:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.71</v>
+        <v>2.96</v>
       </c>
       <c r="F18" t="n">
-        <v>10.1</v>
+        <v>8.76</v>
       </c>
       <c r="G18" t="n">
-        <v>108.9</v>
+        <v>138.7</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>53.57</v>
+        <v>40.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-68.89</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>87.27</v>
+        <v>106.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:33:54</t>
+          <t>06:35:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.29</v>
+        <v>2.85</v>
       </c>
       <c r="F19" t="n">
-        <v>9.550000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>143</v>
+        <v>115.1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>39.51</v>
+        <v>-154.77</v>
       </c>
       <c r="K19" t="n">
-        <v>4.08</v>
+        <v>-130.06</v>
       </c>
       <c r="L19" t="n">
-        <v>39.72</v>
+        <v>202.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:38:29</t>
+          <t>06:39:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="F20" t="n">
-        <v>9.31</v>
+        <v>9.26</v>
       </c>
       <c r="G20" t="n">
-        <v>129.1</v>
+        <v>127.8</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>265.58</v>
+        <v>-180.58</v>
       </c>
       <c r="K20" t="n">
-        <v>-173.88</v>
+        <v>-92.06</v>
       </c>
       <c r="L20" t="n">
-        <v>317.43</v>
+        <v>202.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:39:17</t>
+          <t>06:40:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="F21" t="n">
-        <v>9.08</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>129.1</v>
+        <v>131.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-61.59</v>
+        <v>-247.55</v>
       </c>
       <c r="K21" t="n">
-        <v>-70.84999999999999</v>
+        <v>228.21</v>
       </c>
       <c r="L21" t="n">
-        <v>93.87</v>
+        <v>336.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:41:37</t>
+          <t>06:43:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="F22" t="n">
-        <v>9.26</v>
+        <v>9.59</v>
       </c>
       <c r="G22" t="n">
-        <v>132.2</v>
+        <v>139.7</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-160.76</v>
+        <v>-40.88</v>
       </c>
       <c r="K22" t="n">
-        <v>43.34</v>
+        <v>-46.69</v>
       </c>
       <c r="L22" t="n">
-        <v>166.5</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:46:07</t>
+          <t>06:47:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="F23" t="n">
-        <v>9.029999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>133.5</v>
+        <v>119.4</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="I23" t="n">
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-116.64</v>
+        <v>-158.44</v>
       </c>
       <c r="K23" t="n">
-        <v>-336.84</v>
+        <v>505.33</v>
       </c>
       <c r="L23" t="n">
-        <v>356.47</v>
+        <v>529.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:47:57</t>
+          <t>06:49:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="F24" t="n">
-        <v>9.1</v>
+        <v>8.84</v>
       </c>
       <c r="G24" t="n">
-        <v>135.2</v>
+        <v>138.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6</v>
+        <v>10.9</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>346.33</v>
+        <v>229.52</v>
       </c>
       <c r="K24" t="n">
-        <v>200.94</v>
+        <v>-16.64</v>
       </c>
       <c r="L24" t="n">
-        <v>400.4</v>
+        <v>230.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:50:28</t>
+          <t>06:51:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.93</v>
+        <v>2.68</v>
       </c>
       <c r="F25" t="n">
-        <v>9.279999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>137.6</v>
+        <v>137</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.56</v>
+        <v>-400.14</v>
       </c>
       <c r="K25" t="n">
-        <v>-353.12</v>
+        <v>5.19</v>
       </c>
       <c r="L25" t="n">
-        <v>353.46</v>
+        <v>400.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:55:48</t>
+          <t>06:55:49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.93</v>
+        <v>2.24</v>
       </c>
       <c r="F26" t="n">
-        <v>10.06</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>135.9</v>
+        <v>128.9</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-102.14</v>
+        <v>-140.89</v>
       </c>
       <c r="K26" t="n">
-        <v>284.14</v>
+        <v>205.07</v>
       </c>
       <c r="L26" t="n">
-        <v>301.94</v>
+        <v>248.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:57:52</t>
+          <t>06:57:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="F27" t="n">
-        <v>9.460000000000001</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>124.3</v>
+        <v>104.3</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="I27" t="n">
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>147.73</v>
+        <v>385.23</v>
       </c>
       <c r="K27" t="n">
-        <v>411.69</v>
+        <v>323.98</v>
       </c>
       <c r="L27" t="n">
-        <v>437.39</v>
+        <v>503.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:00:02</t>
+          <t>06:58:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="F28" t="n">
-        <v>9.039999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="G28" t="n">
-        <v>127.3</v>
+        <v>129.2</v>
       </c>
       <c r="H28" t="n">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-237.71</v>
+        <v>254.14</v>
       </c>
       <c r="K28" t="n">
-        <v>-68.12</v>
+        <v>-226.86</v>
       </c>
       <c r="L28" t="n">
-        <v>247.27</v>
+        <v>340.66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:09:40</t>
+          <t>07:09:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.16</v>
+        <v>3.02</v>
       </c>
       <c r="F29" t="n">
-        <v>8.69</v>
+        <v>9.34</v>
       </c>
       <c r="G29" t="n">
-        <v>142.1</v>
+        <v>130.9</v>
       </c>
       <c r="H29" t="n">
-        <v>8.699999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.279999999999999</v>
+        <v>126.74</v>
       </c>
       <c r="K29" t="n">
-        <v>-22.06</v>
+        <v>15.16</v>
       </c>
       <c r="L29" t="n">
-        <v>23.93</v>
+        <v>127.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:11:13</t>
+          <t>07:11:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="F30" t="n">
-        <v>9.43</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>111.1</v>
+        <v>131.6</v>
       </c>
       <c r="H30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>38.13</v>
+        <v>32.45</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.65</v>
+        <v>181.22</v>
       </c>
       <c r="L30" t="n">
-        <v>38.13</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:12:28</t>
+          <t>07:12:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="F31" t="n">
-        <v>8.83</v>
+        <v>9.19</v>
       </c>
       <c r="G31" t="n">
-        <v>146.2</v>
+        <v>126.1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-76.79000000000001</v>
+        <v>144.97</v>
       </c>
       <c r="K31" t="n">
-        <v>74.61</v>
+        <v>120.37</v>
       </c>
       <c r="L31" t="n">
-        <v>107.06</v>
+        <v>188.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:17:17</t>
+          <t>07:17:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.81</v>
+        <v>1.83</v>
       </c>
       <c r="F32" t="n">
-        <v>9.050000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="G32" t="n">
-        <v>134.2</v>
+        <v>123.2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-33.58</v>
+        <v>1.69</v>
       </c>
       <c r="K32" t="n">
-        <v>-58.39</v>
+        <v>-59.77</v>
       </c>
       <c r="L32" t="n">
-        <v>67.36</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:19:39</t>
+          <t>07:19:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.79</v>
+        <v>3.07</v>
       </c>
       <c r="F33" t="n">
-        <v>9.390000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="G33" t="n">
-        <v>128.8</v>
+        <v>131.8</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-25.71</v>
+        <v>-25.14</v>
       </c>
       <c r="K33" t="n">
-        <v>162.22</v>
+        <v>148.03</v>
       </c>
       <c r="L33" t="n">
-        <v>164.25</v>
+        <v>150.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:20:18</t>
+          <t>07:21:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F34" t="n">
-        <v>8.99</v>
+        <v>9.26</v>
       </c>
       <c r="G34" t="n">
-        <v>127.6</v>
+        <v>147.2</v>
       </c>
       <c r="H34" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>47.18</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>37.14</v>
+        <v>97.38</v>
       </c>
       <c r="L34" t="n">
-        <v>60.04</v>
+        <v>138.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:25:28</t>
+          <t>07:26:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="F35" t="n">
-        <v>9.220000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>130.2</v>
+        <v>119.2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>19.79</v>
+        <v>-262.14</v>
       </c>
       <c r="K35" t="n">
-        <v>38.61</v>
+        <v>-68.65000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>43.39</v>
+        <v>270.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:27:30</t>
+          <t>07:28:31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="F36" t="n">
-        <v>9.15</v>
+        <v>9.34</v>
       </c>
       <c r="G36" t="n">
-        <v>140</v>
+        <v>133.5</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-367.51</v>
+        <v>-237.19</v>
       </c>
       <c r="K36" t="n">
-        <v>-166.15</v>
+        <v>-216.03</v>
       </c>
       <c r="L36" t="n">
-        <v>403.32</v>
+        <v>320.82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:29:48</t>
+          <t>07:29:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.82</v>
+        <v>2.49</v>
       </c>
       <c r="F37" t="n">
-        <v>9.640000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="G37" t="n">
-        <v>125</v>
+        <v>131.7</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>372.34</v>
+        <v>-95.61</v>
       </c>
       <c r="K37" t="n">
-        <v>78.45999999999999</v>
+        <v>266.17</v>
       </c>
       <c r="L37" t="n">
-        <v>380.52</v>
+        <v>282.82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:35:40</t>
+          <t>07:33:42</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="F38" t="n">
-        <v>8.66</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>126.1</v>
+        <v>123.1</v>
       </c>
       <c r="H38" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-177.03</v>
+        <v>374.95</v>
       </c>
       <c r="K38" t="n">
-        <v>42.31</v>
+        <v>-289.69</v>
       </c>
       <c r="L38" t="n">
-        <v>182.02</v>
+        <v>473.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:37:44</t>
+          <t>07:35:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.98</v>
+        <v>2.24</v>
       </c>
       <c r="F39" t="n">
-        <v>9.51</v>
+        <v>8.56</v>
       </c>
       <c r="G39" t="n">
-        <v>123.2</v>
+        <v>136.7</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-231.98</v>
+        <v>-452.81</v>
       </c>
       <c r="K39" t="n">
-        <v>199.59</v>
+        <v>-42.9</v>
       </c>
       <c r="L39" t="n">
-        <v>306.03</v>
+        <v>454.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:39:17</t>
+          <t>07:38:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="F40" t="n">
-        <v>9.31</v>
+        <v>8.49</v>
       </c>
       <c r="G40" t="n">
-        <v>123.4</v>
+        <v>132.4</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-313.65</v>
+        <v>413.66</v>
       </c>
       <c r="K40" t="n">
-        <v>-133.86</v>
+        <v>91.67</v>
       </c>
       <c r="L40" t="n">
-        <v>341.02</v>
+        <v>423.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:43:43</t>
+          <t>07:41:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="F41" t="n">
-        <v>9.109999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="G41" t="n">
-        <v>129</v>
+        <v>115.9</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>308.56</v>
+        <v>395.19</v>
       </c>
       <c r="K41" t="n">
-        <v>20.39</v>
+        <v>-207.92</v>
       </c>
       <c r="L41" t="n">
-        <v>309.23</v>
+        <v>446.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:44:48</t>
+          <t>07:43:44</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="F42" t="n">
-        <v>9.49</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>127</v>
+        <v>134.1</v>
       </c>
       <c r="H42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>386.25</v>
+        <v>-256.77</v>
       </c>
       <c r="K42" t="n">
-        <v>-290.79</v>
+        <v>-82.73999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>483.47</v>
+        <v>269.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:45:55</t>
+          <t>07:46:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="F43" t="n">
-        <v>9.1</v>
+        <v>9.94</v>
       </c>
       <c r="G43" t="n">
-        <v>138</v>
+        <v>126.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>213.59</v>
+        <v>-499.09</v>
       </c>
       <c r="K43" t="n">
-        <v>-549.5599999999999</v>
+        <v>-53.05</v>
       </c>
       <c r="L43" t="n">
-        <v>589.61</v>
+        <v>501.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:56:14</t>
+          <t>07:56:39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="F44" t="n">
-        <v>8.949999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>120.3</v>
+        <v>131.5</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-44.52</v>
+        <v>248.23</v>
       </c>
       <c r="K44" t="n">
-        <v>-31.74</v>
+        <v>28.16</v>
       </c>
       <c r="L44" t="n">
-        <v>54.68</v>
+        <v>249.83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:57:55</t>
+          <t>07:59:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="F45" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="G45" t="n">
-        <v>130.4</v>
+        <v>140</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-87.94</v>
+        <v>78.03</v>
       </c>
       <c r="K45" t="n">
-        <v>11.81</v>
+        <v>128.46</v>
       </c>
       <c r="L45" t="n">
-        <v>88.73</v>
+        <v>150.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:59:52</t>
+          <t>08:01:02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.68</v>
+        <v>3.17</v>
       </c>
       <c r="F46" t="n">
-        <v>9.73</v>
+        <v>9.49</v>
       </c>
       <c r="G46" t="n">
-        <v>134.8</v>
+        <v>112.8</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-18.77</v>
+        <v>28.03</v>
       </c>
       <c r="K46" t="n">
-        <v>92.15000000000001</v>
+        <v>-112.14</v>
       </c>
       <c r="L46" t="n">
-        <v>94.05</v>
+        <v>115.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:03:58</t>
+          <t>08:07:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="F47" t="n">
-        <v>9.35</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>131.3</v>
+        <v>134.9</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>111.88</v>
+        <v>-115.68</v>
       </c>
       <c r="K47" t="n">
-        <v>53.26</v>
+        <v>-118.68</v>
       </c>
       <c r="L47" t="n">
-        <v>123.91</v>
+        <v>165.73</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:04:53</t>
+          <t>08:08:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="F48" t="n">
-        <v>9.699999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="G48" t="n">
-        <v>136.7</v>
+        <v>132.1</v>
       </c>
       <c r="H48" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>23.21</v>
+        <v>59.79</v>
       </c>
       <c r="K48" t="n">
-        <v>-17.01</v>
+        <v>65.31</v>
       </c>
       <c r="L48" t="n">
-        <v>28.77</v>
+        <v>88.54000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:06:33</t>
+          <t>08:10:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.25</v>
+        <v>3.07</v>
       </c>
       <c r="F49" t="n">
-        <v>9.390000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>128.5</v>
+        <v>134.3</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>28.56</v>
+        <v>39.74</v>
       </c>
       <c r="K49" t="n">
-        <v>42.46</v>
+        <v>222.16</v>
       </c>
       <c r="L49" t="n">
-        <v>51.17</v>
+        <v>225.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:10:25</t>
+          <t>08:15:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.37</v>
+        <v>2.96</v>
       </c>
       <c r="F50" t="n">
-        <v>9.17</v>
+        <v>8.26</v>
       </c>
       <c r="G50" t="n">
-        <v>135.4</v>
+        <v>128.8</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>51.94</v>
+        <v>-205.24</v>
       </c>
       <c r="K50" t="n">
-        <v>-73.88</v>
+        <v>400.75</v>
       </c>
       <c r="L50" t="n">
-        <v>90.31</v>
+        <v>450.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:11:52</t>
+          <t>08:17:37</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="F51" t="n">
-        <v>9.220000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>128.2</v>
+        <v>139.3</v>
       </c>
       <c r="H51" t="n">
-        <v>9.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>211.26</v>
+        <v>45.45</v>
       </c>
       <c r="K51" t="n">
-        <v>-28.43</v>
+        <v>141.75</v>
       </c>
       <c r="L51" t="n">
-        <v>213.16</v>
+        <v>148.86</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:13:36</t>
+          <t>08:19:29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.52</v>
+        <v>2.53</v>
       </c>
       <c r="F52" t="n">
-        <v>9.630000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="G52" t="n">
-        <v>129.7</v>
+        <v>131.6</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I52" t="n">
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-69.63</v>
+        <v>140.79</v>
       </c>
       <c r="K52" t="n">
-        <v>-35.69</v>
+        <v>-173.53</v>
       </c>
       <c r="L52" t="n">
-        <v>78.23999999999999</v>
+        <v>223.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:17:46</t>
+          <t>08:25:20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>9.09</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>135.1</v>
+        <v>143.6</v>
       </c>
       <c r="H53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-216.75</v>
+        <v>554.17</v>
       </c>
       <c r="K53" t="n">
-        <v>-536.24</v>
+        <v>16.38</v>
       </c>
       <c r="L53" t="n">
-        <v>578.39</v>
+        <v>554.41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:19:00</t>
+          <t>08:26:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="F54" t="n">
-        <v>9</v>
+        <v>9.06</v>
       </c>
       <c r="G54" t="n">
-        <v>129.7</v>
+        <v>123.3</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-92.03</v>
+        <v>470.12</v>
       </c>
       <c r="K54" t="n">
-        <v>-347.46</v>
+        <v>-13.37</v>
       </c>
       <c r="L54" t="n">
-        <v>359.44</v>
+        <v>470.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:21:39</t>
+          <t>08:27:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="F55" t="n">
-        <v>8.92</v>
+        <v>8.59</v>
       </c>
       <c r="G55" t="n">
-        <v>132.1</v>
+        <v>127.3</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>342.38</v>
+        <v>180.13</v>
       </c>
       <c r="K55" t="n">
-        <v>-439.95</v>
+        <v>-56.39</v>
       </c>
       <c r="L55" t="n">
-        <v>557.48</v>
+        <v>188.75</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:26:08</t>
+          <t>08:32:31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.72</v>
+        <v>3.34</v>
       </c>
       <c r="F56" t="n">
-        <v>8.890000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>123.8</v>
+        <v>147.3</v>
       </c>
       <c r="H56" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-101.21</v>
+        <v>353.03</v>
       </c>
       <c r="K56" t="n">
-        <v>-362.11</v>
+        <v>471.37</v>
       </c>
       <c r="L56" t="n">
-        <v>375.99</v>
+        <v>588.91</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:27:07</t>
+          <t>08:34:31</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="F57" t="n">
-        <v>9.640000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="G57" t="n">
-        <v>118.8</v>
+        <v>123.4</v>
       </c>
       <c r="H57" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-213.47</v>
+        <v>740.33</v>
       </c>
       <c r="K57" t="n">
-        <v>-160.26</v>
+        <v>205.5</v>
       </c>
       <c r="L57" t="n">
-        <v>266.93</v>
+        <v>768.3200000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:29:32</t>
+          <t>08:35:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.8</v>
+        <v>3.53</v>
       </c>
       <c r="F58" t="n">
-        <v>9.17</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>139.1</v>
+        <v>128.5</v>
       </c>
       <c r="H58" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-389.96</v>
+        <v>-558.54</v>
       </c>
       <c r="K58" t="n">
-        <v>95.92</v>
+        <v>-148.17</v>
       </c>
       <c r="L58" t="n">
-        <v>401.58</v>
+        <v>577.86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:40:47</t>
+          <t>08:48:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.09</v>
+        <v>2.53</v>
       </c>
       <c r="F59" t="n">
-        <v>8.470000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="G59" t="n">
-        <v>142</v>
+        <v>132.7</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-89.02</v>
+        <v>-97.84999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-77.38</v>
+        <v>-38.26</v>
       </c>
       <c r="L59" t="n">
-        <v>117.95</v>
+        <v>105.06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:41:57</t>
+          <t>08:49:49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="F60" t="n">
-        <v>8.49</v>
+        <v>9.5</v>
       </c>
       <c r="G60" t="n">
-        <v>134.4</v>
+        <v>121.5</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.3</v>
+        <v>-80.76000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>100.98</v>
+        <v>22.74</v>
       </c>
       <c r="L60" t="n">
-        <v>101.61</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:43:21</t>
+          <t>08:52:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="F61" t="n">
-        <v>9.08</v>
+        <v>8.33</v>
       </c>
       <c r="G61" t="n">
-        <v>137.2</v>
+        <v>147.2</v>
       </c>
       <c r="H61" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-79.27</v>
+        <v>48.83</v>
       </c>
       <c r="K61" t="n">
-        <v>3.05</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>79.33</v>
+        <v>94.06999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:47:54</t>
+          <t>08:56:37</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.04</v>
+        <v>2.69</v>
       </c>
       <c r="F62" t="n">
-        <v>9.300000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="G62" t="n">
-        <v>145.4</v>
+        <v>121.8</v>
       </c>
       <c r="H62" t="n">
-        <v>10.2</v>
+        <v>1.1</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-61.82</v>
+        <v>-191.51</v>
       </c>
       <c r="K62" t="n">
-        <v>-187.68</v>
+        <v>217.72</v>
       </c>
       <c r="L62" t="n">
-        <v>197.6</v>
+        <v>289.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:49:31</t>
+          <t>08:58:25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="F63" t="n">
-        <v>9.06</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>135.4</v>
+        <v>124.3</v>
       </c>
       <c r="H63" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="I63" t="n">
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>0.95</v>
+        <v>263.4</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.3</v>
+        <v>-124.51</v>
       </c>
       <c r="L63" t="n">
-        <v>6.37</v>
+        <v>291.34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:50:50</t>
+          <t>09:00:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="F64" t="n">
-        <v>8.85</v>
+        <v>8.48</v>
       </c>
       <c r="G64" t="n">
-        <v>133</v>
+        <v>141.6</v>
       </c>
       <c r="H64" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>59.11</v>
+        <v>211.31</v>
       </c>
       <c r="K64" t="n">
-        <v>-120.87</v>
+        <v>98.86</v>
       </c>
       <c r="L64" t="n">
-        <v>134.55</v>
+        <v>233.29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:55:01</t>
+          <t>09:04:46</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.34</v>
+        <v>2.84</v>
       </c>
       <c r="F65" t="n">
-        <v>8.57</v>
+        <v>9.34</v>
       </c>
       <c r="G65" t="n">
-        <v>137.2</v>
+        <v>130.8</v>
       </c>
       <c r="H65" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-201.07</v>
+        <v>-48.6</v>
       </c>
       <c r="K65" t="n">
-        <v>178.38</v>
+        <v>161.66</v>
       </c>
       <c r="L65" t="n">
-        <v>268.79</v>
+        <v>168.81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:55:51</t>
+          <t>09:06:02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="F66" t="n">
-        <v>9.300000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="G66" t="n">
-        <v>123.3</v>
+        <v>123.6</v>
       </c>
       <c r="H66" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>167.5</v>
+        <v>26.44</v>
       </c>
       <c r="K66" t="n">
-        <v>200.86</v>
+        <v>143.69</v>
       </c>
       <c r="L66" t="n">
-        <v>261.54</v>
+        <v>146.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:57:17</t>
+          <t>09:08:33</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="F67" t="n">
-        <v>8.279999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="G67" t="n">
-        <v>127.7</v>
+        <v>137</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-22.69</v>
+        <v>222.63</v>
       </c>
       <c r="K67" t="n">
-        <v>37.45</v>
+        <v>12.36</v>
       </c>
       <c r="L67" t="n">
-        <v>43.78</v>
+        <v>222.97</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:02:01</t>
+          <t>09:14:37</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.9</v>
+        <v>2.51</v>
       </c>
       <c r="F68" t="n">
-        <v>8.74</v>
+        <v>8.1</v>
       </c>
       <c r="G68" t="n">
-        <v>131.1</v>
+        <v>120.1</v>
       </c>
       <c r="H68" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>109.74</v>
+        <v>-194.73</v>
       </c>
       <c r="K68" t="n">
-        <v>276.2</v>
+        <v>-322.24</v>
       </c>
       <c r="L68" t="n">
-        <v>297.2</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>09:15:50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.64</v>
+        <v>3.12</v>
       </c>
       <c r="F69" t="n">
-        <v>8.69</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>129.2</v>
+        <v>147.7</v>
       </c>
       <c r="H69" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="I69" t="n">
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>125.86</v>
+        <v>118.87</v>
       </c>
       <c r="K69" t="n">
-        <v>214.65</v>
+        <v>-171.2</v>
       </c>
       <c r="L69" t="n">
-        <v>248.83</v>
+        <v>208.42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:06:15</t>
+          <t>09:18:17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="F70" t="n">
-        <v>8.779999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>139.3</v>
+        <v>125.1</v>
       </c>
       <c r="H70" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>376.57</v>
+        <v>50.64</v>
       </c>
       <c r="K70" t="n">
-        <v>-8.83</v>
+        <v>-211.01</v>
       </c>
       <c r="L70" t="n">
-        <v>376.68</v>
+        <v>217</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:12:11</t>
+          <t>09:23:33</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.72</v>
+        <v>3.19</v>
       </c>
       <c r="F71" t="n">
-        <v>9.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>130.9</v>
+        <v>138.7</v>
       </c>
       <c r="H71" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-189.34</v>
+        <v>-287.66</v>
       </c>
       <c r="K71" t="n">
-        <v>-88.43000000000001</v>
+        <v>-134.35</v>
       </c>
       <c r="L71" t="n">
-        <v>208.98</v>
+        <v>317.48</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:13:48</t>
+          <t>09:26:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>9.710000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="G72" t="n">
-        <v>139</v>
+        <v>133.5</v>
       </c>
       <c r="H72" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>527.89</v>
+        <v>281.84</v>
       </c>
       <c r="K72" t="n">
-        <v>144.87</v>
+        <v>251.47</v>
       </c>
       <c r="L72" t="n">
-        <v>547.4</v>
+        <v>377.72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:15:39</t>
+          <t>09:27:03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="F73" t="n">
-        <v>9.74</v>
+        <v>8.6</v>
       </c>
       <c r="G73" t="n">
-        <v>138.5</v>
+        <v>129.1</v>
       </c>
       <c r="H73" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>9.720000000000001</v>
+        <v>118.22</v>
       </c>
       <c r="K73" t="n">
-        <v>-523.85</v>
+        <v>-691.89</v>
       </c>
       <c r="L73" t="n">
-        <v>523.95</v>
+        <v>701.92</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:26:36</t>
+          <t>09:38:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="F74" t="n">
-        <v>9.17</v>
+        <v>9.15</v>
       </c>
       <c r="G74" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>46.13</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-65.84999999999999</v>
+        <v>107.26</v>
       </c>
       <c r="L74" t="n">
-        <v>80.40000000000001</v>
+        <v>127.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:28:10</t>
+          <t>09:39:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="F75" t="n">
-        <v>9.369999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="G75" t="n">
-        <v>138.3</v>
+        <v>130.4</v>
       </c>
       <c r="H75" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="I75" t="n">
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-38.88</v>
+        <v>54.71</v>
       </c>
       <c r="K75" t="n">
-        <v>-72.42</v>
+        <v>121.97</v>
       </c>
       <c r="L75" t="n">
-        <v>82.2</v>
+        <v>133.68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:29:47</t>
+          <t>09:40:39</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="F76" t="n">
-        <v>9.34</v>
+        <v>8.94</v>
       </c>
       <c r="G76" t="n">
-        <v>121.6</v>
+        <v>139.3</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>29.47</v>
+        <v>-139.47</v>
       </c>
       <c r="K76" t="n">
-        <v>-35.27</v>
+        <v>-192.25</v>
       </c>
       <c r="L76" t="n">
-        <v>45.96</v>
+        <v>237.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:34:11</t>
+          <t>09:44:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="F77" t="n">
-        <v>9.25</v>
+        <v>9.1</v>
       </c>
       <c r="G77" t="n">
-        <v>131.1</v>
+        <v>131</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>67.23</v>
+        <v>-290.62</v>
       </c>
       <c r="K77" t="n">
-        <v>-249.1</v>
+        <v>-195.61</v>
       </c>
       <c r="L77" t="n">
-        <v>258.02</v>
+        <v>350.32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:35:45</t>
+          <t>09:45:53</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.13</v>
+        <v>2.89</v>
       </c>
       <c r="F78" t="n">
-        <v>9.029999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="G78" t="n">
-        <v>130.7</v>
+        <v>142.5</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>48.41</v>
+        <v>-108.79</v>
       </c>
       <c r="K78" t="n">
-        <v>273.05</v>
+        <v>237.24</v>
       </c>
       <c r="L78" t="n">
-        <v>277.31</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:37:35</t>
+          <t>09:48:40</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="F79" t="n">
-        <v>8.91</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>145.4</v>
+        <v>134.4</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-88.19</v>
+        <v>-55.02</v>
       </c>
       <c r="K79" t="n">
-        <v>35.66</v>
+        <v>-110.85</v>
       </c>
       <c r="L79" t="n">
-        <v>95.13</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:42:27</t>
+          <t>09:52:50</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.16</v>
+        <v>2.68</v>
       </c>
       <c r="F80" t="n">
-        <v>9.380000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="G80" t="n">
-        <v>134.1</v>
+        <v>129</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>122.69</v>
+        <v>423.03</v>
       </c>
       <c r="K80" t="n">
-        <v>83.53</v>
+        <v>146.84</v>
       </c>
       <c r="L80" t="n">
-        <v>148.42</v>
+        <v>447.79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:43:31</t>
+          <t>09:53:53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.89</v>
+        <v>3.58</v>
       </c>
       <c r="F81" t="n">
-        <v>10.05</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>135.1</v>
+        <v>124.7</v>
       </c>
       <c r="H81" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-185.09</v>
+        <v>-453.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-87.61</v>
+        <v>-218.16</v>
       </c>
       <c r="L81" t="n">
-        <v>204.77</v>
+        <v>503.59</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:44:20</t>
+          <t>09:56:07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="F82" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>128.9</v>
+        <v>129.1</v>
       </c>
       <c r="H82" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>234.66</v>
+        <v>352.17</v>
       </c>
       <c r="K82" t="n">
-        <v>311.65</v>
+        <v>7.26</v>
       </c>
       <c r="L82" t="n">
-        <v>390.12</v>
+        <v>352.25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:50:25</t>
+          <t>10:01:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="F83" t="n">
-        <v>9.51</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>126.6</v>
+        <v>137.3</v>
       </c>
       <c r="H83" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-326.91</v>
+        <v>391.11</v>
       </c>
       <c r="K83" t="n">
-        <v>97.45999999999999</v>
+        <v>-1.15</v>
       </c>
       <c r="L83" t="n">
-        <v>341.13</v>
+        <v>391.11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:52:21</t>
+          <t>10:03:07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.73</v>
+        <v>3.43</v>
       </c>
       <c r="F84" t="n">
-        <v>8.85</v>
+        <v>9.42</v>
       </c>
       <c r="G84" t="n">
-        <v>127.6</v>
+        <v>127.5</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>160.72</v>
+        <v>-60.79</v>
       </c>
       <c r="K84" t="n">
-        <v>189.49</v>
+        <v>-532.01</v>
       </c>
       <c r="L84" t="n">
-        <v>248.47</v>
+        <v>535.48</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:54:15</t>
+          <t>10:04:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="F85" t="n">
-        <v>8.970000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>130.2</v>
+        <v>138</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-549.12</v>
+        <v>215.8</v>
       </c>
       <c r="K85" t="n">
-        <v>-109.28</v>
+        <v>-211.67</v>
       </c>
       <c r="L85" t="n">
-        <v>559.88</v>
+        <v>302.28</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:58:20</t>
+          <t>10:09:22</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.78</v>
+        <v>4.21</v>
       </c>
       <c r="F86" t="n">
-        <v>9.109999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="G86" t="n">
-        <v>123.3</v>
+        <v>121.4</v>
       </c>
       <c r="H86" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>445.91</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>246.43</v>
+        <v>1108.03</v>
       </c>
       <c r="L86" t="n">
-        <v>509.47</v>
+        <v>1110.75</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:00:01</t>
+          <t>10:12:02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="F87" t="n">
-        <v>8.76</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>132.7</v>
+        <v>136.5</v>
       </c>
       <c r="H87" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-184.87</v>
+        <v>579.24</v>
       </c>
       <c r="K87" t="n">
-        <v>-110.84</v>
+        <v>390.27</v>
       </c>
       <c r="L87" t="n">
-        <v>215.56</v>
+        <v>698.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:02:03</t>
+          <t>10:13:13</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.37</v>
+        <v>2.8</v>
       </c>
       <c r="F88" t="n">
-        <v>8.630000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="G88" t="n">
-        <v>134.8</v>
+        <v>143.5</v>
       </c>
       <c r="H88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>333.8</v>
+        <v>-9.34</v>
       </c>
       <c r="K88" t="n">
-        <v>170.89</v>
+        <v>-671.7</v>
       </c>
       <c r="L88" t="n">
-        <v>375</v>
+        <v>671.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-58.79</v>
+        <v>-54.7</v>
       </c>
       <c r="K14" t="n">
-        <v>-14.18</v>
+        <v>-13.2</v>
       </c>
       <c r="L14" t="n">
-        <v>60.47</v>
+        <v>56.27</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-30.37</v>
+        <v>-27.88</v>
       </c>
       <c r="K15" t="n">
-        <v>-107.92</v>
+        <v>-99.06999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>112.11</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-136.22</v>
+        <v>-119.94</v>
       </c>
       <c r="K16" t="n">
-        <v>37.57</v>
+        <v>33.08</v>
       </c>
       <c r="L16" t="n">
-        <v>141.31</v>
+        <v>124.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-144.91</v>
+        <v>-108.01</v>
       </c>
       <c r="K17" t="n">
-        <v>-145.65</v>
+        <v>-108.56</v>
       </c>
       <c r="L17" t="n">
-        <v>205.45</v>
+        <v>153.14</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>40.72</v>
+        <v>55.58</v>
       </c>
       <c r="K18" t="n">
-        <v>98.01000000000001</v>
+        <v>133.79</v>
       </c>
       <c r="L18" t="n">
-        <v>106.13</v>
+        <v>144.87</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-154.77</v>
+        <v>-157.63</v>
       </c>
       <c r="K19" t="n">
-        <v>-130.06</v>
+        <v>-132.47</v>
       </c>
       <c r="L19" t="n">
-        <v>202.16</v>
+        <v>205.9</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-180.58</v>
+        <v>-239.19</v>
       </c>
       <c r="K20" t="n">
-        <v>-92.06</v>
+        <v>-121.93</v>
       </c>
       <c r="L20" t="n">
-        <v>202.69</v>
+        <v>268.48</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-247.55</v>
+        <v>-249.73</v>
       </c>
       <c r="K21" t="n">
-        <v>228.21</v>
+        <v>230.23</v>
       </c>
       <c r="L21" t="n">
-        <v>336.69</v>
+        <v>339.66</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-40.88</v>
+        <v>-100.35</v>
       </c>
       <c r="K22" t="n">
-        <v>-46.69</v>
+        <v>-114.6</v>
       </c>
       <c r="L22" t="n">
-        <v>62.05</v>
+        <v>152.32</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-158.44</v>
+        <v>-152.54</v>
       </c>
       <c r="K23" t="n">
-        <v>505.33</v>
+        <v>486.53</v>
       </c>
       <c r="L23" t="n">
-        <v>529.59</v>
+        <v>509.88</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>229.52</v>
+        <v>316.6</v>
       </c>
       <c r="K24" t="n">
-        <v>-16.64</v>
+        <v>-22.95</v>
       </c>
       <c r="L24" t="n">
-        <v>230.13</v>
+        <v>317.43</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-400.14</v>
+        <v>-464.63</v>
       </c>
       <c r="K25" t="n">
-        <v>5.19</v>
+        <v>6.03</v>
       </c>
       <c r="L25" t="n">
-        <v>400.17</v>
+        <v>464.67</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-140.89</v>
+        <v>-215.9</v>
       </c>
       <c r="K26" t="n">
-        <v>205.07</v>
+        <v>314.26</v>
       </c>
       <c r="L26" t="n">
-        <v>248.81</v>
+        <v>381.27</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>385.23</v>
+        <v>409.86</v>
       </c>
       <c r="K27" t="n">
-        <v>323.98</v>
+        <v>344.7</v>
       </c>
       <c r="L27" t="n">
-        <v>503.35</v>
+        <v>535.54</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>254.14</v>
+        <v>375.35</v>
       </c>
       <c r="K28" t="n">
-        <v>-226.86</v>
+        <v>-335.05</v>
       </c>
       <c r="L28" t="n">
-        <v>340.66</v>
+        <v>503.14</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>126.74</v>
+        <v>131.45</v>
       </c>
       <c r="K29" t="n">
-        <v>15.16</v>
+        <v>15.72</v>
       </c>
       <c r="L29" t="n">
-        <v>127.64</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>32.45</v>
+        <v>22.26</v>
       </c>
       <c r="K30" t="n">
-        <v>181.22</v>
+        <v>124.32</v>
       </c>
       <c r="L30" t="n">
-        <v>184.1</v>
+        <v>126.3</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>144.97</v>
+        <v>115.24</v>
       </c>
       <c r="K31" t="n">
-        <v>120.37</v>
+        <v>95.69</v>
       </c>
       <c r="L31" t="n">
-        <v>188.42</v>
+        <v>149.79</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="K32" t="n">
-        <v>-59.77</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>59.79</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-25.14</v>
+        <v>-25.45</v>
       </c>
       <c r="K33" t="n">
-        <v>148.03</v>
+        <v>149.9</v>
       </c>
       <c r="L33" t="n">
-        <v>150.15</v>
+        <v>152.04</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>98.31999999999999</v>
+        <v>101.01</v>
       </c>
       <c r="K34" t="n">
-        <v>97.38</v>
+        <v>100.05</v>
       </c>
       <c r="L34" t="n">
-        <v>138.38</v>
+        <v>142.17</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-262.14</v>
+        <v>-252.3</v>
       </c>
       <c r="K35" t="n">
-        <v>-68.65000000000001</v>
+        <v>-66.06999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>270.98</v>
+        <v>260.81</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-237.19</v>
+        <v>-274.69</v>
       </c>
       <c r="K36" t="n">
-        <v>-216.03</v>
+        <v>-250.18</v>
       </c>
       <c r="L36" t="n">
-        <v>320.82</v>
+        <v>371.55</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-95.61</v>
+        <v>-99.92</v>
       </c>
       <c r="K37" t="n">
-        <v>266.17</v>
+        <v>278.18</v>
       </c>
       <c r="L37" t="n">
-        <v>282.82</v>
+        <v>295.58</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>374.95</v>
+        <v>380.46</v>
       </c>
       <c r="K38" t="n">
-        <v>-289.69</v>
+        <v>-293.95</v>
       </c>
       <c r="L38" t="n">
-        <v>473.82</v>
+        <v>480.79</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-452.81</v>
+        <v>-412.68</v>
       </c>
       <c r="K39" t="n">
-        <v>-42.9</v>
+        <v>-39.1</v>
       </c>
       <c r="L39" t="n">
-        <v>454.83</v>
+        <v>414.52</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>413.66</v>
+        <v>403.29</v>
       </c>
       <c r="K40" t="n">
-        <v>91.67</v>
+        <v>89.37</v>
       </c>
       <c r="L40" t="n">
-        <v>423.7</v>
+        <v>413.08</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>395.19</v>
+        <v>525.25</v>
       </c>
       <c r="K41" t="n">
-        <v>-207.92</v>
+        <v>-276.35</v>
       </c>
       <c r="L41" t="n">
-        <v>446.55</v>
+        <v>593.51</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-256.77</v>
+        <v>-365.62</v>
       </c>
       <c r="K42" t="n">
-        <v>-82.73999999999999</v>
+        <v>-117.81</v>
       </c>
       <c r="L42" t="n">
-        <v>269.78</v>
+        <v>384.13</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-499.09</v>
+        <v>-582.3200000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-53.05</v>
+        <v>-61.9</v>
       </c>
       <c r="L43" t="n">
-        <v>501.9</v>
+        <v>585.6</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>248.23</v>
+        <v>204.34</v>
       </c>
       <c r="K44" t="n">
-        <v>28.16</v>
+        <v>23.18</v>
       </c>
       <c r="L44" t="n">
-        <v>249.83</v>
+        <v>205.65</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>78.03</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>128.46</v>
+        <v>117.7</v>
       </c>
       <c r="L45" t="n">
-        <v>150.3</v>
+        <v>137.71</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>28.03</v>
+        <v>36.46</v>
       </c>
       <c r="K46" t="n">
-        <v>-112.14</v>
+        <v>-145.86</v>
       </c>
       <c r="L46" t="n">
-        <v>115.59</v>
+        <v>150.35</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-115.68</v>
+        <v>-133.59</v>
       </c>
       <c r="K47" t="n">
-        <v>-118.68</v>
+        <v>-137.06</v>
       </c>
       <c r="L47" t="n">
-        <v>165.73</v>
+        <v>191.39</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>59.79</v>
+        <v>83.66</v>
       </c>
       <c r="K48" t="n">
-        <v>65.31</v>
+        <v>91.39</v>
       </c>
       <c r="L48" t="n">
-        <v>88.54000000000001</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>39.74</v>
+        <v>42.28</v>
       </c>
       <c r="K49" t="n">
-        <v>222.16</v>
+        <v>236.34</v>
       </c>
       <c r="L49" t="n">
-        <v>225.69</v>
+        <v>240.09</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-205.24</v>
+        <v>-212.82</v>
       </c>
       <c r="K50" t="n">
-        <v>400.75</v>
+        <v>415.55</v>
       </c>
       <c r="L50" t="n">
-        <v>450.25</v>
+        <v>466.88</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>45.45</v>
+        <v>69.22</v>
       </c>
       <c r="K51" t="n">
-        <v>141.75</v>
+        <v>215.87</v>
       </c>
       <c r="L51" t="n">
-        <v>148.86</v>
+        <v>226.69</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>140.79</v>
+        <v>146.02</v>
       </c>
       <c r="K52" t="n">
-        <v>-173.53</v>
+        <v>-179.98</v>
       </c>
       <c r="L52" t="n">
-        <v>223.46</v>
+        <v>231.76</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>554.17</v>
+        <v>532.78</v>
       </c>
       <c r="K53" t="n">
-        <v>16.38</v>
+        <v>15.75</v>
       </c>
       <c r="L53" t="n">
-        <v>554.41</v>
+        <v>533.01</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>470.12</v>
+        <v>561.9299999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-13.37</v>
+        <v>-15.98</v>
       </c>
       <c r="L54" t="n">
-        <v>470.31</v>
+        <v>562.16</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>180.13</v>
+        <v>280.69</v>
       </c>
       <c r="K55" t="n">
-        <v>-56.39</v>
+        <v>-87.87</v>
       </c>
       <c r="L55" t="n">
-        <v>188.75</v>
+        <v>294.12</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>353.03</v>
+        <v>409.33</v>
       </c>
       <c r="K56" t="n">
-        <v>471.37</v>
+        <v>546.54</v>
       </c>
       <c r="L56" t="n">
-        <v>588.91</v>
+        <v>682.83</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>740.33</v>
+        <v>833.8</v>
       </c>
       <c r="K57" t="n">
-        <v>205.5</v>
+        <v>231.44</v>
       </c>
       <c r="L57" t="n">
-        <v>768.3200000000001</v>
+        <v>865.33</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-558.54</v>
+        <v>-668.23</v>
       </c>
       <c r="K58" t="n">
-        <v>-148.17</v>
+        <v>-177.27</v>
       </c>
       <c r="L58" t="n">
-        <v>577.86</v>
+        <v>691.34</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-97.84999999999999</v>
+        <v>-101.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.26</v>
+        <v>-39.58</v>
       </c>
       <c r="L59" t="n">
-        <v>105.06</v>
+        <v>108.69</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-80.76000000000001</v>
+        <v>-96.81999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>22.74</v>
+        <v>27.26</v>
       </c>
       <c r="L60" t="n">
-        <v>83.89</v>
+        <v>100.58</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>48.83</v>
+        <v>54.62</v>
       </c>
       <c r="K61" t="n">
-        <v>80.40000000000001</v>
+        <v>89.94</v>
       </c>
       <c r="L61" t="n">
-        <v>94.06999999999999</v>
+        <v>105.23</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-191.51</v>
+        <v>-151.52</v>
       </c>
       <c r="K62" t="n">
-        <v>217.72</v>
+        <v>172.26</v>
       </c>
       <c r="L62" t="n">
-        <v>289.96</v>
+        <v>229.41</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>263.4</v>
+        <v>244.93</v>
       </c>
       <c r="K63" t="n">
-        <v>-124.51</v>
+        <v>-115.79</v>
       </c>
       <c r="L63" t="n">
-        <v>291.34</v>
+        <v>270.92</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>211.31</v>
+        <v>199.77</v>
       </c>
       <c r="K64" t="n">
-        <v>98.86</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>233.29</v>
+        <v>220.55</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-48.6</v>
+        <v>-65.61</v>
       </c>
       <c r="K65" t="n">
-        <v>161.66</v>
+        <v>218.24</v>
       </c>
       <c r="L65" t="n">
-        <v>168.81</v>
+        <v>227.89</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>26.44</v>
+        <v>36.42</v>
       </c>
       <c r="K66" t="n">
-        <v>143.69</v>
+        <v>197.9</v>
       </c>
       <c r="L66" t="n">
-        <v>146.1</v>
+        <v>201.22</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>222.63</v>
+        <v>247.51</v>
       </c>
       <c r="K67" t="n">
-        <v>12.36</v>
+        <v>13.74</v>
       </c>
       <c r="L67" t="n">
-        <v>222.97</v>
+        <v>247.89</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-194.73</v>
+        <v>-208.95</v>
       </c>
       <c r="K68" t="n">
-        <v>-322.24</v>
+        <v>-345.77</v>
       </c>
       <c r="L68" t="n">
-        <v>376.5</v>
+        <v>404</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>118.87</v>
+        <v>177.87</v>
       </c>
       <c r="K69" t="n">
-        <v>-171.2</v>
+        <v>-256.18</v>
       </c>
       <c r="L69" t="n">
-        <v>208.42</v>
+        <v>311.87</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>50.64</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-211.01</v>
+        <v>-295.1</v>
       </c>
       <c r="L70" t="n">
-        <v>217</v>
+        <v>303.48</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-287.66</v>
+        <v>-425.79</v>
       </c>
       <c r="K71" t="n">
-        <v>-134.35</v>
+        <v>-198.86</v>
       </c>
       <c r="L71" t="n">
-        <v>317.48</v>
+        <v>469.94</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>281.84</v>
+        <v>411.64</v>
       </c>
       <c r="K72" t="n">
-        <v>251.47</v>
+        <v>367.29</v>
       </c>
       <c r="L72" t="n">
-        <v>377.72</v>
+        <v>551.6799999999999</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>118.22</v>
+        <v>129.48</v>
       </c>
       <c r="K73" t="n">
-        <v>-691.89</v>
+        <v>-757.8</v>
       </c>
       <c r="L73" t="n">
-        <v>701.92</v>
+        <v>768.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>69.01000000000001</v>
+        <v>63.86</v>
       </c>
       <c r="K74" t="n">
-        <v>107.26</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>127.54</v>
+        <v>118.03</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>54.71</v>
+        <v>47</v>
       </c>
       <c r="K75" t="n">
-        <v>121.97</v>
+        <v>104.78</v>
       </c>
       <c r="L75" t="n">
-        <v>133.68</v>
+        <v>114.83</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-139.47</v>
+        <v>-131.4</v>
       </c>
       <c r="K76" t="n">
-        <v>-192.25</v>
+        <v>-181.13</v>
       </c>
       <c r="L76" t="n">
-        <v>237.51</v>
+        <v>223.77</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-290.62</v>
+        <v>-235.96</v>
       </c>
       <c r="K77" t="n">
-        <v>-195.61</v>
+        <v>-158.82</v>
       </c>
       <c r="L77" t="n">
-        <v>350.32</v>
+        <v>284.43</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-108.79</v>
+        <v>-103.18</v>
       </c>
       <c r="K78" t="n">
-        <v>237.24</v>
+        <v>225.01</v>
       </c>
       <c r="L78" t="n">
-        <v>261</v>
+        <v>247.54</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.02</v>
+        <v>-68.92</v>
       </c>
       <c r="K79" t="n">
-        <v>-110.85</v>
+        <v>-138.84</v>
       </c>
       <c r="L79" t="n">
-        <v>123.75</v>
+        <v>155.01</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>423.03</v>
+        <v>358.78</v>
       </c>
       <c r="K80" t="n">
-        <v>146.84</v>
+        <v>124.54</v>
       </c>
       <c r="L80" t="n">
-        <v>447.79</v>
+        <v>379.78</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-453.88</v>
+        <v>-456.96</v>
       </c>
       <c r="K81" t="n">
-        <v>-218.16</v>
+        <v>-219.64</v>
       </c>
       <c r="L81" t="n">
-        <v>503.59</v>
+        <v>507.01</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>352.17</v>
+        <v>372.47</v>
       </c>
       <c r="K82" t="n">
-        <v>7.26</v>
+        <v>7.67</v>
       </c>
       <c r="L82" t="n">
-        <v>352.25</v>
+        <v>372.55</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>391.11</v>
+        <v>483.85</v>
       </c>
       <c r="K83" t="n">
-        <v>-1.15</v>
+        <v>-1.42</v>
       </c>
       <c r="L83" t="n">
-        <v>391.11</v>
+        <v>483.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-60.79</v>
+        <v>-63.61</v>
       </c>
       <c r="K84" t="n">
-        <v>-532.01</v>
+        <v>-556.76</v>
       </c>
       <c r="L84" t="n">
-        <v>535.48</v>
+        <v>560.38</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>215.8</v>
+        <v>269.13</v>
       </c>
       <c r="K85" t="n">
-        <v>-211.67</v>
+        <v>-263.98</v>
       </c>
       <c r="L85" t="n">
-        <v>302.28</v>
+        <v>376.99</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>77.68000000000001</v>
+        <v>83.44</v>
       </c>
       <c r="K86" t="n">
-        <v>1108.03</v>
+        <v>1190.2</v>
       </c>
       <c r="L86" t="n">
-        <v>1110.75</v>
+        <v>1193.12</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>579.24</v>
+        <v>581.77</v>
       </c>
       <c r="K87" t="n">
-        <v>390.27</v>
+        <v>391.98</v>
       </c>
       <c r="L87" t="n">
-        <v>698.45</v>
+        <v>701.5</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-9.34</v>
+        <v>-9.83</v>
       </c>
       <c r="K88" t="n">
-        <v>-671.7</v>
+        <v>-706.45</v>
       </c>
       <c r="L88" t="n">
-        <v>671.77</v>
+        <v>706.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-54.7</v>
+        <v>-53.43</v>
       </c>
       <c r="K14" t="n">
-        <v>-13.2</v>
+        <v>-12.89</v>
       </c>
       <c r="L14" t="n">
-        <v>56.27</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-27.88</v>
+        <v>-22.68</v>
       </c>
       <c r="K15" t="n">
-        <v>-99.06999999999999</v>
+        <v>-80.59</v>
       </c>
       <c r="L15" t="n">
-        <v>102.92</v>
+        <v>83.72</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-119.94</v>
+        <v>-101.65</v>
       </c>
       <c r="K16" t="n">
-        <v>33.08</v>
+        <v>28.04</v>
       </c>
       <c r="L16" t="n">
-        <v>124.42</v>
+        <v>105.45</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-108.01</v>
+        <v>-93.93000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-108.56</v>
+        <v>-94.41</v>
       </c>
       <c r="L17" t="n">
-        <v>153.14</v>
+        <v>133.17</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>55.58</v>
+        <v>38.28</v>
       </c>
       <c r="K18" t="n">
-        <v>133.79</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>144.87</v>
+        <v>99.78</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-157.63</v>
+        <v>-109.56</v>
       </c>
       <c r="K19" t="n">
-        <v>-132.47</v>
+        <v>-92.06999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>205.9</v>
+        <v>143.11</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-239.19</v>
+        <v>-142.58</v>
       </c>
       <c r="K20" t="n">
-        <v>-121.93</v>
+        <v>-72.68000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>268.48</v>
+        <v>160.04</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-249.73</v>
+        <v>-159.49</v>
       </c>
       <c r="K21" t="n">
-        <v>230.23</v>
+        <v>147.03</v>
       </c>
       <c r="L21" t="n">
-        <v>339.66</v>
+        <v>216.92</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-100.35</v>
+        <v>-63.3</v>
       </c>
       <c r="K22" t="n">
-        <v>-114.6</v>
+        <v>-72.29000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>152.32</v>
+        <v>96.09</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-152.54</v>
+        <v>-90.20999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>486.53</v>
+        <v>287.73</v>
       </c>
       <c r="L23" t="n">
-        <v>509.88</v>
+        <v>301.54</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>316.6</v>
+        <v>186.77</v>
       </c>
       <c r="K24" t="n">
-        <v>-22.95</v>
+        <v>-13.54</v>
       </c>
       <c r="L24" t="n">
-        <v>317.43</v>
+        <v>187.26</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-464.63</v>
+        <v>-244.45</v>
       </c>
       <c r="K25" t="n">
-        <v>6.03</v>
+        <v>3.17</v>
       </c>
       <c r="L25" t="n">
-        <v>464.67</v>
+        <v>244.47</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-215.9</v>
+        <v>-109.02</v>
       </c>
       <c r="K26" t="n">
-        <v>314.26</v>
+        <v>158.68</v>
       </c>
       <c r="L26" t="n">
-        <v>381.27</v>
+        <v>192.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>409.86</v>
+        <v>218.44</v>
       </c>
       <c r="K27" t="n">
-        <v>344.7</v>
+        <v>183.71</v>
       </c>
       <c r="L27" t="n">
-        <v>535.54</v>
+        <v>285.43</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>375.35</v>
+        <v>182.88</v>
       </c>
       <c r="K28" t="n">
-        <v>-335.05</v>
+        <v>-163.24</v>
       </c>
       <c r="L28" t="n">
-        <v>503.14</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>131.45</v>
+        <v>103.89</v>
       </c>
       <c r="K29" t="n">
-        <v>15.72</v>
+        <v>12.43</v>
       </c>
       <c r="L29" t="n">
-        <v>132.39</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>22.26</v>
+        <v>18.82</v>
       </c>
       <c r="K30" t="n">
-        <v>124.32</v>
+        <v>105.11</v>
       </c>
       <c r="L30" t="n">
-        <v>126.3</v>
+        <v>106.78</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>115.24</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>95.69</v>
+        <v>78.17</v>
       </c>
       <c r="L31" t="n">
-        <v>149.79</v>
+        <v>122.37</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="K32" t="n">
-        <v>-68.23999999999999</v>
+        <v>-56.92</v>
       </c>
       <c r="L32" t="n">
-        <v>68.27</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-25.45</v>
+        <v>-20.41</v>
       </c>
       <c r="K33" t="n">
-        <v>149.9</v>
+        <v>120.17</v>
       </c>
       <c r="L33" t="n">
-        <v>152.04</v>
+        <v>121.89</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>101.01</v>
+        <v>73.5</v>
       </c>
       <c r="K34" t="n">
-        <v>100.05</v>
+        <v>72.8</v>
       </c>
       <c r="L34" t="n">
-        <v>142.17</v>
+        <v>103.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-252.3</v>
+        <v>-171.64</v>
       </c>
       <c r="K35" t="n">
-        <v>-66.06999999999999</v>
+        <v>-44.95</v>
       </c>
       <c r="L35" t="n">
-        <v>260.81</v>
+        <v>177.43</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-274.69</v>
+        <v>-158.37</v>
       </c>
       <c r="K36" t="n">
-        <v>-250.18</v>
+        <v>-144.24</v>
       </c>
       <c r="L36" t="n">
-        <v>371.55</v>
+        <v>214.21</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-99.92</v>
+        <v>-60.84</v>
       </c>
       <c r="K37" t="n">
-        <v>278.18</v>
+        <v>169.38</v>
       </c>
       <c r="L37" t="n">
-        <v>295.58</v>
+        <v>179.98</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>380.46</v>
+        <v>218.16</v>
       </c>
       <c r="K38" t="n">
-        <v>-293.95</v>
+        <v>-168.55</v>
       </c>
       <c r="L38" t="n">
-        <v>480.79</v>
+        <v>275.68</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-412.68</v>
+        <v>-248.67</v>
       </c>
       <c r="K39" t="n">
-        <v>-39.1</v>
+        <v>-23.56</v>
       </c>
       <c r="L39" t="n">
-        <v>414.52</v>
+        <v>249.79</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>403.29</v>
+        <v>222.01</v>
       </c>
       <c r="K40" t="n">
-        <v>89.37</v>
+        <v>49.2</v>
       </c>
       <c r="L40" t="n">
-        <v>413.08</v>
+        <v>227.39</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>525.25</v>
+        <v>265.18</v>
       </c>
       <c r="K41" t="n">
-        <v>-276.35</v>
+        <v>-139.52</v>
       </c>
       <c r="L41" t="n">
-        <v>593.51</v>
+        <v>299.64</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-365.62</v>
+        <v>-189.58</v>
       </c>
       <c r="K42" t="n">
-        <v>-117.81</v>
+        <v>-61.08</v>
       </c>
       <c r="L42" t="n">
-        <v>384.13</v>
+        <v>199.17</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-582.3200000000001</v>
+        <v>-297.36</v>
       </c>
       <c r="K43" t="n">
-        <v>-61.9</v>
+        <v>-31.61</v>
       </c>
       <c r="L43" t="n">
-        <v>585.6</v>
+        <v>299.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>204.34</v>
+        <v>154.06</v>
       </c>
       <c r="K44" t="n">
-        <v>23.18</v>
+        <v>17.48</v>
       </c>
       <c r="L44" t="n">
-        <v>205.65</v>
+        <v>155.05</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>71.48999999999999</v>
+        <v>54.91</v>
       </c>
       <c r="K45" t="n">
-        <v>117.7</v>
+        <v>90.41</v>
       </c>
       <c r="L45" t="n">
-        <v>137.71</v>
+        <v>105.78</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>36.46</v>
+        <v>25.26</v>
       </c>
       <c r="K46" t="n">
-        <v>-145.86</v>
+        <v>-101.07</v>
       </c>
       <c r="L46" t="n">
-        <v>150.35</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-133.59</v>
+        <v>-91.38</v>
       </c>
       <c r="K47" t="n">
-        <v>-137.06</v>
+        <v>-93.75</v>
       </c>
       <c r="L47" t="n">
-        <v>191.39</v>
+        <v>130.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>83.66</v>
+        <v>62.72</v>
       </c>
       <c r="K48" t="n">
-        <v>91.39</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>123.9</v>
+        <v>92.88</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>42.28</v>
+        <v>28.11</v>
       </c>
       <c r="K49" t="n">
-        <v>236.34</v>
+        <v>157.15</v>
       </c>
       <c r="L49" t="n">
-        <v>240.09</v>
+        <v>159.65</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-212.82</v>
+        <v>-123.51</v>
       </c>
       <c r="K50" t="n">
-        <v>415.55</v>
+        <v>241.16</v>
       </c>
       <c r="L50" t="n">
-        <v>466.88</v>
+        <v>270.95</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>69.22</v>
+        <v>43.14</v>
       </c>
       <c r="K51" t="n">
-        <v>215.87</v>
+        <v>134.56</v>
       </c>
       <c r="L51" t="n">
-        <v>226.69</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>146.02</v>
+        <v>99.45</v>
       </c>
       <c r="K52" t="n">
-        <v>-179.98</v>
+        <v>-122.58</v>
       </c>
       <c r="L52" t="n">
-        <v>231.76</v>
+        <v>157.85</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>532.78</v>
+        <v>328.78</v>
       </c>
       <c r="K53" t="n">
-        <v>15.75</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>533.01</v>
+        <v>328.92</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>561.9299999999999</v>
+        <v>298.57</v>
       </c>
       <c r="K54" t="n">
-        <v>-15.98</v>
+        <v>-8.49</v>
       </c>
       <c r="L54" t="n">
-        <v>562.16</v>
+        <v>298.69</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>280.69</v>
+        <v>164.89</v>
       </c>
       <c r="K55" t="n">
-        <v>-87.87</v>
+        <v>-51.62</v>
       </c>
       <c r="L55" t="n">
-        <v>294.12</v>
+        <v>172.79</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>409.33</v>
+        <v>225.45</v>
       </c>
       <c r="K56" t="n">
-        <v>546.54</v>
+        <v>301.03</v>
       </c>
       <c r="L56" t="n">
-        <v>682.83</v>
+        <v>376.09</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>833.8</v>
+        <v>430.32</v>
       </c>
       <c r="K57" t="n">
-        <v>231.44</v>
+        <v>119.45</v>
       </c>
       <c r="L57" t="n">
-        <v>865.33</v>
+        <v>446.59</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-668.23</v>
+        <v>-365.14</v>
       </c>
       <c r="K58" t="n">
-        <v>-177.27</v>
+        <v>-96.86</v>
       </c>
       <c r="L58" t="n">
-        <v>691.34</v>
+        <v>377.77</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-101.23</v>
+        <v>-78.02</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.58</v>
+        <v>-30.5</v>
       </c>
       <c r="L59" t="n">
-        <v>108.69</v>
+        <v>83.77</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-96.81999999999999</v>
+        <v>-79.48999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>27.26</v>
+        <v>22.38</v>
       </c>
       <c r="L60" t="n">
-        <v>100.58</v>
+        <v>82.58</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>54.62</v>
+        <v>46.16</v>
       </c>
       <c r="K61" t="n">
-        <v>89.94</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>105.23</v>
+        <v>88.92</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-151.52</v>
+        <v>-120.97</v>
       </c>
       <c r="K62" t="n">
-        <v>172.26</v>
+        <v>137.53</v>
       </c>
       <c r="L62" t="n">
-        <v>229.41</v>
+        <v>183.16</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>244.93</v>
+        <v>175.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-115.79</v>
+        <v>-83.06</v>
       </c>
       <c r="L63" t="n">
-        <v>270.92</v>
+        <v>194.35</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>199.77</v>
+        <v>142.96</v>
       </c>
       <c r="K64" t="n">
-        <v>93.45999999999999</v>
+        <v>66.88</v>
       </c>
       <c r="L64" t="n">
-        <v>220.55</v>
+        <v>157.83</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-65.61</v>
+        <v>-40.66</v>
       </c>
       <c r="K65" t="n">
-        <v>218.24</v>
+        <v>135.26</v>
       </c>
       <c r="L65" t="n">
-        <v>227.89</v>
+        <v>141.24</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>36.42</v>
+        <v>23.88</v>
       </c>
       <c r="K66" t="n">
-        <v>197.9</v>
+        <v>129.77</v>
       </c>
       <c r="L66" t="n">
-        <v>201.22</v>
+        <v>131.95</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>247.51</v>
+        <v>160.58</v>
       </c>
       <c r="K67" t="n">
-        <v>13.74</v>
+        <v>8.92</v>
       </c>
       <c r="L67" t="n">
-        <v>247.89</v>
+        <v>160.83</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-208.95</v>
+        <v>-118.2</v>
       </c>
       <c r="K68" t="n">
-        <v>-345.77</v>
+        <v>-195.6</v>
       </c>
       <c r="L68" t="n">
-        <v>404</v>
+        <v>228.54</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>177.87</v>
+        <v>101.43</v>
       </c>
       <c r="K69" t="n">
-        <v>-256.18</v>
+        <v>-146.09</v>
       </c>
       <c r="L69" t="n">
-        <v>311.87</v>
+        <v>177.85</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>70.81999999999999</v>
+        <v>40.97</v>
       </c>
       <c r="K70" t="n">
-        <v>-295.1</v>
+        <v>-170.72</v>
       </c>
       <c r="L70" t="n">
-        <v>303.48</v>
+        <v>175.57</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-425.79</v>
+        <v>-227.81</v>
       </c>
       <c r="K71" t="n">
-        <v>-198.86</v>
+        <v>-106.39</v>
       </c>
       <c r="L71" t="n">
-        <v>469.94</v>
+        <v>251.43</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>411.64</v>
+        <v>202.27</v>
       </c>
       <c r="K72" t="n">
-        <v>367.29</v>
+        <v>180.47</v>
       </c>
       <c r="L72" t="n">
-        <v>551.6799999999999</v>
+        <v>271.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>129.48</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-757.8</v>
+        <v>-389.77</v>
       </c>
       <c r="L73" t="n">
-        <v>768.78</v>
+        <v>395.42</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>63.86</v>
+        <v>55.05</v>
       </c>
       <c r="K74" t="n">
-        <v>99.26000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="L74" t="n">
-        <v>118.03</v>
+        <v>101.74</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>47</v>
+        <v>39.64</v>
       </c>
       <c r="K75" t="n">
-        <v>104.78</v>
+        <v>88.37</v>
       </c>
       <c r="L75" t="n">
-        <v>114.83</v>
+        <v>96.84999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-131.4</v>
+        <v>-95.94</v>
       </c>
       <c r="K76" t="n">
-        <v>-181.13</v>
+        <v>-132.25</v>
       </c>
       <c r="L76" t="n">
-        <v>223.77</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-235.96</v>
+        <v>-179.17</v>
       </c>
       <c r="K77" t="n">
-        <v>-158.82</v>
+        <v>-120.59</v>
       </c>
       <c r="L77" t="n">
-        <v>284.43</v>
+        <v>215.97</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-103.18</v>
+        <v>-71.47</v>
       </c>
       <c r="K78" t="n">
-        <v>225.01</v>
+        <v>155.86</v>
       </c>
       <c r="L78" t="n">
-        <v>247.54</v>
+        <v>171.47</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-68.92</v>
+        <v>-51.79</v>
       </c>
       <c r="K79" t="n">
-        <v>-138.84</v>
+        <v>-104.34</v>
       </c>
       <c r="L79" t="n">
-        <v>155.01</v>
+        <v>116.48</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>358.78</v>
+        <v>248.6</v>
       </c>
       <c r="K80" t="n">
-        <v>124.54</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>379.78</v>
+        <v>263.15</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-456.96</v>
+        <v>-286.28</v>
       </c>
       <c r="K81" t="n">
-        <v>-219.64</v>
+        <v>-137.6</v>
       </c>
       <c r="L81" t="n">
-        <v>507.01</v>
+        <v>317.63</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>372.47</v>
+        <v>232.35</v>
       </c>
       <c r="K82" t="n">
-        <v>7.67</v>
+        <v>4.79</v>
       </c>
       <c r="L82" t="n">
-        <v>372.55</v>
+        <v>232.4</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>483.85</v>
+        <v>249.23</v>
       </c>
       <c r="K83" t="n">
-        <v>-1.42</v>
+        <v>-0.73</v>
       </c>
       <c r="L83" t="n">
-        <v>483.85</v>
+        <v>249.23</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-63.61</v>
+        <v>-38.13</v>
       </c>
       <c r="K84" t="n">
-        <v>-556.76</v>
+        <v>-333.76</v>
       </c>
       <c r="L84" t="n">
-        <v>560.38</v>
+        <v>335.93</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>269.13</v>
+        <v>157.89</v>
       </c>
       <c r="K85" t="n">
-        <v>-263.98</v>
+        <v>-154.87</v>
       </c>
       <c r="L85" t="n">
-        <v>376.99</v>
+        <v>221.16</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>83.44</v>
+        <v>44.51</v>
       </c>
       <c r="K86" t="n">
-        <v>1190.2</v>
+        <v>634.86</v>
       </c>
       <c r="L86" t="n">
-        <v>1193.12</v>
+        <v>636.42</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>581.77</v>
+        <v>330.68</v>
       </c>
       <c r="K87" t="n">
-        <v>391.98</v>
+        <v>222.8</v>
       </c>
       <c r="L87" t="n">
-        <v>701.5</v>
+        <v>398.74</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-9.83</v>
+        <v>-5.38</v>
       </c>
       <c r="K88" t="n">
-        <v>-706.45</v>
+        <v>-386.77</v>
       </c>
       <c r="L88" t="n">
-        <v>706.52</v>
+        <v>386.81</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-53.43</v>
+        <v>-48.73</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.89</v>
+        <v>-11.76</v>
       </c>
       <c r="L14" t="n">
-        <v>54.96</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-22.68</v>
+        <v>-21.18</v>
       </c>
       <c r="K15" t="n">
-        <v>-80.59</v>
+        <v>-75.26000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>83.72</v>
+        <v>78.19</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-101.65</v>
+        <v>-93.61</v>
       </c>
       <c r="K16" t="n">
-        <v>28.04</v>
+        <v>25.82</v>
       </c>
       <c r="L16" t="n">
-        <v>105.45</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-93.93000000000001</v>
+        <v>-88.59</v>
       </c>
       <c r="K17" t="n">
-        <v>-94.41</v>
+        <v>-89.05</v>
       </c>
       <c r="L17" t="n">
-        <v>133.17</v>
+        <v>125.61</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>38.28</v>
+        <v>37.26</v>
       </c>
       <c r="K18" t="n">
-        <v>92.15000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="L18" t="n">
-        <v>99.78</v>
+        <v>97.13</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-109.56</v>
+        <v>-106.49</v>
       </c>
       <c r="K19" t="n">
-        <v>-92.06999999999999</v>
+        <v>-89.48999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>143.11</v>
+        <v>139.1</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-142.58</v>
+        <v>-143.34</v>
       </c>
       <c r="K20" t="n">
-        <v>-72.68000000000001</v>
+        <v>-73.06999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>160.04</v>
+        <v>160.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-159.49</v>
+        <v>-159.68</v>
       </c>
       <c r="K21" t="n">
-        <v>147.03</v>
+        <v>147.21</v>
       </c>
       <c r="L21" t="n">
-        <v>216.92</v>
+        <v>217.18</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-63.3</v>
+        <v>-63.07</v>
       </c>
       <c r="K22" t="n">
-        <v>-72.29000000000001</v>
+        <v>-72.02</v>
       </c>
       <c r="L22" t="n">
-        <v>96.09</v>
+        <v>95.73</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-90.20999999999999</v>
+        <v>-91.81</v>
       </c>
       <c r="K23" t="n">
-        <v>287.73</v>
+        <v>292.81</v>
       </c>
       <c r="L23" t="n">
-        <v>301.54</v>
+        <v>306.87</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>186.77</v>
+        <v>191.1</v>
       </c>
       <c r="K24" t="n">
-        <v>-13.54</v>
+        <v>-13.85</v>
       </c>
       <c r="L24" t="n">
-        <v>187.26</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-244.45</v>
+        <v>-252.9</v>
       </c>
       <c r="K25" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="L25" t="n">
-        <v>244.47</v>
+        <v>252.92</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-109.02</v>
+        <v>-114.15</v>
       </c>
       <c r="K26" t="n">
-        <v>158.68</v>
+        <v>166.16</v>
       </c>
       <c r="L26" t="n">
-        <v>192.52</v>
+        <v>201.59</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>218.44</v>
+        <v>228.42</v>
       </c>
       <c r="K27" t="n">
-        <v>183.71</v>
+        <v>192.1</v>
       </c>
       <c r="L27" t="n">
-        <v>285.43</v>
+        <v>298.46</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>182.88</v>
+        <v>192.75</v>
       </c>
       <c r="K28" t="n">
-        <v>-163.24</v>
+        <v>-172.06</v>
       </c>
       <c r="L28" t="n">
-        <v>245.13</v>
+        <v>258.37</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>103.89</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>12.43</v>
+        <v>11.48</v>
       </c>
       <c r="L29" t="n">
-        <v>104.63</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>18.82</v>
+        <v>17.5</v>
       </c>
       <c r="K30" t="n">
-        <v>105.11</v>
+        <v>97.73</v>
       </c>
       <c r="L30" t="n">
-        <v>106.78</v>
+        <v>99.28</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>94.15000000000001</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>78.17</v>
+        <v>72.89</v>
       </c>
       <c r="L31" t="n">
-        <v>122.37</v>
+        <v>114.11</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-56.92</v>
+        <v>-53.02</v>
       </c>
       <c r="L32" t="n">
-        <v>56.94</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-20.41</v>
+        <v>-19.63</v>
       </c>
       <c r="K33" t="n">
-        <v>120.17</v>
+        <v>115.57</v>
       </c>
       <c r="L33" t="n">
-        <v>121.89</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>73.5</v>
+        <v>71.12</v>
       </c>
       <c r="K34" t="n">
-        <v>72.8</v>
+        <v>70.44</v>
       </c>
       <c r="L34" t="n">
-        <v>103.45</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-171.64</v>
+        <v>-170.66</v>
       </c>
       <c r="K35" t="n">
-        <v>-44.95</v>
+        <v>-44.69</v>
       </c>
       <c r="L35" t="n">
-        <v>177.43</v>
+        <v>176.41</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-158.37</v>
+        <v>-161.17</v>
       </c>
       <c r="K36" t="n">
-        <v>-144.24</v>
+        <v>-146.79</v>
       </c>
       <c r="L36" t="n">
-        <v>214.21</v>
+        <v>217.99</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-60.84</v>
+        <v>-61.43</v>
       </c>
       <c r="K37" t="n">
-        <v>169.38</v>
+        <v>171.02</v>
       </c>
       <c r="L37" t="n">
-        <v>179.98</v>
+        <v>181.72</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>218.16</v>
+        <v>223.52</v>
       </c>
       <c r="K38" t="n">
-        <v>-168.55</v>
+        <v>-172.7</v>
       </c>
       <c r="L38" t="n">
-        <v>275.68</v>
+        <v>282.47</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-248.67</v>
+        <v>-256.38</v>
       </c>
       <c r="K39" t="n">
-        <v>-23.56</v>
+        <v>-24.29</v>
       </c>
       <c r="L39" t="n">
-        <v>249.79</v>
+        <v>257.53</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>222.01</v>
+        <v>234.28</v>
       </c>
       <c r="K40" t="n">
-        <v>49.2</v>
+        <v>51.92</v>
       </c>
       <c r="L40" t="n">
-        <v>227.39</v>
+        <v>239.96</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>265.18</v>
+        <v>273.58</v>
       </c>
       <c r="K41" t="n">
-        <v>-139.52</v>
+        <v>-143.94</v>
       </c>
       <c r="L41" t="n">
-        <v>299.64</v>
+        <v>309.14</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-189.58</v>
+        <v>-197.58</v>
       </c>
       <c r="K42" t="n">
-        <v>-61.08</v>
+        <v>-63.66</v>
       </c>
       <c r="L42" t="n">
-        <v>199.17</v>
+        <v>207.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-297.36</v>
+        <v>-309.96</v>
       </c>
       <c r="K43" t="n">
-        <v>-31.61</v>
+        <v>-32.95</v>
       </c>
       <c r="L43" t="n">
-        <v>299.03</v>
+        <v>311.71</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>154.06</v>
+        <v>144.77</v>
       </c>
       <c r="K44" t="n">
-        <v>17.48</v>
+        <v>16.42</v>
       </c>
       <c r="L44" t="n">
-        <v>155.05</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>54.91</v>
+        <v>51.39</v>
       </c>
       <c r="K45" t="n">
-        <v>90.41</v>
+        <v>84.61</v>
       </c>
       <c r="L45" t="n">
-        <v>105.78</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>25.26</v>
+        <v>23.7</v>
       </c>
       <c r="K46" t="n">
-        <v>-101.07</v>
+        <v>-94.83</v>
       </c>
       <c r="L46" t="n">
-        <v>104.17</v>
+        <v>97.73999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-91.38</v>
+        <v>-89.22</v>
       </c>
       <c r="K47" t="n">
-        <v>-93.75</v>
+        <v>-91.53</v>
       </c>
       <c r="L47" t="n">
-        <v>130.91</v>
+        <v>127.82</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>62.72</v>
+        <v>60.72</v>
       </c>
       <c r="K48" t="n">
-        <v>68.51000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>92.88</v>
+        <v>89.92</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>28.11</v>
+        <v>27.69</v>
       </c>
       <c r="K49" t="n">
-        <v>157.15</v>
+        <v>154.76</v>
       </c>
       <c r="L49" t="n">
-        <v>159.65</v>
+        <v>157.22</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-123.51</v>
+        <v>-125.8</v>
       </c>
       <c r="K50" t="n">
-        <v>241.16</v>
+        <v>245.64</v>
       </c>
       <c r="L50" t="n">
-        <v>270.95</v>
+        <v>275.98</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>43.14</v>
+        <v>43.71</v>
       </c>
       <c r="K51" t="n">
-        <v>134.56</v>
+        <v>136.31</v>
       </c>
       <c r="L51" t="n">
-        <v>141.31</v>
+        <v>143.14</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>99.45</v>
+        <v>98.66</v>
       </c>
       <c r="K52" t="n">
-        <v>-122.58</v>
+        <v>-121.61</v>
       </c>
       <c r="L52" t="n">
-        <v>157.85</v>
+        <v>156.6</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>328.78</v>
+        <v>329.67</v>
       </c>
       <c r="K53" t="n">
-        <v>9.720000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="L53" t="n">
-        <v>328.92</v>
+        <v>329.82</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>298.57</v>
+        <v>304.58</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.49</v>
+        <v>-8.66</v>
       </c>
       <c r="L54" t="n">
-        <v>298.69</v>
+        <v>304.71</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>164.89</v>
+        <v>165.93</v>
       </c>
       <c r="K55" t="n">
-        <v>-51.62</v>
+        <v>-51.95</v>
       </c>
       <c r="L55" t="n">
-        <v>172.79</v>
+        <v>173.87</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>225.45</v>
+        <v>229.26</v>
       </c>
       <c r="K56" t="n">
-        <v>301.03</v>
+        <v>306.1</v>
       </c>
       <c r="L56" t="n">
-        <v>376.09</v>
+        <v>382.44</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>430.32</v>
+        <v>441.13</v>
       </c>
       <c r="K57" t="n">
-        <v>119.45</v>
+        <v>122.45</v>
       </c>
       <c r="L57" t="n">
-        <v>446.59</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-365.14</v>
+        <v>-372.28</v>
       </c>
       <c r="K58" t="n">
-        <v>-96.86</v>
+        <v>-98.76000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>377.77</v>
+        <v>385.15</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-78.02</v>
+        <v>-72.88</v>
       </c>
       <c r="K59" t="n">
-        <v>-30.5</v>
+        <v>-28.49</v>
       </c>
       <c r="L59" t="n">
-        <v>83.77</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-79.48999999999999</v>
+        <v>-73.44</v>
       </c>
       <c r="K60" t="n">
-        <v>22.38</v>
+        <v>20.68</v>
       </c>
       <c r="L60" t="n">
-        <v>82.58</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>46.16</v>
+        <v>42.1</v>
       </c>
       <c r="K61" t="n">
-        <v>76.01000000000001</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>88.92</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-120.97</v>
+        <v>-115.31</v>
       </c>
       <c r="K62" t="n">
-        <v>137.53</v>
+        <v>131.1</v>
       </c>
       <c r="L62" t="n">
-        <v>183.16</v>
+        <v>174.6</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>175.7</v>
+        <v>170.01</v>
       </c>
       <c r="K63" t="n">
-        <v>-83.06</v>
+        <v>-80.37</v>
       </c>
       <c r="L63" t="n">
-        <v>194.35</v>
+        <v>188.05</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>142.96</v>
+        <v>138.93</v>
       </c>
       <c r="K64" t="n">
-        <v>66.88</v>
+        <v>65</v>
       </c>
       <c r="L64" t="n">
-        <v>157.83</v>
+        <v>153.39</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-40.66</v>
+        <v>-41.02</v>
       </c>
       <c r="K65" t="n">
-        <v>135.26</v>
+        <v>136.43</v>
       </c>
       <c r="L65" t="n">
-        <v>141.24</v>
+        <v>142.46</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>23.88</v>
+        <v>23.91</v>
       </c>
       <c r="K66" t="n">
-        <v>129.77</v>
+        <v>129.91</v>
       </c>
       <c r="L66" t="n">
-        <v>131.95</v>
+        <v>132.09</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>160.58</v>
+        <v>159.99</v>
       </c>
       <c r="K67" t="n">
-        <v>8.92</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>160.83</v>
+        <v>160.24</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-118.2</v>
+        <v>-121.46</v>
       </c>
       <c r="K68" t="n">
-        <v>-195.6</v>
+        <v>-200.99</v>
       </c>
       <c r="L68" t="n">
-        <v>228.54</v>
+        <v>234.84</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>101.43</v>
+        <v>103.42</v>
       </c>
       <c r="K69" t="n">
-        <v>-146.09</v>
+        <v>-148.95</v>
       </c>
       <c r="L69" t="n">
-        <v>177.85</v>
+        <v>181.33</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>40.97</v>
+        <v>41.52</v>
       </c>
       <c r="K70" t="n">
-        <v>-170.72</v>
+        <v>-173.01</v>
       </c>
       <c r="L70" t="n">
-        <v>175.57</v>
+        <v>177.93</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-227.81</v>
+        <v>-233.7</v>
       </c>
       <c r="K71" t="n">
-        <v>-106.39</v>
+        <v>-109.15</v>
       </c>
       <c r="L71" t="n">
-        <v>251.43</v>
+        <v>257.93</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>202.27</v>
+        <v>210.22</v>
       </c>
       <c r="K72" t="n">
-        <v>180.47</v>
+        <v>187.57</v>
       </c>
       <c r="L72" t="n">
-        <v>271.08</v>
+        <v>281.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>66.59999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="K73" t="n">
-        <v>-389.77</v>
+        <v>-402.4</v>
       </c>
       <c r="L73" t="n">
-        <v>395.42</v>
+        <v>408.23</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>55.05</v>
+        <v>50.93</v>
       </c>
       <c r="K74" t="n">
-        <v>85.56</v>
+        <v>79.16</v>
       </c>
       <c r="L74" t="n">
-        <v>101.74</v>
+        <v>94.13</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>39.64</v>
+        <v>36.58</v>
       </c>
       <c r="K75" t="n">
-        <v>88.37</v>
+        <v>81.55</v>
       </c>
       <c r="L75" t="n">
-        <v>96.84999999999999</v>
+        <v>89.38</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-95.94</v>
+        <v>-90.44</v>
       </c>
       <c r="K76" t="n">
-        <v>-132.25</v>
+        <v>-124.66</v>
       </c>
       <c r="L76" t="n">
-        <v>163.39</v>
+        <v>154.01</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-179.17</v>
+        <v>-173.01</v>
       </c>
       <c r="K77" t="n">
-        <v>-120.59</v>
+        <v>-116.45</v>
       </c>
       <c r="L77" t="n">
-        <v>215.97</v>
+        <v>208.55</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-71.47</v>
+        <v>-69.56999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>155.86</v>
+        <v>151.71</v>
       </c>
       <c r="L78" t="n">
-        <v>171.47</v>
+        <v>166.9</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-51.79</v>
+        <v>-49.74</v>
       </c>
       <c r="K79" t="n">
-        <v>-104.34</v>
+        <v>-100.2</v>
       </c>
       <c r="L79" t="n">
-        <v>116.48</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>248.6</v>
+        <v>247.13</v>
       </c>
       <c r="K80" t="n">
-        <v>86.29000000000001</v>
+        <v>85.78</v>
       </c>
       <c r="L80" t="n">
-        <v>263.15</v>
+        <v>261.6</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-286.28</v>
+        <v>-285.61</v>
       </c>
       <c r="K81" t="n">
-        <v>-137.6</v>
+        <v>-137.28</v>
       </c>
       <c r="L81" t="n">
-        <v>317.63</v>
+        <v>316.89</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>232.35</v>
+        <v>231.49</v>
       </c>
       <c r="K82" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="L82" t="n">
-        <v>232.4</v>
+        <v>231.54</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>249.23</v>
+        <v>258.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="L83" t="n">
-        <v>249.23</v>
+        <v>258.86</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-38.13</v>
+        <v>-38.3</v>
       </c>
       <c r="K84" t="n">
-        <v>-333.76</v>
+        <v>-335.21</v>
       </c>
       <c r="L84" t="n">
-        <v>335.93</v>
+        <v>337.39</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>157.89</v>
+        <v>159.99</v>
       </c>
       <c r="K85" t="n">
-        <v>-154.87</v>
+        <v>-156.93</v>
       </c>
       <c r="L85" t="n">
-        <v>221.16</v>
+        <v>224.11</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>44.51</v>
+        <v>45.95</v>
       </c>
       <c r="K86" t="n">
-        <v>634.86</v>
+        <v>655.49</v>
       </c>
       <c r="L86" t="n">
-        <v>636.42</v>
+        <v>657.1</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>330.68</v>
+        <v>339.22</v>
       </c>
       <c r="K87" t="n">
-        <v>222.8</v>
+        <v>228.56</v>
       </c>
       <c r="L87" t="n">
-        <v>398.74</v>
+        <v>409.03</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.38</v>
+        <v>-5.5</v>
       </c>
       <c r="K88" t="n">
-        <v>-386.77</v>
+        <v>-395.29</v>
       </c>
       <c r="L88" t="n">
-        <v>386.81</v>
+        <v>395.33</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-48.73</v>
+        <v>-32.84</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.76</v>
+        <v>-7.92</v>
       </c>
       <c r="L14" t="n">
-        <v>50.12</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-21.18</v>
+        <v>-13.47</v>
       </c>
       <c r="K15" t="n">
-        <v>-75.26000000000001</v>
+        <v>-47.88</v>
       </c>
       <c r="L15" t="n">
-        <v>78.19</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-93.61</v>
+        <v>-55.53</v>
       </c>
       <c r="K16" t="n">
-        <v>25.82</v>
+        <v>15.32</v>
       </c>
       <c r="L16" t="n">
-        <v>97.11</v>
+        <v>57.61</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-88.59</v>
+        <v>-58.85</v>
       </c>
       <c r="K17" t="n">
-        <v>-89.05</v>
+        <v>-59.15</v>
       </c>
       <c r="L17" t="n">
-        <v>125.61</v>
+        <v>83.43000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>37.26</v>
+        <v>21.18</v>
       </c>
       <c r="K18" t="n">
-        <v>89.7</v>
+        <v>50.99</v>
       </c>
       <c r="L18" t="n">
-        <v>97.13</v>
+        <v>55.21</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-106.49</v>
+        <v>-61.83</v>
       </c>
       <c r="K19" t="n">
-        <v>-89.48999999999999</v>
+        <v>-51.96</v>
       </c>
       <c r="L19" t="n">
-        <v>139.1</v>
+        <v>80.77</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-143.34</v>
+        <v>-78.42</v>
       </c>
       <c r="K20" t="n">
-        <v>-73.06999999999999</v>
+        <v>-39.98</v>
       </c>
       <c r="L20" t="n">
-        <v>160.89</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-159.68</v>
+        <v>-89.72</v>
       </c>
       <c r="K21" t="n">
-        <v>147.21</v>
+        <v>82.72</v>
       </c>
       <c r="L21" t="n">
-        <v>217.18</v>
+        <v>122.03</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-63.07</v>
+        <v>-18.02</v>
       </c>
       <c r="K22" t="n">
-        <v>-72.02</v>
+        <v>-20.58</v>
       </c>
       <c r="L22" t="n">
-        <v>95.73</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-91.81</v>
+        <v>-57.86</v>
       </c>
       <c r="K23" t="n">
-        <v>292.81</v>
+        <v>184.55</v>
       </c>
       <c r="L23" t="n">
-        <v>306.87</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>191.1</v>
+        <v>112.55</v>
       </c>
       <c r="K24" t="n">
-        <v>-13.85</v>
+        <v>-8.16</v>
       </c>
       <c r="L24" t="n">
-        <v>191.6</v>
+        <v>112.84</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-252.9</v>
+        <v>-159.39</v>
       </c>
       <c r="K25" t="n">
-        <v>3.28</v>
+        <v>2.07</v>
       </c>
       <c r="L25" t="n">
-        <v>252.92</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-114.15</v>
+        <v>-78.23999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>166.16</v>
+        <v>113.89</v>
       </c>
       <c r="L26" t="n">
-        <v>201.59</v>
+        <v>138.17</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>228.42</v>
+        <v>163.35</v>
       </c>
       <c r="K27" t="n">
-        <v>192.1</v>
+        <v>137.38</v>
       </c>
       <c r="L27" t="n">
-        <v>298.46</v>
+        <v>213.43</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>192.75</v>
+        <v>120.6</v>
       </c>
       <c r="K28" t="n">
-        <v>-172.06</v>
+        <v>-107.65</v>
       </c>
       <c r="L28" t="n">
-        <v>258.37</v>
+        <v>161.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>96.01000000000001</v>
+        <v>54.13</v>
       </c>
       <c r="K29" t="n">
-        <v>11.48</v>
+        <v>6.47</v>
       </c>
       <c r="L29" t="n">
-        <v>96.7</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>17.5</v>
+        <v>12.15</v>
       </c>
       <c r="K30" t="n">
-        <v>97.73</v>
+        <v>67.87</v>
       </c>
       <c r="L30" t="n">
-        <v>99.28</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>87.79000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="K31" t="n">
-        <v>72.89</v>
+        <v>44.92</v>
       </c>
       <c r="L31" t="n">
-        <v>114.11</v>
+        <v>70.31999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="K32" t="n">
-        <v>-53.02</v>
+        <v>-39.76</v>
       </c>
       <c r="L32" t="n">
-        <v>53.04</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-19.63</v>
+        <v>-10.93</v>
       </c>
       <c r="K33" t="n">
-        <v>115.57</v>
+        <v>64.38</v>
       </c>
       <c r="L33" t="n">
-        <v>117.23</v>
+        <v>65.31</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>71.12</v>
+        <v>45.59</v>
       </c>
       <c r="K34" t="n">
-        <v>70.44</v>
+        <v>45.15</v>
       </c>
       <c r="L34" t="n">
-        <v>100.1</v>
+        <v>64.17</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-170.66</v>
+        <v>-103.17</v>
       </c>
       <c r="K35" t="n">
-        <v>-44.69</v>
+        <v>-27.02</v>
       </c>
       <c r="L35" t="n">
-        <v>176.41</v>
+        <v>106.64</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-161.17</v>
+        <v>-86.68000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-146.79</v>
+        <v>-78.95</v>
       </c>
       <c r="L36" t="n">
-        <v>217.99</v>
+        <v>117.25</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-61.43</v>
+        <v>-37.63</v>
       </c>
       <c r="K37" t="n">
-        <v>171.02</v>
+        <v>104.76</v>
       </c>
       <c r="L37" t="n">
-        <v>181.72</v>
+        <v>111.31</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>223.52</v>
+        <v>141.12</v>
       </c>
       <c r="K38" t="n">
-        <v>-172.7</v>
+        <v>-109.03</v>
       </c>
       <c r="L38" t="n">
-        <v>282.47</v>
+        <v>178.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-256.38</v>
+        <v>-175.56</v>
       </c>
       <c r="K39" t="n">
-        <v>-24.29</v>
+        <v>-16.63</v>
       </c>
       <c r="L39" t="n">
-        <v>257.53</v>
+        <v>176.35</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>234.28</v>
+        <v>166.91</v>
       </c>
       <c r="K40" t="n">
-        <v>51.92</v>
+        <v>36.99</v>
       </c>
       <c r="L40" t="n">
-        <v>239.96</v>
+        <v>170.95</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>273.58</v>
+        <v>160.42</v>
       </c>
       <c r="K41" t="n">
-        <v>-143.94</v>
+        <v>-84.40000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>309.14</v>
+        <v>181.27</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-197.58</v>
+        <v>-134.84</v>
       </c>
       <c r="K42" t="n">
-        <v>-63.66</v>
+        <v>-43.45</v>
       </c>
       <c r="L42" t="n">
-        <v>207.59</v>
+        <v>141.67</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-309.96</v>
+        <v>-203.7</v>
       </c>
       <c r="K43" t="n">
-        <v>-32.95</v>
+        <v>-21.65</v>
       </c>
       <c r="L43" t="n">
-        <v>311.71</v>
+        <v>204.85</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>144.77</v>
+        <v>86.7</v>
       </c>
       <c r="K44" t="n">
-        <v>16.42</v>
+        <v>9.84</v>
       </c>
       <c r="L44" t="n">
-        <v>145.7</v>
+        <v>87.26000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>51.39</v>
+        <v>31.54</v>
       </c>
       <c r="K45" t="n">
-        <v>84.61</v>
+        <v>51.92</v>
       </c>
       <c r="L45" t="n">
-        <v>99</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>23.7</v>
+        <v>13.07</v>
       </c>
       <c r="K46" t="n">
-        <v>-94.83</v>
+        <v>-52.29</v>
       </c>
       <c r="L46" t="n">
-        <v>97.73999999999999</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-89.22</v>
+        <v>-49.88</v>
       </c>
       <c r="K47" t="n">
-        <v>-91.53</v>
+        <v>-51.18</v>
       </c>
       <c r="L47" t="n">
-        <v>127.82</v>
+        <v>71.45999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>60.72</v>
+        <v>34.07</v>
       </c>
       <c r="K48" t="n">
-        <v>66.31999999999999</v>
+        <v>37.22</v>
       </c>
       <c r="L48" t="n">
-        <v>89.92</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>27.69</v>
+        <v>15.42</v>
       </c>
       <c r="K49" t="n">
-        <v>154.76</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>157.22</v>
+        <v>87.58</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-125.8</v>
+        <v>-68.83</v>
       </c>
       <c r="K50" t="n">
-        <v>245.64</v>
+        <v>134.39</v>
       </c>
       <c r="L50" t="n">
-        <v>275.98</v>
+        <v>150.99</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>43.71</v>
+        <v>23.08</v>
       </c>
       <c r="K51" t="n">
-        <v>136.31</v>
+        <v>71.97</v>
       </c>
       <c r="L51" t="n">
-        <v>143.14</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>98.66</v>
+        <v>59.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-121.61</v>
+        <v>-73.70999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>156.6</v>
+        <v>94.91</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>329.67</v>
+        <v>197.53</v>
       </c>
       <c r="K53" t="n">
-        <v>9.75</v>
+        <v>5.84</v>
       </c>
       <c r="L53" t="n">
-        <v>329.82</v>
+        <v>197.62</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>304.58</v>
+        <v>176.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.66</v>
+        <v>-5.01</v>
       </c>
       <c r="L54" t="n">
-        <v>304.71</v>
+        <v>176.3</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>165.93</v>
+        <v>96.91</v>
       </c>
       <c r="K55" t="n">
-        <v>-51.95</v>
+        <v>-30.34</v>
       </c>
       <c r="L55" t="n">
-        <v>173.87</v>
+        <v>101.55</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>229.26</v>
+        <v>129.31</v>
       </c>
       <c r="K56" t="n">
-        <v>306.1</v>
+        <v>172.65</v>
       </c>
       <c r="L56" t="n">
-        <v>382.44</v>
+        <v>215.7</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>441.13</v>
+        <v>250.97</v>
       </c>
       <c r="K57" t="n">
-        <v>122.45</v>
+        <v>69.66</v>
       </c>
       <c r="L57" t="n">
-        <v>457.81</v>
+        <v>260.46</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-372.28</v>
+        <v>-207.71</v>
       </c>
       <c r="K58" t="n">
-        <v>-98.76000000000001</v>
+        <v>-55.1</v>
       </c>
       <c r="L58" t="n">
-        <v>385.15</v>
+        <v>214.9</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-72.88</v>
+        <v>-44.91</v>
       </c>
       <c r="K59" t="n">
-        <v>-28.49</v>
+        <v>-17.56</v>
       </c>
       <c r="L59" t="n">
-        <v>78.25</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-73.44</v>
+        <v>-41.66</v>
       </c>
       <c r="K60" t="n">
-        <v>20.68</v>
+        <v>11.73</v>
       </c>
       <c r="L60" t="n">
-        <v>76.3</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>42.1</v>
+        <v>23.62</v>
       </c>
       <c r="K61" t="n">
-        <v>69.31999999999999</v>
+        <v>38.9</v>
       </c>
       <c r="L61" t="n">
-        <v>81.09999999999999</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-115.31</v>
+        <v>-69.19</v>
       </c>
       <c r="K62" t="n">
-        <v>131.1</v>
+        <v>78.66</v>
       </c>
       <c r="L62" t="n">
-        <v>174.6</v>
+        <v>104.76</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>170.01</v>
+        <v>92.58</v>
       </c>
       <c r="K63" t="n">
-        <v>-80.37</v>
+        <v>-43.76</v>
       </c>
       <c r="L63" t="n">
-        <v>188.05</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>138.93</v>
+        <v>80.83</v>
       </c>
       <c r="K64" t="n">
-        <v>65</v>
+        <v>37.82</v>
       </c>
       <c r="L64" t="n">
-        <v>153.39</v>
+        <v>89.23999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-41.02</v>
+        <v>-23.05</v>
       </c>
       <c r="K65" t="n">
-        <v>136.43</v>
+        <v>76.66</v>
       </c>
       <c r="L65" t="n">
-        <v>142.46</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>23.91</v>
+        <v>13.25</v>
       </c>
       <c r="K66" t="n">
-        <v>129.91</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>132.09</v>
+        <v>73.22</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>159.99</v>
+        <v>93.36</v>
       </c>
       <c r="K67" t="n">
-        <v>8.880000000000001</v>
+        <v>5.18</v>
       </c>
       <c r="L67" t="n">
-        <v>160.24</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-121.46</v>
+        <v>-78.88</v>
       </c>
       <c r="K68" t="n">
-        <v>-200.99</v>
+        <v>-130.53</v>
       </c>
       <c r="L68" t="n">
-        <v>234.84</v>
+        <v>152.51</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>103.42</v>
+        <v>60.91</v>
       </c>
       <c r="K69" t="n">
-        <v>-148.95</v>
+        <v>-87.72</v>
       </c>
       <c r="L69" t="n">
-        <v>181.33</v>
+        <v>106.79</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>41.52</v>
+        <v>25.14</v>
       </c>
       <c r="K70" t="n">
-        <v>-173.01</v>
+        <v>-104.76</v>
       </c>
       <c r="L70" t="n">
-        <v>177.93</v>
+        <v>107.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-233.7</v>
+        <v>-133.84</v>
       </c>
       <c r="K71" t="n">
-        <v>-109.15</v>
+        <v>-62.51</v>
       </c>
       <c r="L71" t="n">
-        <v>257.93</v>
+        <v>147.72</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>210.22</v>
+        <v>124.34</v>
       </c>
       <c r="K72" t="n">
-        <v>187.57</v>
+        <v>110.94</v>
       </c>
       <c r="L72" t="n">
-        <v>281.74</v>
+        <v>166.63</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>68.75</v>
+        <v>42.54</v>
       </c>
       <c r="K73" t="n">
-        <v>-402.4</v>
+        <v>-248.95</v>
       </c>
       <c r="L73" t="n">
-        <v>408.23</v>
+        <v>252.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>50.93</v>
+        <v>29.42</v>
       </c>
       <c r="K74" t="n">
-        <v>79.16</v>
+        <v>45.72</v>
       </c>
       <c r="L74" t="n">
-        <v>94.13</v>
+        <v>54.37</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>36.58</v>
+        <v>22.54</v>
       </c>
       <c r="K75" t="n">
-        <v>81.55</v>
+        <v>50.26</v>
       </c>
       <c r="L75" t="n">
-        <v>89.38</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-90.44</v>
+        <v>-49.66</v>
       </c>
       <c r="K76" t="n">
-        <v>-124.66</v>
+        <v>-68.45999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>154.01</v>
+        <v>84.58</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-173.01</v>
+        <v>-100.06</v>
       </c>
       <c r="K77" t="n">
-        <v>-116.45</v>
+        <v>-67.34999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>208.55</v>
+        <v>120.62</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-69.56999999999999</v>
+        <v>-40.08</v>
       </c>
       <c r="K78" t="n">
-        <v>151.71</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>166.9</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-49.74</v>
+        <v>-25.67</v>
       </c>
       <c r="K79" t="n">
-        <v>-100.2</v>
+        <v>-51.72</v>
       </c>
       <c r="L79" t="n">
-        <v>111.86</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>247.13</v>
+        <v>144.21</v>
       </c>
       <c r="K80" t="n">
-        <v>85.78</v>
+        <v>50.06</v>
       </c>
       <c r="L80" t="n">
-        <v>261.6</v>
+        <v>152.65</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-285.61</v>
+        <v>-144.21</v>
       </c>
       <c r="K81" t="n">
-        <v>-137.28</v>
+        <v>-69.31</v>
       </c>
       <c r="L81" t="n">
-        <v>316.89</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>231.49</v>
+        <v>122.47</v>
       </c>
       <c r="K82" t="n">
-        <v>4.77</v>
+        <v>2.52</v>
       </c>
       <c r="L82" t="n">
-        <v>231.54</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>258.86</v>
+        <v>156.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.76</v>
+        <v>-0.46</v>
       </c>
       <c r="L83" t="n">
-        <v>258.86</v>
+        <v>156.98</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-38.3</v>
+        <v>-21.26</v>
       </c>
       <c r="K84" t="n">
-        <v>-335.21</v>
+        <v>-186.1</v>
       </c>
       <c r="L84" t="n">
-        <v>337.39</v>
+        <v>187.31</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>159.99</v>
+        <v>93.19</v>
       </c>
       <c r="K85" t="n">
-        <v>-156.93</v>
+        <v>-91.41</v>
       </c>
       <c r="L85" t="n">
-        <v>224.11</v>
+        <v>130.54</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>45.95</v>
+        <v>24.79</v>
       </c>
       <c r="K86" t="n">
-        <v>655.49</v>
+        <v>353.66</v>
       </c>
       <c r="L86" t="n">
-        <v>657.1</v>
+        <v>354.53</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>339.22</v>
+        <v>208.7</v>
       </c>
       <c r="K87" t="n">
-        <v>228.56</v>
+        <v>140.62</v>
       </c>
       <c r="L87" t="n">
-        <v>409.03</v>
+        <v>251.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.5</v>
+        <v>-3.37</v>
       </c>
       <c r="K88" t="n">
-        <v>-395.29</v>
+        <v>-242.3</v>
       </c>
       <c r="L88" t="n">
-        <v>395.33</v>
+        <v>242.33</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-32.84</v>
+        <v>-34.48</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.92</v>
+        <v>-8.32</v>
       </c>
       <c r="L14" t="n">
-        <v>33.78</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.47</v>
+        <v>-13.65</v>
       </c>
       <c r="K15" t="n">
-        <v>-47.88</v>
+        <v>-48.5</v>
       </c>
       <c r="L15" t="n">
-        <v>49.74</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.53</v>
+        <v>-55.41</v>
       </c>
       <c r="K16" t="n">
-        <v>15.32</v>
+        <v>15.28</v>
       </c>
       <c r="L16" t="n">
-        <v>57.61</v>
+        <v>57.48</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-58.85</v>
+        <v>-57.21</v>
       </c>
       <c r="K17" t="n">
-        <v>-59.15</v>
+        <v>-57.5</v>
       </c>
       <c r="L17" t="n">
-        <v>83.43000000000001</v>
+        <v>81.11</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>21.18</v>
+        <v>22.23</v>
       </c>
       <c r="K18" t="n">
-        <v>50.99</v>
+        <v>53.52</v>
       </c>
       <c r="L18" t="n">
-        <v>55.21</v>
+        <v>57.95</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-61.83</v>
+        <v>-61.43</v>
       </c>
       <c r="K19" t="n">
-        <v>-51.96</v>
+        <v>-51.62</v>
       </c>
       <c r="L19" t="n">
-        <v>80.77</v>
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-78.42</v>
+        <v>-80.63</v>
       </c>
       <c r="K20" t="n">
-        <v>-39.98</v>
+        <v>-41.1</v>
       </c>
       <c r="L20" t="n">
-        <v>88.03</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-89.72</v>
+        <v>-88.05</v>
       </c>
       <c r="K21" t="n">
-        <v>82.72</v>
+        <v>81.17</v>
       </c>
       <c r="L21" t="n">
-        <v>122.03</v>
+        <v>119.75</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-18.02</v>
+        <v>-17.64</v>
       </c>
       <c r="K22" t="n">
-        <v>-20.58</v>
+        <v>-20.15</v>
       </c>
       <c r="L22" t="n">
-        <v>27.35</v>
+        <v>26.78</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-57.86</v>
+        <v>-55.74</v>
       </c>
       <c r="K23" t="n">
-        <v>184.55</v>
+        <v>177.8</v>
       </c>
       <c r="L23" t="n">
-        <v>193.41</v>
+        <v>186.33</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>112.55</v>
+        <v>116.48</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.16</v>
+        <v>-8.44</v>
       </c>
       <c r="L24" t="n">
-        <v>112.84</v>
+        <v>116.79</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-159.39</v>
+        <v>-157.77</v>
       </c>
       <c r="K25" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="L25" t="n">
-        <v>159.4</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-78.23999999999999</v>
+        <v>-82.06999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>113.89</v>
+        <v>119.46</v>
       </c>
       <c r="L26" t="n">
-        <v>138.17</v>
+        <v>144.94</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>163.35</v>
+        <v>160.64</v>
       </c>
       <c r="K27" t="n">
-        <v>137.38</v>
+        <v>135.1</v>
       </c>
       <c r="L27" t="n">
-        <v>213.43</v>
+        <v>209.9</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>120.6</v>
+        <v>124.27</v>
       </c>
       <c r="K28" t="n">
-        <v>-107.65</v>
+        <v>-110.93</v>
       </c>
       <c r="L28" t="n">
-        <v>161.66</v>
+        <v>166.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>54.13</v>
+        <v>54.84</v>
       </c>
       <c r="K29" t="n">
-        <v>6.47</v>
+        <v>6.56</v>
       </c>
       <c r="L29" t="n">
-        <v>54.51</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>12.15</v>
+        <v>11.71</v>
       </c>
       <c r="K30" t="n">
-        <v>67.87</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>68.95</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>54.1</v>
+        <v>52.62</v>
       </c>
       <c r="K31" t="n">
-        <v>44.92</v>
+        <v>43.69</v>
       </c>
       <c r="L31" t="n">
-        <v>70.31999999999999</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="K32" t="n">
-        <v>-39.76</v>
+        <v>-42.12</v>
       </c>
       <c r="L32" t="n">
-        <v>39.78</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-10.93</v>
+        <v>-11.03</v>
       </c>
       <c r="K33" t="n">
-        <v>64.38</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>65.31</v>
+        <v>65.89</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>45.59</v>
+        <v>46.13</v>
       </c>
       <c r="K34" t="n">
-        <v>45.15</v>
+        <v>45.69</v>
       </c>
       <c r="L34" t="n">
-        <v>64.17</v>
+        <v>64.93000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-103.17</v>
+        <v>-101.84</v>
       </c>
       <c r="K35" t="n">
-        <v>-27.02</v>
+        <v>-26.67</v>
       </c>
       <c r="L35" t="n">
-        <v>106.64</v>
+        <v>105.27</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-86.68000000000001</v>
+        <v>-85.93000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-78.95</v>
+        <v>-78.26000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>117.25</v>
+        <v>116.23</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-37.63</v>
+        <v>-37.25</v>
       </c>
       <c r="K37" t="n">
-        <v>104.76</v>
+        <v>103.7</v>
       </c>
       <c r="L37" t="n">
-        <v>111.31</v>
+        <v>110.19</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>141.12</v>
+        <v>136.88</v>
       </c>
       <c r="K38" t="n">
-        <v>-109.03</v>
+        <v>-105.76</v>
       </c>
       <c r="L38" t="n">
-        <v>178.33</v>
+        <v>172.97</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-175.56</v>
+        <v>-169.32</v>
       </c>
       <c r="K39" t="n">
-        <v>-16.63</v>
+        <v>-16.04</v>
       </c>
       <c r="L39" t="n">
-        <v>176.35</v>
+        <v>170.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>166.91</v>
+        <v>161.91</v>
       </c>
       <c r="K40" t="n">
-        <v>36.99</v>
+        <v>35.88</v>
       </c>
       <c r="L40" t="n">
-        <v>170.95</v>
+        <v>165.84</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>160.42</v>
+        <v>161.57</v>
       </c>
       <c r="K41" t="n">
-        <v>-84.40000000000001</v>
+        <v>-85.01000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>181.27</v>
+        <v>182.57</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-134.84</v>
+        <v>-139.88</v>
       </c>
       <c r="K42" t="n">
-        <v>-43.45</v>
+        <v>-45.07</v>
       </c>
       <c r="L42" t="n">
-        <v>141.67</v>
+        <v>146.96</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-203.7</v>
+        <v>-201.59</v>
       </c>
       <c r="K43" t="n">
-        <v>-21.65</v>
+        <v>-21.43</v>
       </c>
       <c r="L43" t="n">
-        <v>204.85</v>
+        <v>202.72</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>86.7</v>
+        <v>83.66</v>
       </c>
       <c r="K44" t="n">
-        <v>9.84</v>
+        <v>9.49</v>
       </c>
       <c r="L44" t="n">
-        <v>87.26000000000001</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>31.54</v>
+        <v>31.5</v>
       </c>
       <c r="K45" t="n">
-        <v>51.92</v>
+        <v>51.86</v>
       </c>
       <c r="L45" t="n">
-        <v>60.75</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>13.07</v>
+        <v>13.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-52.29</v>
+        <v>-54.36</v>
       </c>
       <c r="L46" t="n">
-        <v>53.9</v>
+        <v>56.03</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-49.88</v>
+        <v>-50.7</v>
       </c>
       <c r="K47" t="n">
-        <v>-51.18</v>
+        <v>-52.01</v>
       </c>
       <c r="L47" t="n">
-        <v>71.45999999999999</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>34.07</v>
+        <v>36.25</v>
       </c>
       <c r="K48" t="n">
-        <v>37.22</v>
+        <v>39.6</v>
       </c>
       <c r="L48" t="n">
-        <v>50.46</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>15.42</v>
+        <v>15.32</v>
       </c>
       <c r="K49" t="n">
-        <v>86.20999999999999</v>
+        <v>85.66</v>
       </c>
       <c r="L49" t="n">
-        <v>87.58</v>
+        <v>87.02</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-68.83</v>
+        <v>-66.79000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>134.39</v>
+        <v>130.42</v>
       </c>
       <c r="L50" t="n">
-        <v>150.99</v>
+        <v>146.53</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>23.08</v>
+        <v>24.41</v>
       </c>
       <c r="K51" t="n">
-        <v>71.97</v>
+        <v>76.13</v>
       </c>
       <c r="L51" t="n">
-        <v>75.58</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>59.8</v>
+        <v>60.26</v>
       </c>
       <c r="K52" t="n">
-        <v>-73.70999999999999</v>
+        <v>-74.28</v>
       </c>
       <c r="L52" t="n">
-        <v>94.91</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>197.53</v>
+        <v>190.64</v>
       </c>
       <c r="K53" t="n">
-        <v>5.84</v>
+        <v>5.64</v>
       </c>
       <c r="L53" t="n">
-        <v>197.62</v>
+        <v>190.72</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>176.22</v>
+        <v>174.12</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.01</v>
+        <v>-4.95</v>
       </c>
       <c r="L54" t="n">
-        <v>176.3</v>
+        <v>174.19</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>96.91</v>
+        <v>102.41</v>
       </c>
       <c r="K55" t="n">
-        <v>-30.34</v>
+        <v>-32.06</v>
       </c>
       <c r="L55" t="n">
-        <v>101.55</v>
+        <v>107.32</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>129.31</v>
+        <v>128.63</v>
       </c>
       <c r="K56" t="n">
-        <v>172.65</v>
+        <v>171.75</v>
       </c>
       <c r="L56" t="n">
-        <v>215.7</v>
+        <v>214.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>250.97</v>
+        <v>244.04</v>
       </c>
       <c r="K57" t="n">
-        <v>69.66</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>260.46</v>
+        <v>253.27</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-207.71</v>
+        <v>-209.68</v>
       </c>
       <c r="K58" t="n">
-        <v>-55.1</v>
+        <v>-55.63</v>
       </c>
       <c r="L58" t="n">
-        <v>214.9</v>
+        <v>216.94</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-44.91</v>
+        <v>-46.01</v>
       </c>
       <c r="K59" t="n">
-        <v>-17.56</v>
+        <v>-17.99</v>
       </c>
       <c r="L59" t="n">
-        <v>48.22</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-41.66</v>
+        <v>-43.69</v>
       </c>
       <c r="K60" t="n">
-        <v>11.73</v>
+        <v>12.3</v>
       </c>
       <c r="L60" t="n">
-        <v>43.28</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>23.62</v>
+        <v>24.53</v>
       </c>
       <c r="K61" t="n">
-        <v>38.9</v>
+        <v>40.39</v>
       </c>
       <c r="L61" t="n">
-        <v>45.51</v>
+        <v>47.26</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-69.19</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>78.66</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>104.76</v>
+        <v>100.41</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>92.58</v>
+        <v>89.73</v>
       </c>
       <c r="K63" t="n">
-        <v>-43.76</v>
+        <v>-42.42</v>
       </c>
       <c r="L63" t="n">
-        <v>102.4</v>
+        <v>99.25</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>80.83</v>
+        <v>79.27</v>
       </c>
       <c r="K64" t="n">
-        <v>37.82</v>
+        <v>37.08</v>
       </c>
       <c r="L64" t="n">
-        <v>89.23999999999999</v>
+        <v>87.51000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-23.05</v>
+        <v>-23.95</v>
       </c>
       <c r="K65" t="n">
-        <v>76.66</v>
+        <v>79.66</v>
       </c>
       <c r="L65" t="n">
-        <v>80.05</v>
+        <v>83.18000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>13.25</v>
+        <v>13.9</v>
       </c>
       <c r="K66" t="n">
-        <v>72.01000000000001</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>73.22</v>
+        <v>76.81</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>93.36</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>5.18</v>
+        <v>5.24</v>
       </c>
       <c r="L67" t="n">
-        <v>93.5</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-78.88</v>
+        <v>-77.88</v>
       </c>
       <c r="K68" t="n">
-        <v>-130.53</v>
+        <v>-128.87</v>
       </c>
       <c r="L68" t="n">
-        <v>152.51</v>
+        <v>150.57</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>60.91</v>
+        <v>63.68</v>
       </c>
       <c r="K69" t="n">
-        <v>-87.72</v>
+        <v>-91.70999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>106.79</v>
+        <v>111.65</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>25.14</v>
+        <v>26.09</v>
       </c>
       <c r="K70" t="n">
-        <v>-104.76</v>
+        <v>-108.72</v>
       </c>
       <c r="L70" t="n">
-        <v>107.73</v>
+        <v>111.81</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-133.84</v>
+        <v>-138.78</v>
       </c>
       <c r="K71" t="n">
-        <v>-62.51</v>
+        <v>-64.81</v>
       </c>
       <c r="L71" t="n">
-        <v>147.72</v>
+        <v>153.17</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>124.34</v>
+        <v>127.44</v>
       </c>
       <c r="K72" t="n">
-        <v>110.94</v>
+        <v>113.7</v>
       </c>
       <c r="L72" t="n">
-        <v>166.63</v>
+        <v>170.79</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>42.54</v>
+        <v>41.3</v>
       </c>
       <c r="K73" t="n">
-        <v>-248.95</v>
+        <v>-241.69</v>
       </c>
       <c r="L73" t="n">
-        <v>252.56</v>
+        <v>245.19</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>29.42</v>
+        <v>29.6</v>
       </c>
       <c r="K74" t="n">
-        <v>45.72</v>
+        <v>46.01</v>
       </c>
       <c r="L74" t="n">
-        <v>54.37</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>22.54</v>
+        <v>22.48</v>
       </c>
       <c r="K75" t="n">
-        <v>50.26</v>
+        <v>50.12</v>
       </c>
       <c r="L75" t="n">
-        <v>55.08</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-49.66</v>
+        <v>-48.38</v>
       </c>
       <c r="K76" t="n">
-        <v>-68.45999999999999</v>
+        <v>-66.69</v>
       </c>
       <c r="L76" t="n">
-        <v>84.58</v>
+        <v>82.39</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-100.06</v>
+        <v>-95.08</v>
       </c>
       <c r="K77" t="n">
-        <v>-67.34999999999999</v>
+        <v>-63.99</v>
       </c>
       <c r="L77" t="n">
-        <v>120.62</v>
+        <v>114.61</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-40.08</v>
+        <v>-39.03</v>
       </c>
       <c r="K78" t="n">
-        <v>87.40000000000001</v>
+        <v>85.11</v>
       </c>
       <c r="L78" t="n">
-        <v>96.15000000000001</v>
+        <v>93.63</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-25.67</v>
+        <v>-26.44</v>
       </c>
       <c r="K79" t="n">
-        <v>-51.72</v>
+        <v>-53.26</v>
       </c>
       <c r="L79" t="n">
-        <v>57.74</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>144.21</v>
+        <v>137.69</v>
       </c>
       <c r="K80" t="n">
-        <v>50.06</v>
+        <v>47.79</v>
       </c>
       <c r="L80" t="n">
-        <v>152.65</v>
+        <v>145.75</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-144.21</v>
+        <v>-138.15</v>
       </c>
       <c r="K81" t="n">
-        <v>-69.31</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>160</v>
+        <v>153.28</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>122.47</v>
+        <v>120.21</v>
       </c>
       <c r="K82" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="L82" t="n">
-        <v>122.5</v>
+        <v>120.24</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>156.98</v>
+        <v>156.17</v>
       </c>
       <c r="K83" t="n">
         <v>-0.46</v>
       </c>
       <c r="L83" t="n">
-        <v>156.98</v>
+        <v>156.17</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-21.26</v>
+        <v>-20.66</v>
       </c>
       <c r="K84" t="n">
-        <v>-186.1</v>
+        <v>-180.86</v>
       </c>
       <c r="L84" t="n">
-        <v>187.31</v>
+        <v>182.04</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>93.19</v>
+        <v>94.28</v>
       </c>
       <c r="K85" t="n">
-        <v>-91.41</v>
+        <v>-92.48</v>
       </c>
       <c r="L85" t="n">
-        <v>130.54</v>
+        <v>132.07</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>24.79</v>
+        <v>24.8</v>
       </c>
       <c r="K86" t="n">
-        <v>353.66</v>
+        <v>353.7</v>
       </c>
       <c r="L86" t="n">
-        <v>354.53</v>
+        <v>354.57</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>208.7</v>
+        <v>201.46</v>
       </c>
       <c r="K87" t="n">
-        <v>140.62</v>
+        <v>135.74</v>
       </c>
       <c r="L87" t="n">
-        <v>251.65</v>
+        <v>242.93</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.37</v>
+        <v>-3.27</v>
       </c>
       <c r="K88" t="n">
-        <v>-242.3</v>
+        <v>-235.01</v>
       </c>
       <c r="L88" t="n">
-        <v>242.33</v>
+        <v>235.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-34.48</v>
+        <v>-36.35</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.32</v>
+        <v>-8.77</v>
       </c>
       <c r="L14" t="n">
-        <v>35.47</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.65</v>
+        <v>-13.85</v>
       </c>
       <c r="K15" t="n">
-        <v>-48.5</v>
+        <v>-49.2</v>
       </c>
       <c r="L15" t="n">
-        <v>50.38</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.41</v>
+        <v>-55.28</v>
       </c>
       <c r="K16" t="n">
-        <v>15.28</v>
+        <v>15.25</v>
       </c>
       <c r="L16" t="n">
-        <v>57.48</v>
+        <v>57.34</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-57.21</v>
+        <v>-55.33</v>
       </c>
       <c r="K17" t="n">
-        <v>-57.5</v>
+        <v>-55.62</v>
       </c>
       <c r="L17" t="n">
-        <v>81.11</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>22.23</v>
+        <v>23.43</v>
       </c>
       <c r="K18" t="n">
-        <v>53.52</v>
+        <v>56.41</v>
       </c>
       <c r="L18" t="n">
-        <v>57.95</v>
+        <v>61.08</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-61.43</v>
+        <v>-60.97</v>
       </c>
       <c r="K19" t="n">
-        <v>-51.62</v>
+        <v>-51.23</v>
       </c>
       <c r="L19" t="n">
-        <v>80.23999999999999</v>
+        <v>79.63</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-80.63</v>
+        <v>-83.16</v>
       </c>
       <c r="K20" t="n">
-        <v>-41.1</v>
+        <v>-42.39</v>
       </c>
       <c r="L20" t="n">
-        <v>90.5</v>
+        <v>93.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-88.05</v>
+        <v>-86.13</v>
       </c>
       <c r="K21" t="n">
-        <v>81.17</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>119.75</v>
+        <v>117.15</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-17.64</v>
+        <v>-19.13</v>
       </c>
       <c r="K22" t="n">
-        <v>-20.15</v>
+        <v>-21.84</v>
       </c>
       <c r="L22" t="n">
-        <v>26.78</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-55.74</v>
+        <v>-53.32</v>
       </c>
       <c r="K23" t="n">
-        <v>177.8</v>
+        <v>170.08</v>
       </c>
       <c r="L23" t="n">
-        <v>186.33</v>
+        <v>178.24</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>116.48</v>
+        <v>120.98</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.44</v>
+        <v>-8.77</v>
       </c>
       <c r="L24" t="n">
-        <v>116.79</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-157.77</v>
+        <v>-155.91</v>
       </c>
       <c r="K25" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="L25" t="n">
-        <v>157.78</v>
+        <v>155.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-82.06999999999999</v>
+        <v>-86.45</v>
       </c>
       <c r="K26" t="n">
-        <v>119.46</v>
+        <v>125.84</v>
       </c>
       <c r="L26" t="n">
-        <v>144.94</v>
+        <v>152.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>160.64</v>
+        <v>157.54</v>
       </c>
       <c r="K27" t="n">
-        <v>135.1</v>
+        <v>132.49</v>
       </c>
       <c r="L27" t="n">
-        <v>209.9</v>
+        <v>205.85</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>124.27</v>
+        <v>128.46</v>
       </c>
       <c r="K28" t="n">
-        <v>-110.93</v>
+        <v>-114.67</v>
       </c>
       <c r="L28" t="n">
-        <v>166.58</v>
+        <v>172.19</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>54.84</v>
+        <v>55.65</v>
       </c>
       <c r="K29" t="n">
-        <v>6.56</v>
+        <v>6.66</v>
       </c>
       <c r="L29" t="n">
-        <v>55.23</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>11.71</v>
+        <v>11.21</v>
       </c>
       <c r="K30" t="n">
-        <v>65.40000000000001</v>
+        <v>62.58</v>
       </c>
       <c r="L30" t="n">
-        <v>66.44</v>
+        <v>63.57</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>52.62</v>
+        <v>50.93</v>
       </c>
       <c r="K31" t="n">
-        <v>43.69</v>
+        <v>42.29</v>
       </c>
       <c r="L31" t="n">
-        <v>68.40000000000001</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="K32" t="n">
-        <v>-42.12</v>
+        <v>-44.81</v>
       </c>
       <c r="L32" t="n">
-        <v>42.14</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.03</v>
+        <v>-11.14</v>
       </c>
       <c r="K33" t="n">
-        <v>64.95999999999999</v>
+        <v>65.62</v>
       </c>
       <c r="L33" t="n">
-        <v>65.89</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>46.13</v>
+        <v>46.75</v>
       </c>
       <c r="K34" t="n">
-        <v>45.69</v>
+        <v>46.31</v>
       </c>
       <c r="L34" t="n">
-        <v>64.93000000000001</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-101.84</v>
+        <v>-100.32</v>
       </c>
       <c r="K35" t="n">
-        <v>-26.67</v>
+        <v>-26.27</v>
       </c>
       <c r="L35" t="n">
-        <v>105.27</v>
+        <v>103.71</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-85.93000000000001</v>
+        <v>-85.06999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-78.26000000000001</v>
+        <v>-77.48</v>
       </c>
       <c r="L36" t="n">
-        <v>116.23</v>
+        <v>115.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-37.25</v>
+        <v>-36.81</v>
       </c>
       <c r="K37" t="n">
-        <v>103.7</v>
+        <v>102.49</v>
       </c>
       <c r="L37" t="n">
-        <v>110.19</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>136.88</v>
+        <v>132.03</v>
       </c>
       <c r="K38" t="n">
-        <v>-105.76</v>
+        <v>-102.01</v>
       </c>
       <c r="L38" t="n">
-        <v>172.97</v>
+        <v>166.85</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-169.32</v>
+        <v>-162.19</v>
       </c>
       <c r="K39" t="n">
-        <v>-16.04</v>
+        <v>-15.37</v>
       </c>
       <c r="L39" t="n">
-        <v>170.08</v>
+        <v>162.91</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>161.91</v>
+        <v>156.2</v>
       </c>
       <c r="K40" t="n">
-        <v>35.88</v>
+        <v>34.62</v>
       </c>
       <c r="L40" t="n">
-        <v>165.84</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>161.57</v>
+        <v>162.88</v>
       </c>
       <c r="K41" t="n">
-        <v>-85.01000000000001</v>
+        <v>-85.7</v>
       </c>
       <c r="L41" t="n">
-        <v>182.57</v>
+        <v>184.05</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-139.88</v>
+        <v>-145.64</v>
       </c>
       <c r="K42" t="n">
-        <v>-45.07</v>
+        <v>-46.93</v>
       </c>
       <c r="L42" t="n">
-        <v>146.96</v>
+        <v>153.01</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-201.59</v>
+        <v>-199.17</v>
       </c>
       <c r="K43" t="n">
-        <v>-21.43</v>
+        <v>-21.17</v>
       </c>
       <c r="L43" t="n">
-        <v>202.72</v>
+        <v>200.29</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>83.66</v>
+        <v>80.19</v>
       </c>
       <c r="K44" t="n">
-        <v>9.49</v>
+        <v>9.1</v>
       </c>
       <c r="L44" t="n">
-        <v>84.2</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>31.5</v>
+        <v>31.46</v>
       </c>
       <c r="K45" t="n">
-        <v>51.86</v>
+        <v>51.79</v>
       </c>
       <c r="L45" t="n">
-        <v>60.68</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>13.59</v>
+        <v>14.18</v>
       </c>
       <c r="K46" t="n">
-        <v>-54.36</v>
+        <v>-56.72</v>
       </c>
       <c r="L46" t="n">
-        <v>56.03</v>
+        <v>58.46</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-50.7</v>
+        <v>-51.63</v>
       </c>
       <c r="K47" t="n">
-        <v>-52.01</v>
+        <v>-52.97</v>
       </c>
       <c r="L47" t="n">
-        <v>72.63</v>
+        <v>73.97</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>36.25</v>
+        <v>38.74</v>
       </c>
       <c r="K48" t="n">
-        <v>39.6</v>
+        <v>42.31</v>
       </c>
       <c r="L48" t="n">
-        <v>53.68</v>
+        <v>57.37</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>15.32</v>
+        <v>15.21</v>
       </c>
       <c r="K49" t="n">
-        <v>85.66</v>
+        <v>85.03</v>
       </c>
       <c r="L49" t="n">
-        <v>87.02</v>
+        <v>86.38</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-66.79000000000001</v>
+        <v>-64.47</v>
       </c>
       <c r="K50" t="n">
-        <v>130.42</v>
+        <v>125.89</v>
       </c>
       <c r="L50" t="n">
-        <v>146.53</v>
+        <v>141.44</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>24.41</v>
+        <v>25.93</v>
       </c>
       <c r="K51" t="n">
-        <v>76.13</v>
+        <v>80.88</v>
       </c>
       <c r="L51" t="n">
-        <v>79.95</v>
+        <v>84.94</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>60.26</v>
+        <v>60.79</v>
       </c>
       <c r="K52" t="n">
-        <v>-74.28</v>
+        <v>-74.93000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>95.65000000000001</v>
+        <v>96.48999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>190.64</v>
+        <v>182.76</v>
       </c>
       <c r="K53" t="n">
-        <v>5.64</v>
+        <v>5.4</v>
       </c>
       <c r="L53" t="n">
-        <v>190.72</v>
+        <v>182.84</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>174.12</v>
+        <v>171.71</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.95</v>
+        <v>-4.88</v>
       </c>
       <c r="L54" t="n">
-        <v>174.19</v>
+        <v>171.78</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>102.41</v>
+        <v>108.7</v>
       </c>
       <c r="K55" t="n">
-        <v>-32.06</v>
+        <v>-34.03</v>
       </c>
       <c r="L55" t="n">
-        <v>107.32</v>
+        <v>113.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>128.63</v>
+        <v>127.14</v>
       </c>
       <c r="K56" t="n">
-        <v>171.75</v>
+        <v>169.76</v>
       </c>
       <c r="L56" t="n">
-        <v>214.58</v>
+        <v>212.1</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>244.04</v>
+        <v>236.13</v>
       </c>
       <c r="K57" t="n">
-        <v>67.73999999999999</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>253.27</v>
+        <v>245.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-209.68</v>
+        <v>-208.43</v>
       </c>
       <c r="K58" t="n">
-        <v>-55.63</v>
+        <v>-55.29</v>
       </c>
       <c r="L58" t="n">
-        <v>216.94</v>
+        <v>215.64</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-46.01</v>
+        <v>-47.27</v>
       </c>
       <c r="K59" t="n">
-        <v>-17.99</v>
+        <v>-18.48</v>
       </c>
       <c r="L59" t="n">
-        <v>49.4</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-43.69</v>
+        <v>-46</v>
       </c>
       <c r="K60" t="n">
-        <v>12.3</v>
+        <v>12.95</v>
       </c>
       <c r="L60" t="n">
-        <v>45.39</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>24.53</v>
+        <v>25.57</v>
       </c>
       <c r="K61" t="n">
-        <v>40.39</v>
+        <v>42.1</v>
       </c>
       <c r="L61" t="n">
-        <v>47.26</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-66.31999999999999</v>
+        <v>-63.04</v>
       </c>
       <c r="K62" t="n">
-        <v>75.40000000000001</v>
+        <v>71.67</v>
       </c>
       <c r="L62" t="n">
-        <v>100.41</v>
+        <v>95.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>89.73</v>
+        <v>86.47</v>
       </c>
       <c r="K63" t="n">
-        <v>-42.42</v>
+        <v>-40.88</v>
       </c>
       <c r="L63" t="n">
-        <v>99.25</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>79.27</v>
+        <v>77.48</v>
       </c>
       <c r="K64" t="n">
-        <v>37.08</v>
+        <v>36.25</v>
       </c>
       <c r="L64" t="n">
-        <v>87.51000000000001</v>
+        <v>85.54000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-23.95</v>
+        <v>-24.98</v>
       </c>
       <c r="K65" t="n">
-        <v>79.66</v>
+        <v>83.09</v>
       </c>
       <c r="L65" t="n">
-        <v>83.18000000000001</v>
+        <v>86.76000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>13.9</v>
+        <v>14.64</v>
       </c>
       <c r="K66" t="n">
-        <v>75.54000000000001</v>
+        <v>79.56</v>
       </c>
       <c r="L66" t="n">
-        <v>76.81</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>94.29000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="K67" t="n">
-        <v>5.24</v>
+        <v>5.29</v>
       </c>
       <c r="L67" t="n">
-        <v>94.43000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-77.88</v>
+        <v>-76.73</v>
       </c>
       <c r="K68" t="n">
-        <v>-128.87</v>
+        <v>-126.97</v>
       </c>
       <c r="L68" t="n">
-        <v>150.57</v>
+        <v>148.35</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>63.68</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-91.70999999999999</v>
+        <v>-96.28</v>
       </c>
       <c r="L69" t="n">
-        <v>111.65</v>
+        <v>117.21</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>26.09</v>
+        <v>27.18</v>
       </c>
       <c r="K70" t="n">
-        <v>-108.72</v>
+        <v>-113.26</v>
       </c>
       <c r="L70" t="n">
-        <v>111.81</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-138.78</v>
+        <v>-144.42</v>
       </c>
       <c r="K71" t="n">
-        <v>-64.81</v>
+        <v>-67.45</v>
       </c>
       <c r="L71" t="n">
-        <v>153.17</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>127.44</v>
+        <v>130.98</v>
       </c>
       <c r="K72" t="n">
-        <v>113.7</v>
+        <v>116.87</v>
       </c>
       <c r="L72" t="n">
-        <v>170.79</v>
+        <v>175.54</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>41.3</v>
+        <v>39.88</v>
       </c>
       <c r="K73" t="n">
-        <v>-241.69</v>
+        <v>-233.38</v>
       </c>
       <c r="L73" t="n">
-        <v>245.19</v>
+        <v>236.76</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>29.6</v>
+        <v>29.81</v>
       </c>
       <c r="K74" t="n">
-        <v>46.01</v>
+        <v>46.34</v>
       </c>
       <c r="L74" t="n">
-        <v>54.71</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>22.48</v>
+        <v>22.41</v>
       </c>
       <c r="K75" t="n">
-        <v>50.12</v>
+        <v>49.97</v>
       </c>
       <c r="L75" t="n">
-        <v>54.93</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-48.38</v>
+        <v>-46.91</v>
       </c>
       <c r="K76" t="n">
-        <v>-66.69</v>
+        <v>-64.66</v>
       </c>
       <c r="L76" t="n">
-        <v>82.39</v>
+        <v>79.89</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-95.08</v>
+        <v>-89.38</v>
       </c>
       <c r="K77" t="n">
-        <v>-63.99</v>
+        <v>-60.16</v>
       </c>
       <c r="L77" t="n">
-        <v>114.61</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-39.03</v>
+        <v>-37.82</v>
       </c>
       <c r="K78" t="n">
-        <v>85.11</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>93.63</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-26.44</v>
+        <v>-27.49</v>
       </c>
       <c r="K79" t="n">
-        <v>-53.26</v>
+        <v>-55.38</v>
       </c>
       <c r="L79" t="n">
-        <v>59.47</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>137.69</v>
+        <v>130.24</v>
       </c>
       <c r="K80" t="n">
-        <v>47.79</v>
+        <v>45.21</v>
       </c>
       <c r="L80" t="n">
-        <v>145.75</v>
+        <v>137.86</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-138.15</v>
+        <v>-131.83</v>
       </c>
       <c r="K81" t="n">
-        <v>-66.40000000000001</v>
+        <v>-63.36</v>
       </c>
       <c r="L81" t="n">
-        <v>153.28</v>
+        <v>146.27</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>120.21</v>
+        <v>117.63</v>
       </c>
       <c r="K82" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="L82" t="n">
-        <v>120.24</v>
+        <v>117.65</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>156.17</v>
+        <v>155.24</v>
       </c>
       <c r="K83" t="n">
         <v>-0.46</v>
       </c>
       <c r="L83" t="n">
-        <v>156.17</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-20.66</v>
+        <v>-19.95</v>
       </c>
       <c r="K84" t="n">
-        <v>-180.86</v>
+        <v>-174.6</v>
       </c>
       <c r="L84" t="n">
-        <v>182.04</v>
+        <v>175.74</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>94.28</v>
+        <v>95.53</v>
       </c>
       <c r="K85" t="n">
-        <v>-92.48</v>
+        <v>-93.70999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>132.07</v>
+        <v>133.82</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>24.8</v>
+        <v>23.48</v>
       </c>
       <c r="K86" t="n">
-        <v>353.7</v>
+        <v>334.93</v>
       </c>
       <c r="L86" t="n">
-        <v>354.57</v>
+        <v>335.75</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>201.46</v>
+        <v>193.19</v>
       </c>
       <c r="K87" t="n">
-        <v>135.74</v>
+        <v>130.17</v>
       </c>
       <c r="L87" t="n">
-        <v>242.93</v>
+        <v>232.95</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.27</v>
+        <v>-3.15</v>
       </c>
       <c r="K88" t="n">
-        <v>-235.01</v>
+        <v>-226.67</v>
       </c>
       <c r="L88" t="n">
-        <v>235.03</v>
+        <v>226.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.17</v>
+        <v>2.93</v>
       </c>
       <c r="F14" t="n">
-        <v>9.65</v>
+        <v>7.05</v>
       </c>
       <c r="G14" t="n">
-        <v>123.8</v>
+        <v>131.7</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-36.35</v>
+        <v>-51.34</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.77</v>
+        <v>34.95</v>
       </c>
       <c r="L14" t="n">
-        <v>37.4</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:23:21</t>
+          <t>06:23:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="F15" t="n">
-        <v>8.76</v>
+        <v>10.26</v>
       </c>
       <c r="G15" t="n">
-        <v>133.7</v>
+        <v>141.2</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9</v>
+        <v>12.3</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.85</v>
+        <v>-57.91</v>
       </c>
       <c r="K15" t="n">
-        <v>-49.2</v>
+        <v>-48.97</v>
       </c>
       <c r="L15" t="n">
-        <v>51.11</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:25:10</t>
+          <t>06:26:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="F16" t="n">
-        <v>9.42</v>
+        <v>5.67</v>
       </c>
       <c r="G16" t="n">
-        <v>121.8</v>
+        <v>132.4</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="I16" t="n">
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.28</v>
+        <v>-21.84</v>
       </c>
       <c r="K16" t="n">
-        <v>15.25</v>
+        <v>47.32</v>
       </c>
       <c r="L16" t="n">
-        <v>57.34</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:31:09</t>
+          <t>06:30:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="F17" t="n">
-        <v>8.710000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="G17" t="n">
-        <v>121.5</v>
+        <v>127.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-55.33</v>
+        <v>-66.39</v>
       </c>
       <c r="K17" t="n">
-        <v>-55.62</v>
+        <v>-82.92</v>
       </c>
       <c r="L17" t="n">
-        <v>78.45999999999999</v>
+        <v>106.22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:33:26</t>
+          <t>06:32:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="F18" t="n">
-        <v>8.76</v>
+        <v>5.42</v>
       </c>
       <c r="G18" t="n">
-        <v>138.7</v>
+        <v>143.5</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>23.43</v>
+        <v>-66.14</v>
       </c>
       <c r="K18" t="n">
-        <v>56.41</v>
+        <v>-26.52</v>
       </c>
       <c r="L18" t="n">
-        <v>61.08</v>
+        <v>71.26000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:35:36</t>
+          <t>06:34:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="F19" t="n">
-        <v>9.029999999999999</v>
+        <v>6.54</v>
       </c>
       <c r="G19" t="n">
-        <v>115.1</v>
+        <v>140.8</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-60.97</v>
+        <v>53.93</v>
       </c>
       <c r="K19" t="n">
-        <v>-51.23</v>
+        <v>-6.14</v>
       </c>
       <c r="L19" t="n">
-        <v>79.63</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:39:16</t>
+          <t>06:38:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.96</v>
+        <v>2.22</v>
       </c>
       <c r="F20" t="n">
-        <v>9.26</v>
+        <v>4.42</v>
       </c>
       <c r="G20" t="n">
-        <v>127.8</v>
+        <v>143.7</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I20" t="n">
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-83.16</v>
+        <v>-49.71</v>
       </c>
       <c r="K20" t="n">
-        <v>-42.39</v>
+        <v>82.63</v>
       </c>
       <c r="L20" t="n">
-        <v>93.34</v>
+        <v>96.43000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:40:58</t>
+          <t>06:40:10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="F21" t="n">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="G21" t="n">
-        <v>131.2</v>
+        <v>134.4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-86.13</v>
+        <v>-70.61</v>
       </c>
       <c r="K21" t="n">
-        <v>79.40000000000001</v>
+        <v>-38.36</v>
       </c>
       <c r="L21" t="n">
-        <v>117.15</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:43:31</t>
+          <t>06:40:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.98</v>
+        <v>2.09</v>
       </c>
       <c r="F22" t="n">
-        <v>9.59</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>139.7</v>
+        <v>148.4</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-19.13</v>
+        <v>-26.25</v>
       </c>
       <c r="K22" t="n">
-        <v>-21.84</v>
+        <v>133.27</v>
       </c>
       <c r="L22" t="n">
-        <v>29.03</v>
+        <v>135.83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:47:57</t>
+          <t>06:44:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="F23" t="n">
-        <v>8.279999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="G23" t="n">
-        <v>119.4</v>
+        <v>134.8</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-53.32</v>
+        <v>-109.42</v>
       </c>
       <c r="K23" t="n">
-        <v>170.08</v>
+        <v>-73.91</v>
       </c>
       <c r="L23" t="n">
-        <v>178.24</v>
+        <v>132.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:49:38</t>
+          <t>06:46:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="F24" t="n">
-        <v>8.84</v>
+        <v>7.88</v>
       </c>
       <c r="G24" t="n">
-        <v>138.8</v>
+        <v>132</v>
       </c>
       <c r="H24" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>120.98</v>
+        <v>116.94</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.77</v>
+        <v>-95.68000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>121.3</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:51:33</t>
+          <t>06:48:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="F25" t="n">
-        <v>8.960000000000001</v>
+        <v>7.12</v>
       </c>
       <c r="G25" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-155.91</v>
+        <v>136.53</v>
       </c>
       <c r="K25" t="n">
-        <v>2.02</v>
+        <v>45.57</v>
       </c>
       <c r="L25" t="n">
-        <v>155.93</v>
+        <v>143.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:55:49</t>
+          <t>06:52:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.24</v>
+        <v>1.57</v>
       </c>
       <c r="F26" t="n">
-        <v>9.970000000000001</v>
+        <v>2.43</v>
       </c>
       <c r="G26" t="n">
-        <v>128.9</v>
+        <v>139.7</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-86.45</v>
+        <v>-120.3</v>
       </c>
       <c r="K26" t="n">
-        <v>125.84</v>
+        <v>150.53</v>
       </c>
       <c r="L26" t="n">
-        <v>152.67</v>
+        <v>192.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:57:27</t>
+          <t>06:55:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="G27" t="n">
-        <v>104.3</v>
+        <v>142.6</v>
       </c>
       <c r="H27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>157.54</v>
+        <v>221.59</v>
       </c>
       <c r="K27" t="n">
-        <v>132.49</v>
+        <v>-16.19</v>
       </c>
       <c r="L27" t="n">
-        <v>205.85</v>
+        <v>222.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:58:16</t>
+          <t>06:57:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="F28" t="n">
-        <v>9.82</v>
+        <v>10.46</v>
       </c>
       <c r="G28" t="n">
-        <v>129.2</v>
+        <v>132.4</v>
       </c>
       <c r="H28" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>128.46</v>
+        <v>155.85</v>
       </c>
       <c r="K28" t="n">
-        <v>-114.67</v>
+        <v>-241.59</v>
       </c>
       <c r="L28" t="n">
-        <v>172.19</v>
+        <v>287.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:09:25</t>
+          <t>07:09:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="F29" t="n">
-        <v>9.34</v>
+        <v>5.55</v>
       </c>
       <c r="G29" t="n">
-        <v>130.9</v>
+        <v>128.8</v>
       </c>
       <c r="H29" t="n">
-        <v>2.2</v>
+        <v>10.1</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>55.65</v>
+        <v>70.63</v>
       </c>
       <c r="K29" t="n">
-        <v>6.66</v>
+        <v>24.95</v>
       </c>
       <c r="L29" t="n">
-        <v>56.05</v>
+        <v>74.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:11:20</t>
+          <t>07:10:37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="F30" t="n">
-        <v>9.050000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="G30" t="n">
-        <v>131.6</v>
+        <v>141</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>11.21</v>
+        <v>-49.05</v>
       </c>
       <c r="K30" t="n">
-        <v>62.58</v>
+        <v>-5.52</v>
       </c>
       <c r="L30" t="n">
-        <v>63.57</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:12:52</t>
+          <t>07:11:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="F31" t="n">
-        <v>9.19</v>
+        <v>6.89</v>
       </c>
       <c r="G31" t="n">
-        <v>126.1</v>
+        <v>131.3</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>50.93</v>
+        <v>-50.97</v>
       </c>
       <c r="K31" t="n">
-        <v>42.29</v>
+        <v>1.14</v>
       </c>
       <c r="L31" t="n">
-        <v>66.2</v>
+        <v>50.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:17:38</t>
+          <t>07:15:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.83</v>
+        <v>2.73</v>
       </c>
       <c r="F32" t="n">
-        <v>7.62</v>
+        <v>10.46</v>
       </c>
       <c r="G32" t="n">
-        <v>123.2</v>
+        <v>124.3</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>1.27</v>
+        <v>-11.74</v>
       </c>
       <c r="K32" t="n">
-        <v>-44.81</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>44.83</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:19:48</t>
+          <t>07:17:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.07</v>
+        <v>2.39</v>
       </c>
       <c r="F33" t="n">
-        <v>8.75</v>
+        <v>7.87</v>
       </c>
       <c r="G33" t="n">
-        <v>131.8</v>
+        <v>125.7</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.14</v>
+        <v>55.76</v>
       </c>
       <c r="K33" t="n">
-        <v>65.62</v>
+        <v>-29.42</v>
       </c>
       <c r="L33" t="n">
-        <v>66.56</v>
+        <v>63.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:21:36</t>
+          <t>07:20:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F34" t="n">
-        <v>9.26</v>
+        <v>7.53</v>
       </c>
       <c r="G34" t="n">
-        <v>147.2</v>
+        <v>133.3</v>
       </c>
       <c r="H34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>46.75</v>
+        <v>-76.03</v>
       </c>
       <c r="K34" t="n">
-        <v>46.31</v>
+        <v>-20.2</v>
       </c>
       <c r="L34" t="n">
-        <v>65.8</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:26:53</t>
+          <t>07:24:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.54</v>
+        <v>3.02</v>
       </c>
       <c r="F35" t="n">
-        <v>9.199999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="G35" t="n">
-        <v>119.2</v>
+        <v>132.1</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-100.32</v>
+        <v>-80.73</v>
       </c>
       <c r="K35" t="n">
-        <v>-26.27</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>103.71</v>
+        <v>111.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:28:31</t>
+          <t>07:25:50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="F36" t="n">
-        <v>9.34</v>
+        <v>7.75</v>
       </c>
       <c r="G36" t="n">
-        <v>133.5</v>
+        <v>128.1</v>
       </c>
       <c r="H36" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-85.06999999999999</v>
+        <v>-31.69</v>
       </c>
       <c r="K36" t="n">
-        <v>-77.48</v>
+        <v>105.36</v>
       </c>
       <c r="L36" t="n">
-        <v>115.06</v>
+        <v>110.03</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:29:27</t>
+          <t>07:28:09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="F37" t="n">
-        <v>8.94</v>
+        <v>9.06</v>
       </c>
       <c r="G37" t="n">
-        <v>131.7</v>
+        <v>139.8</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-36.81</v>
+        <v>-70.22</v>
       </c>
       <c r="K37" t="n">
-        <v>102.49</v>
+        <v>-110.75</v>
       </c>
       <c r="L37" t="n">
-        <v>108.9</v>
+        <v>131.13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:33:42</t>
+          <t>07:31:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="F38" t="n">
-        <v>9.140000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>123.1</v>
+        <v>120.4</v>
       </c>
       <c r="H38" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>132.03</v>
+        <v>-177.67</v>
       </c>
       <c r="K38" t="n">
-        <v>-102.01</v>
+        <v>-25.86</v>
       </c>
       <c r="L38" t="n">
-        <v>166.85</v>
+        <v>179.55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:35:49</t>
+          <t>07:32:57</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="F39" t="n">
-        <v>8.56</v>
+        <v>9.75</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7</v>
+        <v>134.3</v>
       </c>
       <c r="H39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-162.19</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-15.37</v>
+        <v>122.76</v>
       </c>
       <c r="L39" t="n">
-        <v>162.91</v>
+        <v>143.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:38:13</t>
+          <t>07:35:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="F40" t="n">
-        <v>8.49</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>132.4</v>
+        <v>149.4</v>
       </c>
       <c r="H40" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>156.2</v>
+        <v>120.66</v>
       </c>
       <c r="K40" t="n">
-        <v>34.62</v>
+        <v>-83.06</v>
       </c>
       <c r="L40" t="n">
-        <v>159.99</v>
+        <v>146.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:41:54</t>
+          <t>07:40:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="F41" t="n">
-        <v>10.01</v>
+        <v>5.12</v>
       </c>
       <c r="G41" t="n">
-        <v>115.9</v>
+        <v>131.9</v>
       </c>
       <c r="H41" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>162.88</v>
+        <v>15.38</v>
       </c>
       <c r="K41" t="n">
-        <v>-85.7</v>
+        <v>-173.95</v>
       </c>
       <c r="L41" t="n">
-        <v>184.05</v>
+        <v>174.63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:43:44</t>
+          <t>07:42:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="F42" t="n">
-        <v>9.279999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="G42" t="n">
-        <v>134.1</v>
+        <v>148.2</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-145.64</v>
+        <v>-210.15</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.93</v>
+        <v>-66.48</v>
       </c>
       <c r="L42" t="n">
-        <v>153.01</v>
+        <v>220.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:46:03</t>
+          <t>07:44:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="F43" t="n">
-        <v>9.94</v>
+        <v>9.9</v>
       </c>
       <c r="G43" t="n">
-        <v>126.8</v>
+        <v>135.2</v>
       </c>
       <c r="H43" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-199.17</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-21.17</v>
+        <v>-167.28</v>
       </c>
       <c r="L43" t="n">
-        <v>200.29</v>
+        <v>191.26</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:56:39</t>
+          <t>07:56:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="F44" t="n">
-        <v>9.300000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="G44" t="n">
-        <v>131.5</v>
+        <v>136.1</v>
       </c>
       <c r="H44" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>80.19</v>
+        <v>33.67</v>
       </c>
       <c r="K44" t="n">
-        <v>9.1</v>
+        <v>53.8</v>
       </c>
       <c r="L44" t="n">
-        <v>80.7</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:59:17</t>
+          <t>07:59:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.55</v>
+        <v>3.16</v>
       </c>
       <c r="F45" t="n">
-        <v>9.34</v>
+        <v>9.83</v>
       </c>
       <c r="G45" t="n">
-        <v>140</v>
+        <v>135.4</v>
       </c>
       <c r="H45" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>31.46</v>
+        <v>-40.07</v>
       </c>
       <c r="K45" t="n">
-        <v>51.79</v>
+        <v>56.88</v>
       </c>
       <c r="L45" t="n">
-        <v>60.6</v>
+        <v>69.58</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:01:02</t>
+          <t>08:01:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,28 +1969,28 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.17</v>
+        <v>2.68</v>
       </c>
       <c r="F46" t="n">
-        <v>9.49</v>
+        <v>8.77</v>
       </c>
       <c r="G46" t="n">
-        <v>112.8</v>
+        <v>122.1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>14.18</v>
+        <v>-41.78</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.72</v>
+        <v>-42.53</v>
       </c>
       <c r="L46" t="n">
-        <v>58.46</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="47">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="F47" t="n">
-        <v>8.640000000000001</v>
+        <v>10.46</v>
       </c>
       <c r="G47" t="n">
-        <v>134.9</v>
+        <v>142.2</v>
       </c>
       <c r="H47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-51.63</v>
+        <v>31.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-52.97</v>
+        <v>68.03</v>
       </c>
       <c r="L47" t="n">
-        <v>73.97</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:08:27</t>
+          <t>08:08:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.03</v>
+        <v>3.21</v>
       </c>
       <c r="F48" t="n">
-        <v>8.44</v>
+        <v>10.46</v>
       </c>
       <c r="G48" t="n">
-        <v>132.1</v>
+        <v>128.6</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>38.74</v>
+        <v>18.41</v>
       </c>
       <c r="K48" t="n">
-        <v>42.31</v>
+        <v>88.12</v>
       </c>
       <c r="L48" t="n">
-        <v>57.37</v>
+        <v>90.03</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:10:10</t>
+          <t>08:09:31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="F49" t="n">
-        <v>8.960000000000001</v>
+        <v>10.46</v>
       </c>
       <c r="G49" t="n">
-        <v>134.3</v>
+        <v>139.4</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>15.21</v>
+        <v>93.27</v>
       </c>
       <c r="K49" t="n">
-        <v>85.03</v>
+        <v>55.69</v>
       </c>
       <c r="L49" t="n">
-        <v>86.38</v>
+        <v>108.63</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:15:10</t>
+          <t>08:14:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="F50" t="n">
-        <v>8.26</v>
+        <v>10.46</v>
       </c>
       <c r="G50" t="n">
-        <v>128.8</v>
+        <v>133.2</v>
       </c>
       <c r="H50" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-64.47</v>
+        <v>41.93</v>
       </c>
       <c r="K50" t="n">
-        <v>125.89</v>
+        <v>81.78</v>
       </c>
       <c r="L50" t="n">
-        <v>141.44</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:17:37</t>
+          <t>08:16:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.13</v>
+        <v>2.52</v>
       </c>
       <c r="F51" t="n">
-        <v>9.199999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="G51" t="n">
-        <v>139.3</v>
+        <v>119.9</v>
       </c>
       <c r="H51" t="n">
-        <v>11.2</v>
+        <v>2.8</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>25.93</v>
+        <v>-80.37</v>
       </c>
       <c r="K51" t="n">
-        <v>80.88</v>
+        <v>61.37</v>
       </c>
       <c r="L51" t="n">
-        <v>84.94</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:19:29</t>
+          <t>08:17:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.53</v>
+        <v>3.07</v>
       </c>
       <c r="F52" t="n">
-        <v>9.23</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>131.6</v>
+        <v>138.3</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3</v>
+        <v>7.7</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>60.79</v>
+        <v>143.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-74.93000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="L52" t="n">
-        <v>96.48999999999999</v>
+        <v>143.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:25:20</t>
+          <t>08:22:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="F53" t="n">
-        <v>9.449999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="G53" t="n">
-        <v>143.6</v>
+        <v>137.5</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>182.76</v>
+        <v>37.51</v>
       </c>
       <c r="K53" t="n">
-        <v>5.4</v>
+        <v>143.69</v>
       </c>
       <c r="L53" t="n">
-        <v>182.84</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:26:36</t>
+          <t>08:24:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="F54" t="n">
-        <v>9.06</v>
+        <v>6.65</v>
       </c>
       <c r="G54" t="n">
-        <v>123.3</v>
+        <v>121.2</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>171.71</v>
+        <v>107.9</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.88</v>
+        <v>-38.48</v>
       </c>
       <c r="L54" t="n">
-        <v>171.78</v>
+        <v>114.55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:27:51</t>
+          <t>08:26:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="F55" t="n">
-        <v>8.59</v>
+        <v>10.46</v>
       </c>
       <c r="G55" t="n">
-        <v>127.3</v>
+        <v>150.9</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>108.7</v>
+        <v>165.41</v>
       </c>
       <c r="K55" t="n">
-        <v>-34.03</v>
+        <v>115.84</v>
       </c>
       <c r="L55" t="n">
-        <v>113.91</v>
+        <v>201.94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:32:31</t>
+          <t>08:30:32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="F56" t="n">
-        <v>9.039999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="G56" t="n">
-        <v>147.3</v>
+        <v>130.8</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>127.14</v>
+        <v>245.78</v>
       </c>
       <c r="K56" t="n">
-        <v>169.76</v>
+        <v>40.95</v>
       </c>
       <c r="L56" t="n">
-        <v>212.1</v>
+        <v>249.17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:34:31</t>
+          <t>08:32:54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.23</v>
+        <v>3.53</v>
       </c>
       <c r="F57" t="n">
-        <v>9.07</v>
+        <v>9.51</v>
       </c>
       <c r="G57" t="n">
-        <v>123.4</v>
+        <v>130.4</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>236.13</v>
+        <v>10.21</v>
       </c>
       <c r="K57" t="n">
-        <v>65.54000000000001</v>
+        <v>-250.13</v>
       </c>
       <c r="L57" t="n">
-        <v>245.05</v>
+        <v>250.34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:35:43</t>
+          <t>08:33:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.53</v>
+        <v>2.43</v>
       </c>
       <c r="F58" t="n">
-        <v>9.699999999999999</v>
+        <v>7.52</v>
       </c>
       <c r="G58" t="n">
-        <v>128.5</v>
+        <v>130.6</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-208.43</v>
+        <v>-117.53</v>
       </c>
       <c r="K58" t="n">
-        <v>-55.29</v>
+        <v>-115.26</v>
       </c>
       <c r="L58" t="n">
-        <v>215.64</v>
+        <v>164.62</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:48:12</t>
+          <t>08:44:29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.53</v>
+        <v>2.96</v>
       </c>
       <c r="F59" t="n">
-        <v>9.06</v>
+        <v>10.46</v>
       </c>
       <c r="G59" t="n">
-        <v>132.7</v>
+        <v>135.1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1</v>
+        <v>5.5</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-47.27</v>
+        <v>20.01</v>
       </c>
       <c r="K59" t="n">
-        <v>-18.48</v>
+        <v>52.2</v>
       </c>
       <c r="L59" t="n">
-        <v>50.75</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:49:49</t>
+          <t>08:45:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="F60" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="G60" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="H60" t="n">
         <v>9.5</v>
       </c>
-      <c r="G60" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>5.3</v>
-      </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-46</v>
+        <v>31.27</v>
       </c>
       <c r="K60" t="n">
-        <v>12.95</v>
+        <v>48.98</v>
       </c>
       <c r="L60" t="n">
-        <v>47.79</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:52:12</t>
+          <t>08:48:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.05</v>
+        <v>2.67</v>
       </c>
       <c r="F61" t="n">
-        <v>8.33</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>147.2</v>
+        <v>132.3</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>25.57</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>42.1</v>
+        <v>37.9</v>
       </c>
       <c r="L61" t="n">
-        <v>49.25</v>
+        <v>77.38</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:56:37</t>
+          <t>08:54:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.69</v>
+        <v>3.42</v>
       </c>
       <c r="F62" t="n">
-        <v>8.66</v>
+        <v>10.46</v>
       </c>
       <c r="G62" t="n">
-        <v>121.8</v>
+        <v>109.9</v>
       </c>
       <c r="H62" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-63.04</v>
+        <v>87.83</v>
       </c>
       <c r="K62" t="n">
-        <v>71.67</v>
+        <v>-40.77</v>
       </c>
       <c r="L62" t="n">
-        <v>95.45</v>
+        <v>96.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:58:25</t>
+          <t>08:55:33</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="F63" t="n">
-        <v>8.029999999999999</v>
+        <v>10.43</v>
       </c>
       <c r="G63" t="n">
-        <v>124.3</v>
+        <v>120.5</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>86.47</v>
+        <v>64.19</v>
       </c>
       <c r="K63" t="n">
-        <v>-40.88</v>
+        <v>-23.87</v>
       </c>
       <c r="L63" t="n">
-        <v>95.65000000000001</v>
+        <v>68.48999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:00:10</t>
+          <t>08:57:59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="F64" t="n">
-        <v>8.48</v>
+        <v>10.46</v>
       </c>
       <c r="G64" t="n">
-        <v>141.6</v>
+        <v>136.2</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>77.48</v>
+        <v>-18.92</v>
       </c>
       <c r="K64" t="n">
-        <v>36.25</v>
+        <v>63.3</v>
       </c>
       <c r="L64" t="n">
-        <v>85.54000000000001</v>
+        <v>66.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:04:46</t>
+          <t>09:03:16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="F65" t="n">
-        <v>9.34</v>
+        <v>10.46</v>
       </c>
       <c r="G65" t="n">
-        <v>130.8</v>
+        <v>123.4</v>
       </c>
       <c r="H65" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I65" t="n">
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-24.98</v>
+        <v>78.69</v>
       </c>
       <c r="K65" t="n">
-        <v>83.09</v>
+        <v>-91.27</v>
       </c>
       <c r="L65" t="n">
-        <v>86.76000000000001</v>
+        <v>120.51</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:06:02</t>
+          <t>09:05:44</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="F66" t="n">
-        <v>9.43</v>
+        <v>9.66</v>
       </c>
       <c r="G66" t="n">
-        <v>123.6</v>
+        <v>124.6</v>
       </c>
       <c r="H66" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="I66" t="n">
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>14.64</v>
+        <v>112.4</v>
       </c>
       <c r="K66" t="n">
-        <v>79.56</v>
+        <v>-0.11</v>
       </c>
       <c r="L66" t="n">
-        <v>80.90000000000001</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:08:33</t>
+          <t>09:06:46</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.68</v>
+        <v>2.49</v>
       </c>
       <c r="F67" t="n">
-        <v>8.77</v>
+        <v>7.77</v>
       </c>
       <c r="G67" t="n">
-        <v>137</v>
+        <v>138.5</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>95.36</v>
+        <v>-102.69</v>
       </c>
       <c r="K67" t="n">
-        <v>5.29</v>
+        <v>47.16</v>
       </c>
       <c r="L67" t="n">
-        <v>95.5</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:14:37</t>
+          <t>09:12:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.51</v>
+        <v>3.16</v>
       </c>
       <c r="F68" t="n">
-        <v>8.1</v>
+        <v>10.46</v>
       </c>
       <c r="G68" t="n">
-        <v>120.1</v>
+        <v>142.1</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-76.73</v>
+        <v>81.69</v>
       </c>
       <c r="K68" t="n">
-        <v>-126.97</v>
+        <v>-111.29</v>
       </c>
       <c r="L68" t="n">
-        <v>148.35</v>
+        <v>138.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:15:50</t>
+          <t>09:13:02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="F69" t="n">
-        <v>9.640000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="G69" t="n">
-        <v>147.7</v>
+        <v>133.2</v>
       </c>
       <c r="H69" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>66.84999999999999</v>
+        <v>-76.43000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-96.28</v>
+        <v>108.59</v>
       </c>
       <c r="L69" t="n">
-        <v>117.21</v>
+        <v>132.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:18:17</t>
+          <t>09:13:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.93</v>
+        <v>2.63</v>
       </c>
       <c r="F70" t="n">
-        <v>8.529999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="G70" t="n">
-        <v>125.1</v>
+        <v>124.9</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>27.18</v>
+        <v>-104.06</v>
       </c>
       <c r="K70" t="n">
-        <v>-113.26</v>
+        <v>-66.54000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>116.47</v>
+        <v>123.52</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:23:33</t>
+          <t>09:18:21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="F71" t="n">
-        <v>8.779999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="G71" t="n">
-        <v>138.7</v>
+        <v>134.4</v>
       </c>
       <c r="H71" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-144.42</v>
+        <v>151.94</v>
       </c>
       <c r="K71" t="n">
-        <v>-67.45</v>
+        <v>-155.79</v>
       </c>
       <c r="L71" t="n">
-        <v>159.4</v>
+        <v>217.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:26:01</t>
+          <t>09:20:10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="F72" t="n">
-        <v>8.67</v>
+        <v>10.27</v>
       </c>
       <c r="G72" t="n">
-        <v>133.5</v>
+        <v>121.2</v>
       </c>
       <c r="H72" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>130.98</v>
+        <v>70.64</v>
       </c>
       <c r="K72" t="n">
-        <v>116.87</v>
+        <v>-254.78</v>
       </c>
       <c r="L72" t="n">
-        <v>175.54</v>
+        <v>264.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:27:03</t>
+          <t>09:21:46</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="F73" t="n">
-        <v>8.6</v>
+        <v>10.46</v>
       </c>
       <c r="G73" t="n">
-        <v>129.1</v>
+        <v>133.2</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>39.88</v>
+        <v>160.59</v>
       </c>
       <c r="K73" t="n">
-        <v>-233.38</v>
+        <v>-232.38</v>
       </c>
       <c r="L73" t="n">
-        <v>236.76</v>
+        <v>282.47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:38:19</t>
+          <t>09:31:22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="F74" t="n">
-        <v>9.15</v>
+        <v>10.46</v>
       </c>
       <c r="G74" t="n">
-        <v>133</v>
+        <v>106.5</v>
       </c>
       <c r="H74" t="n">
-        <v>9.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>29.81</v>
+        <v>31.04</v>
       </c>
       <c r="K74" t="n">
-        <v>46.34</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>55.1</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:39:25</t>
+          <t>09:32:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="F75" t="n">
-        <v>7.86</v>
+        <v>10.46</v>
       </c>
       <c r="G75" t="n">
-        <v>130.4</v>
+        <v>148.8</v>
       </c>
       <c r="H75" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>22.41</v>
+        <v>-74.45999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>49.97</v>
+        <v>-23.41</v>
       </c>
       <c r="L75" t="n">
-        <v>54.76</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:40:39</t>
+          <t>09:34:38</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="F76" t="n">
-        <v>8.94</v>
+        <v>10.46</v>
       </c>
       <c r="G76" t="n">
-        <v>139.3</v>
+        <v>131.2</v>
       </c>
       <c r="H76" t="n">
-        <v>9.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="I76" t="n">
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-46.91</v>
+        <v>-81.87</v>
       </c>
       <c r="K76" t="n">
-        <v>-64.66</v>
+        <v>-55.12</v>
       </c>
       <c r="L76" t="n">
-        <v>79.89</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:44:46</t>
+          <t>09:40:24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="F77" t="n">
-        <v>9.1</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>131</v>
+        <v>120.7</v>
       </c>
       <c r="H77" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-89.38</v>
+        <v>82.62</v>
       </c>
       <c r="K77" t="n">
-        <v>-60.16</v>
+        <v>69.72</v>
       </c>
       <c r="L77" t="n">
-        <v>107.74</v>
+        <v>108.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:45:53</t>
+          <t>09:41:39</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.89</v>
+        <v>3.16</v>
       </c>
       <c r="F78" t="n">
-        <v>9.07</v>
+        <v>10.46</v>
       </c>
       <c r="G78" t="n">
-        <v>142.5</v>
+        <v>131.5</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-37.82</v>
+        <v>-28.61</v>
       </c>
       <c r="K78" t="n">
-        <v>82.48999999999999</v>
+        <v>-65.23999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>90.75</v>
+        <v>71.23999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:48:40</t>
+          <t>09:42:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.45</v>
+        <v>2.66</v>
       </c>
       <c r="F79" t="n">
-        <v>9.109999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="G79" t="n">
         <v>134.4</v>
       </c>
       <c r="H79" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="I79" t="n">
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-27.49</v>
+        <v>59.57</v>
       </c>
       <c r="K79" t="n">
-        <v>-55.38</v>
+        <v>51.04</v>
       </c>
       <c r="L79" t="n">
-        <v>61.83</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:52:50</t>
+          <t>09:47:54</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.68</v>
+        <v>3.78</v>
       </c>
       <c r="F80" t="n">
-        <v>9.24</v>
+        <v>10.46</v>
       </c>
       <c r="G80" t="n">
-        <v>129</v>
+        <v>134.9</v>
       </c>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>130.24</v>
+        <v>-125.09</v>
       </c>
       <c r="K80" t="n">
-        <v>45.21</v>
+        <v>-70.38</v>
       </c>
       <c r="L80" t="n">
-        <v>137.86</v>
+        <v>143.53</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:53:53</t>
+          <t>09:50:33</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.58</v>
+        <v>3.11</v>
       </c>
       <c r="F81" t="n">
-        <v>9.279999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="G81" t="n">
-        <v>124.7</v>
+        <v>135.6</v>
       </c>
       <c r="H81" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I81" t="n">
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-131.83</v>
+        <v>32.39</v>
       </c>
       <c r="K81" t="n">
-        <v>-63.36</v>
+        <v>-76.33</v>
       </c>
       <c r="L81" t="n">
-        <v>146.27</v>
+        <v>82.91</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:56:07</t>
+          <t>09:51:45</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="F82" t="n">
-        <v>9.300000000000001</v>
+        <v>10.46</v>
       </c>
       <c r="G82" t="n">
-        <v>129.1</v>
+        <v>133.4</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>117.63</v>
+        <v>116.63</v>
       </c>
       <c r="K82" t="n">
-        <v>2.42</v>
+        <v>-3.01</v>
       </c>
       <c r="L82" t="n">
-        <v>117.65</v>
+        <v>116.67</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:01:52</t>
+          <t>09:56:35</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="F83" t="n">
-        <v>9.210000000000001</v>
+        <v>10.46</v>
       </c>
       <c r="G83" t="n">
-        <v>137.3</v>
+        <v>123.2</v>
       </c>
       <c r="H83" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>155.24</v>
+        <v>-182.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.46</v>
+        <v>46.75</v>
       </c>
       <c r="L83" t="n">
-        <v>155.25</v>
+        <v>188.74</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:03:07</t>
+          <t>09:58:12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="F84" t="n">
-        <v>9.42</v>
+        <v>10.46</v>
       </c>
       <c r="G84" t="n">
-        <v>127.5</v>
+        <v>136.9</v>
       </c>
       <c r="H84" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-19.95</v>
+        <v>120.42</v>
       </c>
       <c r="K84" t="n">
-        <v>-174.6</v>
+        <v>-119.54</v>
       </c>
       <c r="L84" t="n">
-        <v>175.74</v>
+        <v>169.67</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:04:20</t>
+          <t>10:00:01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="F85" t="n">
-        <v>9.380000000000001</v>
+        <v>10.46</v>
       </c>
       <c r="G85" t="n">
-        <v>138</v>
+        <v>138.5</v>
       </c>
       <c r="H85" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I85" t="n">
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>95.53</v>
+        <v>235.38</v>
       </c>
       <c r="K85" t="n">
-        <v>-93.70999999999999</v>
+        <v>-94.73</v>
       </c>
       <c r="L85" t="n">
-        <v>133.82</v>
+        <v>253.72</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:09:22</t>
+          <t>10:04:21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.21</v>
+        <v>3.16</v>
       </c>
       <c r="F86" t="n">
-        <v>9.19</v>
+        <v>10.46</v>
       </c>
       <c r="G86" t="n">
-        <v>121.4</v>
+        <v>139.9</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>23.48</v>
+        <v>244.8</v>
       </c>
       <c r="K86" t="n">
-        <v>334.93</v>
+        <v>124.56</v>
       </c>
       <c r="L86" t="n">
-        <v>335.75</v>
+        <v>274.67</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:12:02</t>
+          <t>10:05:25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="F87" t="n">
-        <v>9.529999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="G87" t="n">
-        <v>136.5</v>
+        <v>142.1</v>
       </c>
       <c r="H87" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>193.19</v>
+        <v>-163.05</v>
       </c>
       <c r="K87" t="n">
-        <v>130.17</v>
+        <v>235.05</v>
       </c>
       <c r="L87" t="n">
-        <v>232.95</v>
+        <v>286.06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:13:13</t>
+          <t>10:07:21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="F88" t="n">
-        <v>9.19</v>
+        <v>10.46</v>
       </c>
       <c r="G88" t="n">
-        <v>143.5</v>
+        <v>129.7</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.15</v>
+        <v>96.89</v>
       </c>
       <c r="K88" t="n">
-        <v>-226.67</v>
+        <v>-242.57</v>
       </c>
       <c r="L88" t="n">
-        <v>226.7</v>
+        <v>261.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-51.34</v>
+        <v>-49.2</v>
       </c>
       <c r="K14" t="n">
-        <v>34.95</v>
+        <v>33.49</v>
       </c>
       <c r="L14" t="n">
-        <v>62.1</v>
+        <v>59.51</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-57.91</v>
+        <v>-56.73</v>
       </c>
       <c r="K15" t="n">
-        <v>-48.97</v>
+        <v>-47.97</v>
       </c>
       <c r="L15" t="n">
-        <v>75.84</v>
+        <v>74.29000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-66.39</v>
+        <v>-67.7</v>
       </c>
       <c r="K17" t="n">
-        <v>-82.92</v>
+        <v>-84.54000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>106.22</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-66.14</v>
+        <v>-67.44</v>
       </c>
       <c r="K18" t="n">
-        <v>-26.52</v>
+        <v>-27.04</v>
       </c>
       <c r="L18" t="n">
-        <v>71.26000000000001</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>53.93</v>
+        <v>51.69</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.14</v>
+        <v>-5.89</v>
       </c>
       <c r="L19" t="n">
-        <v>54.28</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-49.71</v>
+        <v>-53.39</v>
       </c>
       <c r="K20" t="n">
-        <v>82.63</v>
+        <v>88.75</v>
       </c>
       <c r="L20" t="n">
-        <v>96.43000000000001</v>
+        <v>103.57</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-70.61</v>
+        <v>-67.67</v>
       </c>
       <c r="K21" t="n">
-        <v>-38.36</v>
+        <v>-36.76</v>
       </c>
       <c r="L21" t="n">
-        <v>80.36</v>
+        <v>77.01000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-26.25</v>
+        <v>-25.15</v>
       </c>
       <c r="K22" t="n">
-        <v>133.27</v>
+        <v>127.72</v>
       </c>
       <c r="L22" t="n">
-        <v>135.83</v>
+        <v>130.17</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-109.42</v>
+        <v>-115.62</v>
       </c>
       <c r="K23" t="n">
-        <v>-73.91</v>
+        <v>-78.09</v>
       </c>
       <c r="L23" t="n">
-        <v>132.05</v>
+        <v>139.52</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>116.94</v>
+        <v>114.55</v>
       </c>
       <c r="K24" t="n">
-        <v>-95.68000000000001</v>
+        <v>-93.73</v>
       </c>
       <c r="L24" t="n">
-        <v>151.09</v>
+        <v>148.01</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>136.53</v>
+        <v>139.21</v>
       </c>
       <c r="K25" t="n">
-        <v>45.57</v>
+        <v>46.47</v>
       </c>
       <c r="L25" t="n">
-        <v>143.94</v>
+        <v>146.76</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-120.3</v>
+        <v>-124.93</v>
       </c>
       <c r="K26" t="n">
-        <v>150.53</v>
+        <v>156.32</v>
       </c>
       <c r="L26" t="n">
-        <v>192.7</v>
+        <v>200.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>221.59</v>
+        <v>212.35</v>
       </c>
       <c r="K27" t="n">
-        <v>-16.19</v>
+        <v>-15.52</v>
       </c>
       <c r="L27" t="n">
-        <v>222.18</v>
+        <v>212.92</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>155.85</v>
+        <v>164.67</v>
       </c>
       <c r="K28" t="n">
-        <v>-241.59</v>
+        <v>-255.26</v>
       </c>
       <c r="L28" t="n">
-        <v>287.49</v>
+        <v>303.77</v>
       </c>
     </row>
     <row r="29">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-49.05</v>
+        <v>-47.01</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.52</v>
+        <v>-5.29</v>
       </c>
       <c r="L30" t="n">
-        <v>49.36</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-50.97</v>
+        <v>-52.94</v>
       </c>
       <c r="K31" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="L31" t="n">
-        <v>50.99</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-11.74</v>
+        <v>-12.61</v>
       </c>
       <c r="K32" t="n">
-        <v>80.56999999999999</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>81.42</v>
+        <v>87.45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>55.76</v>
+        <v>53.44</v>
       </c>
       <c r="K33" t="n">
-        <v>-29.42</v>
+        <v>-28.2</v>
       </c>
       <c r="L33" t="n">
-        <v>63.05</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-76.03</v>
+        <v>-77.52</v>
       </c>
       <c r="K34" t="n">
-        <v>-20.2</v>
+        <v>-20.59</v>
       </c>
       <c r="L34" t="n">
-        <v>78.66</v>
+        <v>80.20999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-80.73</v>
+        <v>-85.3</v>
       </c>
       <c r="K35" t="n">
-        <v>-76.95999999999999</v>
+        <v>-81.31999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>111.53</v>
+        <v>117.85</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-31.69</v>
+        <v>-32.91</v>
       </c>
       <c r="K36" t="n">
-        <v>105.36</v>
+        <v>109.42</v>
       </c>
       <c r="L36" t="n">
-        <v>110.03</v>
+        <v>114.26</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-70.22</v>
+        <v>-71.59999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-110.75</v>
+        <v>-112.92</v>
       </c>
       <c r="L37" t="n">
-        <v>131.13</v>
+        <v>133.71</v>
       </c>
     </row>
     <row r="38">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>120.66</v>
+        <v>127.49</v>
       </c>
       <c r="K40" t="n">
-        <v>-83.06</v>
+        <v>-87.76000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>146.48</v>
+        <v>154.77</v>
       </c>
     </row>
     <row r="41">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-210.15</v>
+        <v>-218.24</v>
       </c>
       <c r="K42" t="n">
-        <v>-66.48</v>
+        <v>-69.04000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>220.42</v>
+        <v>228.9</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>92.70999999999999</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-167.28</v>
+        <v>-160.31</v>
       </c>
       <c r="L43" t="n">
-        <v>191.26</v>
+        <v>183.29</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>33.67</v>
+        <v>32.98</v>
       </c>
       <c r="K44" t="n">
-        <v>53.8</v>
+        <v>52.7</v>
       </c>
       <c r="L44" t="n">
-        <v>63.46</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-40.07</v>
+        <v>-41.61</v>
       </c>
       <c r="K45" t="n">
-        <v>56.88</v>
+        <v>59.07</v>
       </c>
       <c r="L45" t="n">
-        <v>69.58</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-41.78</v>
+        <v>-43.38</v>
       </c>
       <c r="K46" t="n">
-        <v>-42.53</v>
+        <v>-44.16</v>
       </c>
       <c r="L46" t="n">
-        <v>59.62</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>31.64</v>
+        <v>30.99</v>
       </c>
       <c r="K47" t="n">
-        <v>68.03</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>75.03</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>18.41</v>
+        <v>19.45</v>
       </c>
       <c r="K48" t="n">
-        <v>88.12</v>
+        <v>93.11</v>
       </c>
       <c r="L48" t="n">
-        <v>90.03</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>93.27</v>
+        <v>98.55</v>
       </c>
       <c r="K49" t="n">
-        <v>55.69</v>
+        <v>58.84</v>
       </c>
       <c r="L49" t="n">
-        <v>108.63</v>
+        <v>114.78</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>41.93</v>
+        <v>42.76</v>
       </c>
       <c r="K50" t="n">
-        <v>81.78</v>
+        <v>83.38</v>
       </c>
       <c r="L50" t="n">
-        <v>91.90000000000001</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-80.37</v>
+        <v>-86.31999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>61.37</v>
+        <v>65.91</v>
       </c>
       <c r="L51" t="n">
-        <v>101.12</v>
+        <v>108.61</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>143.8</v>
+        <v>149.33</v>
       </c>
       <c r="K52" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="L52" t="n">
-        <v>143.8</v>
+        <v>149.33</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>37.51</v>
+        <v>38.25</v>
       </c>
       <c r="K53" t="n">
-        <v>143.69</v>
+        <v>146.51</v>
       </c>
       <c r="L53" t="n">
-        <v>148.5</v>
+        <v>151.42</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>107.9</v>
+        <v>105.69</v>
       </c>
       <c r="K54" t="n">
-        <v>-38.48</v>
+        <v>-37.69</v>
       </c>
       <c r="L54" t="n">
-        <v>114.55</v>
+        <v>112.21</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>165.41</v>
+        <v>177.67</v>
       </c>
       <c r="K55" t="n">
-        <v>115.84</v>
+        <v>124.43</v>
       </c>
       <c r="L55" t="n">
-        <v>201.94</v>
+        <v>216.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>245.78</v>
+        <v>240.77</v>
       </c>
       <c r="K56" t="n">
-        <v>40.95</v>
+        <v>40.12</v>
       </c>
       <c r="L56" t="n">
-        <v>249.17</v>
+        <v>244.09</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>10.21</v>
+        <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>-250.13</v>
+        <v>-269.3</v>
       </c>
       <c r="L57" t="n">
-        <v>250.34</v>
+        <v>269.53</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-117.53</v>
+        <v>-112.64</v>
       </c>
       <c r="K58" t="n">
-        <v>-115.26</v>
+        <v>-110.46</v>
       </c>
       <c r="L58" t="n">
-        <v>164.62</v>
+        <v>157.76</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>20.01</v>
+        <v>20.4</v>
       </c>
       <c r="K59" t="n">
-        <v>52.2</v>
+        <v>53.23</v>
       </c>
       <c r="L59" t="n">
-        <v>55.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>31.27</v>
+        <v>33.59</v>
       </c>
       <c r="K60" t="n">
-        <v>48.98</v>
+        <v>52.61</v>
       </c>
       <c r="L60" t="n">
-        <v>58.11</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="61">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>87.83</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-40.77</v>
+        <v>-39.04</v>
       </c>
       <c r="L62" t="n">
-        <v>96.83</v>
+        <v>92.72</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>64.19</v>
+        <v>61.52</v>
       </c>
       <c r="K63" t="n">
-        <v>-23.87</v>
+        <v>-22.88</v>
       </c>
       <c r="L63" t="n">
-        <v>68.48999999999999</v>
+        <v>65.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-18.92</v>
+        <v>-18.12</v>
       </c>
       <c r="K64" t="n">
-        <v>63.3</v>
+        <v>60.61</v>
       </c>
       <c r="L64" t="n">
-        <v>66.06</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>78.69</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-91.27</v>
+        <v>-96.44</v>
       </c>
       <c r="L65" t="n">
-        <v>120.51</v>
+        <v>127.33</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>112.4</v>
+        <v>114.61</v>
       </c>
       <c r="K66" t="n">
         <v>-0.11</v>
       </c>
       <c r="L66" t="n">
-        <v>112.4</v>
+        <v>114.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-102.69</v>
+        <v>-110.29</v>
       </c>
       <c r="K67" t="n">
-        <v>47.16</v>
+        <v>50.65</v>
       </c>
       <c r="L67" t="n">
-        <v>113</v>
+        <v>121.37</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>81.69</v>
+        <v>78.28</v>
       </c>
       <c r="K68" t="n">
-        <v>-111.29</v>
+        <v>-106.65</v>
       </c>
       <c r="L68" t="n">
-        <v>138.05</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-76.43000000000001</v>
+        <v>-82.09</v>
       </c>
       <c r="K69" t="n">
-        <v>108.59</v>
+        <v>116.63</v>
       </c>
       <c r="L69" t="n">
-        <v>132.79</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-104.06</v>
+        <v>-99.73</v>
       </c>
       <c r="K70" t="n">
-        <v>-66.54000000000001</v>
+        <v>-63.77</v>
       </c>
       <c r="L70" t="n">
-        <v>123.52</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>151.94</v>
+        <v>148.84</v>
       </c>
       <c r="K71" t="n">
-        <v>-155.79</v>
+        <v>-152.61</v>
       </c>
       <c r="L71" t="n">
-        <v>217.62</v>
+        <v>213.18</v>
       </c>
     </row>
     <row r="72">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>160.59</v>
+        <v>163.74</v>
       </c>
       <c r="K73" t="n">
-        <v>-232.38</v>
+        <v>-236.94</v>
       </c>
       <c r="L73" t="n">
-        <v>282.47</v>
+        <v>288.01</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>31.04</v>
+        <v>32.22</v>
       </c>
       <c r="K74" t="n">
-        <v>65.84999999999999</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>72.8</v>
+        <v>75.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-74.45999999999999</v>
+        <v>-78.68000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-23.41</v>
+        <v>-24.74</v>
       </c>
       <c r="L75" t="n">
-        <v>78.06</v>
+        <v>82.47</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-81.87</v>
+        <v>-86.51000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-55.12</v>
+        <v>-58.24</v>
       </c>
       <c r="L76" t="n">
-        <v>98.7</v>
+        <v>104.28</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>82.62</v>
+        <v>87.3</v>
       </c>
       <c r="K77" t="n">
-        <v>69.72</v>
+        <v>73.67</v>
       </c>
       <c r="L77" t="n">
-        <v>108.11</v>
+        <v>114.23</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-28.61</v>
+        <v>-29.71</v>
       </c>
       <c r="K78" t="n">
-        <v>-65.23999999999999</v>
+        <v>-67.75</v>
       </c>
       <c r="L78" t="n">
-        <v>71.23999999999999</v>
+        <v>73.98</v>
       </c>
     </row>
     <row r="79">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-125.09</v>
+        <v>-119.76</v>
       </c>
       <c r="K80" t="n">
-        <v>-70.38</v>
+        <v>-67.39</v>
       </c>
       <c r="L80" t="n">
-        <v>143.53</v>
+        <v>137.42</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>32.39</v>
+        <v>33.03</v>
       </c>
       <c r="K81" t="n">
-        <v>-76.33</v>
+        <v>-77.81999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>82.91</v>
+        <v>84.54000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-182.86</v>
+        <v>-196.45</v>
       </c>
       <c r="K83" t="n">
-        <v>46.75</v>
+        <v>50.22</v>
       </c>
       <c r="L83" t="n">
-        <v>188.74</v>
+        <v>202.76</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>120.42</v>
+        <v>127.25</v>
       </c>
       <c r="K84" t="n">
-        <v>-119.54</v>
+        <v>-126.32</v>
       </c>
       <c r="L84" t="n">
-        <v>169.67</v>
+        <v>179.31</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>235.38</v>
+        <v>235.64</v>
       </c>
       <c r="K85" t="n">
-        <v>-94.73</v>
+        <v>-94.83</v>
       </c>
       <c r="L85" t="n">
-        <v>253.72</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>244.8</v>
+        <v>254.22</v>
       </c>
       <c r="K86" t="n">
-        <v>124.56</v>
+        <v>129.35</v>
       </c>
       <c r="L86" t="n">
-        <v>274.67</v>
+        <v>285.23</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-163.05</v>
+        <v>-169.32</v>
       </c>
       <c r="K87" t="n">
-        <v>235.05</v>
+        <v>244.09</v>
       </c>
       <c r="L87" t="n">
-        <v>286.06</v>
+        <v>297.06</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>96.89</v>
+        <v>100.61</v>
       </c>
       <c r="K88" t="n">
-        <v>-242.57</v>
+        <v>-251.9</v>
       </c>
       <c r="L88" t="n">
-        <v>261.2</v>
+        <v>271.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="F14" t="n">
-        <v>7.05</v>
+        <v>5.98</v>
       </c>
       <c r="G14" t="n">
-        <v>131.7</v>
+        <v>110.3</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>44.8</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-49.2</v>
+        <v>-32.79</v>
       </c>
       <c r="K14" t="n">
-        <v>33.49</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>59.51</v>
+        <v>33.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:23:41</t>
+          <t>06:23:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="F15" t="n">
-        <v>10.26</v>
+        <v>2.81</v>
       </c>
       <c r="G15" t="n">
-        <v>141.2</v>
+        <v>139.1</v>
       </c>
       <c r="H15" t="n">
-        <v>12.3</v>
+        <v>29.4</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-56.73</v>
+        <v>-26.33</v>
       </c>
       <c r="K15" t="n">
-        <v>-47.97</v>
+        <v>-18.75</v>
       </c>
       <c r="L15" t="n">
-        <v>74.29000000000001</v>
+        <v>32.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:26:14</t>
+          <t>06:25:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.69</v>
+        <v>2.11</v>
       </c>
       <c r="F16" t="n">
-        <v>5.67</v>
+        <v>9.68</v>
       </c>
       <c r="G16" t="n">
-        <v>132.4</v>
+        <v>126.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-21.84</v>
+        <v>18.21</v>
       </c>
       <c r="K16" t="n">
-        <v>47.32</v>
+        <v>-25.69</v>
       </c>
       <c r="L16" t="n">
-        <v>52.12</v>
+        <v>31.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:30:41</t>
+          <t>06:30:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="F17" t="n">
-        <v>7.37</v>
+        <v>7.05</v>
       </c>
       <c r="G17" t="n">
-        <v>127.7</v>
+        <v>123.7</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>35.7</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-67.7</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-84.54000000000001</v>
+        <v>-25.84</v>
       </c>
       <c r="L17" t="n">
-        <v>108.3</v>
+        <v>69.22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:32:21</t>
+          <t>06:31:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="F18" t="n">
-        <v>5.42</v>
+        <v>7.27</v>
       </c>
       <c r="G18" t="n">
-        <v>143.5</v>
+        <v>142.4</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-67.44</v>
+        <v>32.66</v>
       </c>
       <c r="K18" t="n">
-        <v>-27.04</v>
+        <v>19.63</v>
       </c>
       <c r="L18" t="n">
-        <v>72.66</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:34:16</t>
+          <t>06:33:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="F19" t="n">
-        <v>6.54</v>
+        <v>7.74</v>
       </c>
       <c r="G19" t="n">
-        <v>140.8</v>
+        <v>129.7</v>
       </c>
       <c r="H19" t="n">
-        <v>5.9</v>
+        <v>31.1</v>
       </c>
       <c r="I19" t="n">
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>51.69</v>
+        <v>32.83</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.89</v>
+        <v>116.89</v>
       </c>
       <c r="L19" t="n">
-        <v>52.02</v>
+        <v>121.41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:38:32</t>
+          <t>06:36:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>4.42</v>
+        <v>9.06</v>
       </c>
       <c r="G20" t="n">
-        <v>143.7</v>
+        <v>141.5</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>29.8</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-53.39</v>
+        <v>50.5</v>
       </c>
       <c r="K20" t="n">
-        <v>88.75</v>
+        <v>34.89</v>
       </c>
       <c r="L20" t="n">
-        <v>103.57</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:40:10</t>
+          <t>06:37:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.87</v>
+        <v>2.22</v>
       </c>
       <c r="F21" t="n">
-        <v>8.67</v>
+        <v>4.83</v>
       </c>
       <c r="G21" t="n">
-        <v>134.4</v>
+        <v>125</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-67.67</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-36.76</v>
+        <v>-35.12</v>
       </c>
       <c r="L21" t="n">
-        <v>77.01000000000001</v>
+        <v>84.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:40:59</t>
+          <t>06:38:50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="F22" t="n">
-        <v>8.359999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="G22" t="n">
-        <v>148.4</v>
+        <v>131.2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-25.15</v>
+        <v>38.36</v>
       </c>
       <c r="K22" t="n">
-        <v>127.72</v>
+        <v>-87.08</v>
       </c>
       <c r="L22" t="n">
-        <v>130.17</v>
+        <v>95.15000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:44:18</t>
+          <t>06:43:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="F23" t="n">
-        <v>3.65</v>
+        <v>8.94</v>
       </c>
       <c r="G23" t="n">
-        <v>134.8</v>
+        <v>119.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6</v>
+        <v>22.8</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-115.62</v>
+        <v>126.42</v>
       </c>
       <c r="K23" t="n">
-        <v>-78.09</v>
+        <v>28.66</v>
       </c>
       <c r="L23" t="n">
-        <v>139.52</v>
+        <v>129.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:46:10</t>
+          <t>06:44:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.74</v>
+        <v>2.35</v>
       </c>
       <c r="F24" t="n">
-        <v>7.88</v>
+        <v>6.3</v>
       </c>
       <c r="G24" t="n">
-        <v>132</v>
+        <v>137.8</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>114.55</v>
+        <v>48.02</v>
       </c>
       <c r="K24" t="n">
-        <v>-93.73</v>
+        <v>-107.03</v>
       </c>
       <c r="L24" t="n">
-        <v>148.01</v>
+        <v>117.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:48:06</t>
+          <t>06:46:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="F25" t="n">
-        <v>7.12</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>117</v>
+        <v>125.2</v>
       </c>
       <c r="H25" t="n">
-        <v>3.8</v>
+        <v>29.3</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>139.21</v>
+        <v>-171.53</v>
       </c>
       <c r="K25" t="n">
-        <v>46.47</v>
+        <v>-48.86</v>
       </c>
       <c r="L25" t="n">
-        <v>146.76</v>
+        <v>178.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:52:44</t>
+          <t>06:50:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.57</v>
+        <v>2.66</v>
       </c>
       <c r="F26" t="n">
-        <v>2.43</v>
+        <v>8.76</v>
       </c>
       <c r="G26" t="n">
-        <v>139.7</v>
+        <v>132.1</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>49.3</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-124.93</v>
+        <v>122.25</v>
       </c>
       <c r="K26" t="n">
-        <v>156.32</v>
+        <v>-164.05</v>
       </c>
       <c r="L26" t="n">
-        <v>200.11</v>
+        <v>204.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:55:10</t>
+          <t>06:51:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="F27" t="n">
-        <v>8.4</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>142.6</v>
+        <v>132.3</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>212.35</v>
+        <v>-66.06999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-15.52</v>
+        <v>177.8</v>
       </c>
       <c r="L27" t="n">
-        <v>212.92</v>
+        <v>189.68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:57:08</t>
+          <t>06:53:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.56</v>
+        <v>3.06</v>
       </c>
       <c r="F28" t="n">
-        <v>10.46</v>
+        <v>8.1</v>
       </c>
       <c r="G28" t="n">
-        <v>132.4</v>
+        <v>137.8</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>25.6</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>164.67</v>
+        <v>161.03</v>
       </c>
       <c r="K28" t="n">
-        <v>-255.26</v>
+        <v>112.42</v>
       </c>
       <c r="L28" t="n">
-        <v>303.77</v>
+        <v>196.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:09:00</t>
+          <t>07:03:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="F29" t="n">
-        <v>5.55</v>
+        <v>10.46</v>
       </c>
       <c r="G29" t="n">
-        <v>128.8</v>
+        <v>154.5</v>
       </c>
       <c r="H29" t="n">
-        <v>10.1</v>
+        <v>63.1</v>
       </c>
       <c r="I29" t="n">
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>70.63</v>
+        <v>5.23</v>
       </c>
       <c r="K29" t="n">
-        <v>24.95</v>
+        <v>30.7</v>
       </c>
       <c r="L29" t="n">
-        <v>74.91</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:10:37</t>
+          <t>07:05:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="F30" t="n">
-        <v>8.69</v>
+        <v>6.23</v>
       </c>
       <c r="G30" t="n">
-        <v>141</v>
+        <v>136.2</v>
       </c>
       <c r="H30" t="n">
-        <v>7.2</v>
+        <v>20.5</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-47.01</v>
+        <v>-17.47</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.29</v>
+        <v>-34.29</v>
       </c>
       <c r="L30" t="n">
-        <v>47.3</v>
+        <v>38.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:11:34</t>
+          <t>07:06:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.32</v>
+        <v>2.73</v>
       </c>
       <c r="F31" t="n">
-        <v>6.89</v>
+        <v>7.89</v>
       </c>
       <c r="G31" t="n">
-        <v>131.3</v>
+        <v>128.1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-52.94</v>
+        <v>14.1</v>
       </c>
       <c r="K31" t="n">
-        <v>1.18</v>
+        <v>-37.98</v>
       </c>
       <c r="L31" t="n">
-        <v>52.95</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:15:49</t>
+          <t>07:10:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="F32" t="n">
-        <v>10.46</v>
+        <v>3.23</v>
       </c>
       <c r="G32" t="n">
-        <v>124.3</v>
+        <v>137</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7</v>
+        <v>36.3</v>
       </c>
       <c r="I32" t="n">
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-12.61</v>
+        <v>-44.63</v>
       </c>
       <c r="K32" t="n">
-        <v>86.54000000000001</v>
+        <v>30.21</v>
       </c>
       <c r="L32" t="n">
-        <v>87.45</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:17:55</t>
+          <t>07:11:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="F33" t="n">
-        <v>7.87</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>125.7</v>
+        <v>124.3</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1</v>
+        <v>31.9</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>53.44</v>
+        <v>52.04</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.2</v>
+        <v>-28.67</v>
       </c>
       <c r="L33" t="n">
-        <v>60.42</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:20:19</t>
+          <t>07:13:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="F34" t="n">
-        <v>7.53</v>
+        <v>7.04</v>
       </c>
       <c r="G34" t="n">
-        <v>133.3</v>
+        <v>136</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>-77.52</v>
+        <v>41.88</v>
       </c>
       <c r="K34" t="n">
-        <v>-20.59</v>
+        <v>44.11</v>
       </c>
       <c r="L34" t="n">
-        <v>80.20999999999999</v>
+        <v>60.82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:24:00</t>
+          <t>07:18:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="F35" t="n">
-        <v>10.46</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>132.1</v>
+        <v>120</v>
       </c>
       <c r="H35" t="n">
-        <v>3.9</v>
+        <v>53.3</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-85.3</v>
+        <v>87.61</v>
       </c>
       <c r="K35" t="n">
-        <v>-81.31999999999999</v>
+        <v>-1.87</v>
       </c>
       <c r="L35" t="n">
-        <v>117.85</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:25:50</t>
+          <t>07:20:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="F36" t="n">
-        <v>7.75</v>
+        <v>9.56</v>
       </c>
       <c r="G36" t="n">
-        <v>128.1</v>
+        <v>149.5</v>
       </c>
       <c r="H36" t="n">
-        <v>1.7</v>
+        <v>62.7</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-32.91</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>109.42</v>
+        <v>-51.24</v>
       </c>
       <c r="L36" t="n">
-        <v>114.26</v>
+        <v>97.54000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:28:09</t>
+          <t>07:22:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="F37" t="n">
-        <v>9.06</v>
+        <v>7.66</v>
       </c>
       <c r="G37" t="n">
-        <v>139.8</v>
+        <v>130.9</v>
       </c>
       <c r="H37" t="n">
-        <v>1.9</v>
+        <v>45.3</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-71.59999999999999</v>
+        <v>-58.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-112.92</v>
+        <v>54.28</v>
       </c>
       <c r="L37" t="n">
-        <v>133.71</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:31:41</t>
+          <t>07:28:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="F38" t="n">
-        <v>9.449999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="G38" t="n">
-        <v>120.4</v>
+        <v>141.9</v>
       </c>
       <c r="H38" t="n">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-177.67</v>
+        <v>-2.39</v>
       </c>
       <c r="K38" t="n">
-        <v>-25.86</v>
+        <v>-106.28</v>
       </c>
       <c r="L38" t="n">
-        <v>179.55</v>
+        <v>106.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:32:57</t>
+          <t>07:30:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="F39" t="n">
-        <v>9.75</v>
+        <v>8.24</v>
       </c>
       <c r="G39" t="n">
-        <v>134.3</v>
+        <v>138</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>58.4</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>74.51000000000001</v>
+        <v>-63.07</v>
       </c>
       <c r="K39" t="n">
-        <v>122.76</v>
+        <v>-92.38</v>
       </c>
       <c r="L39" t="n">
-        <v>143.6</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:35:06</t>
+          <t>07:32:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.54</v>
+        <v>3.17</v>
       </c>
       <c r="F40" t="n">
-        <v>8.130000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="G40" t="n">
-        <v>149.4</v>
+        <v>124.8</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>127.49</v>
+        <v>23.77</v>
       </c>
       <c r="K40" t="n">
-        <v>-87.76000000000001</v>
+        <v>-129.01</v>
       </c>
       <c r="L40" t="n">
-        <v>154.77</v>
+        <v>131.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:40:55</t>
+          <t>07:37:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.25</v>
+        <v>3.33</v>
       </c>
       <c r="F41" t="n">
-        <v>5.12</v>
+        <v>10.46</v>
       </c>
       <c r="G41" t="n">
-        <v>131.9</v>
+        <v>130.9</v>
       </c>
       <c r="H41" t="n">
-        <v>3.3</v>
+        <v>45.9</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>15.38</v>
+        <v>113.37</v>
       </c>
       <c r="K41" t="n">
-        <v>-173.95</v>
+        <v>152.32</v>
       </c>
       <c r="L41" t="n">
-        <v>174.63</v>
+        <v>189.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:42:43</t>
+          <t>07:39:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="F42" t="n">
-        <v>9.58</v>
+        <v>10.46</v>
       </c>
       <c r="G42" t="n">
-        <v>148.2</v>
+        <v>124.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-218.24</v>
+        <v>127.32</v>
       </c>
       <c r="K42" t="n">
-        <v>-69.04000000000001</v>
+        <v>-126.69</v>
       </c>
       <c r="L42" t="n">
-        <v>228.9</v>
+        <v>179.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:44:20</t>
+          <t>07:40:59</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="F43" t="n">
-        <v>9.9</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>135.2</v>
+        <v>131.9</v>
       </c>
       <c r="H43" t="n">
-        <v>3.5</v>
+        <v>21.1</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>88.84999999999999</v>
+        <v>183.31</v>
       </c>
       <c r="K43" t="n">
-        <v>-160.31</v>
+        <v>-47.15</v>
       </c>
       <c r="L43" t="n">
-        <v>183.29</v>
+        <v>189.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:56:50</t>
+          <t>07:48:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="F44" t="n">
-        <v>9.19</v>
+        <v>10.46</v>
       </c>
       <c r="G44" t="n">
-        <v>136.1</v>
+        <v>119.4</v>
       </c>
       <c r="H44" t="n">
-        <v>5.9</v>
+        <v>29.4</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>32.98</v>
+        <v>4.42</v>
       </c>
       <c r="K44" t="n">
-        <v>52.7</v>
+        <v>51.46</v>
       </c>
       <c r="L44" t="n">
-        <v>62.17</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:59:16</t>
+          <t>07:50:03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="F45" t="n">
-        <v>9.83</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>135.4</v>
+        <v>132.2</v>
       </c>
       <c r="H45" t="n">
-        <v>5.4</v>
+        <v>31.4</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>-41.61</v>
+        <v>47.35</v>
       </c>
       <c r="K45" t="n">
-        <v>59.07</v>
+        <v>18.38</v>
       </c>
       <c r="L45" t="n">
-        <v>72.25</v>
+        <v>50.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:01:09</t>
+          <t>07:52:04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="F46" t="n">
-        <v>8.77</v>
+        <v>6.71</v>
       </c>
       <c r="G46" t="n">
-        <v>122.1</v>
+        <v>130.3</v>
       </c>
       <c r="H46" t="n">
-        <v>3.3</v>
+        <v>23</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-43.38</v>
+        <v>31.38</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.16</v>
+        <v>-27.44</v>
       </c>
       <c r="L46" t="n">
-        <v>61.91</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:07:00</t>
+          <t>07:56:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.03</v>
+        <v>2.51</v>
       </c>
       <c r="F47" t="n">
-        <v>10.46</v>
+        <v>7.94</v>
       </c>
       <c r="G47" t="n">
-        <v>142.2</v>
+        <v>132.7</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>68.7</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>30.99</v>
+        <v>37.41</v>
       </c>
       <c r="K47" t="n">
-        <v>66.65000000000001</v>
+        <v>-38.92</v>
       </c>
       <c r="L47" t="n">
-        <v>73.5</v>
+        <v>53.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:08:16</t>
+          <t>07:58:04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="F48" t="n">
         <v>10.46</v>
       </c>
       <c r="G48" t="n">
-        <v>128.6</v>
+        <v>142.8</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>19.45</v>
+        <v>41.46</v>
       </c>
       <c r="K48" t="n">
-        <v>93.11</v>
+        <v>-53.67</v>
       </c>
       <c r="L48" t="n">
-        <v>95.12</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:09:31</t>
+          <t>07:59:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.95</v>
+        <v>2.46</v>
       </c>
       <c r="F49" t="n">
-        <v>10.46</v>
+        <v>5.27</v>
       </c>
       <c r="G49" t="n">
-        <v>139.4</v>
+        <v>123.1</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>98.55</v>
+        <v>33.26</v>
       </c>
       <c r="K49" t="n">
-        <v>58.84</v>
+        <v>49.18</v>
       </c>
       <c r="L49" t="n">
-        <v>114.78</v>
+        <v>59.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:14:10</t>
+          <t>08:05:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="F50" t="n">
-        <v>10.46</v>
+        <v>9.85</v>
       </c>
       <c r="G50" t="n">
-        <v>133.2</v>
+        <v>129.9</v>
       </c>
       <c r="H50" t="n">
-        <v>5.5</v>
+        <v>52.3</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>42.76</v>
+        <v>-42.46</v>
       </c>
       <c r="K50" t="n">
-        <v>83.38</v>
+        <v>95.59</v>
       </c>
       <c r="L50" t="n">
-        <v>93.7</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:16:10</t>
+          <t>08:08:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.52</v>
+        <v>2.29</v>
       </c>
       <c r="F51" t="n">
-        <v>7.86</v>
+        <v>7.2</v>
       </c>
       <c r="G51" t="n">
-        <v>119.9</v>
+        <v>124.8</v>
       </c>
       <c r="H51" t="n">
-        <v>2.8</v>
+        <v>45</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-86.31999999999999</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>65.91</v>
+        <v>-20.71</v>
       </c>
       <c r="L51" t="n">
-        <v>108.61</v>
+        <v>79.84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:17:22</t>
+          <t>08:09:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="F52" t="n">
-        <v>8.359999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="G52" t="n">
-        <v>138.3</v>
+        <v>130.6</v>
       </c>
       <c r="H52" t="n">
-        <v>7.7</v>
+        <v>35.3</v>
       </c>
       <c r="I52" t="n">
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>149.33</v>
+        <v>-65.34999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>0.75</v>
+        <v>71.97</v>
       </c>
       <c r="L52" t="n">
-        <v>149.33</v>
+        <v>97.20999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:22:16</t>
+          <t>08:15:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="F53" t="n">
-        <v>9.65</v>
+        <v>9.34</v>
       </c>
       <c r="G53" t="n">
-        <v>137.5</v>
+        <v>127.1</v>
       </c>
       <c r="H53" t="n">
-        <v>1.1</v>
+        <v>23.7</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>38.25</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>146.51</v>
+        <v>74.5</v>
       </c>
       <c r="L53" t="n">
-        <v>151.42</v>
+        <v>116.46</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:24:11</t>
+          <t>08:17:05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="F54" t="n">
-        <v>6.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>121.2</v>
+        <v>135.8</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>105.69</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-37.69</v>
+        <v>78.36</v>
       </c>
       <c r="L54" t="n">
-        <v>112.21</v>
+        <v>107.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:26:05</t>
+          <t>08:19:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.32</v>
+        <v>2.47</v>
       </c>
       <c r="F55" t="n">
-        <v>10.46</v>
+        <v>6.92</v>
       </c>
       <c r="G55" t="n">
-        <v>150.9</v>
+        <v>141.3</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9</v>
+        <v>43.7</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>177.67</v>
+        <v>48.58</v>
       </c>
       <c r="K55" t="n">
-        <v>124.43</v>
+        <v>165.19</v>
       </c>
       <c r="L55" t="n">
-        <v>216.91</v>
+        <v>172.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:30:32</t>
+          <t>08:22:32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.83</v>
+        <v>3.99</v>
       </c>
       <c r="F56" t="n">
-        <v>9.32</v>
+        <v>10.46</v>
       </c>
       <c r="G56" t="n">
-        <v>130.8</v>
+        <v>124.5</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>55.2</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>240.77</v>
+        <v>232.55</v>
       </c>
       <c r="K56" t="n">
-        <v>40.12</v>
+        <v>-158.35</v>
       </c>
       <c r="L56" t="n">
-        <v>244.09</v>
+        <v>281.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:32:54</t>
+          <t>08:23:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.53</v>
+        <v>2.76</v>
       </c>
       <c r="F57" t="n">
-        <v>9.51</v>
+        <v>10.46</v>
       </c>
       <c r="G57" t="n">
-        <v>130.4</v>
+        <v>138.4</v>
       </c>
       <c r="H57" t="n">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>11</v>
+        <v>-101.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-269.3</v>
+        <v>151.88</v>
       </c>
       <c r="L57" t="n">
-        <v>269.53</v>
+        <v>182.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:33:45</t>
+          <t>08:24:52</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.43</v>
+        <v>2.84</v>
       </c>
       <c r="F58" t="n">
-        <v>7.52</v>
+        <v>10.44</v>
       </c>
       <c r="G58" t="n">
-        <v>130.6</v>
+        <v>134.6</v>
       </c>
       <c r="H58" t="n">
-        <v>2.2</v>
+        <v>59.1</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>-112.64</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>-110.46</v>
+        <v>-115.77</v>
       </c>
       <c r="L58" t="n">
-        <v>157.76</v>
+        <v>149.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:44:29</t>
+          <t>08:33:51</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="F59" t="n">
         <v>10.46</v>
       </c>
       <c r="G59" t="n">
-        <v>135.1</v>
+        <v>129.1</v>
       </c>
       <c r="H59" t="n">
-        <v>5.5</v>
+        <v>20.5</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>20.4</v>
+        <v>42.2</v>
       </c>
       <c r="K59" t="n">
-        <v>53.23</v>
+        <v>2.99</v>
       </c>
       <c r="L59" t="n">
-        <v>57</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:45:45</t>
+          <t>08:35:20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="F60" t="n">
-        <v>8.09</v>
+        <v>6.98</v>
       </c>
       <c r="G60" t="n">
-        <v>115.9</v>
+        <v>130.4</v>
       </c>
       <c r="H60" t="n">
-        <v>9.5</v>
+        <v>57.2</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>33.59</v>
+        <v>-33.74</v>
       </c>
       <c r="K60" t="n">
-        <v>52.61</v>
+        <v>-5.95</v>
       </c>
       <c r="L60" t="n">
-        <v>62.42</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:48:16</t>
+          <t>08:37:14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="F61" t="n">
-        <v>8.890000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>132.3</v>
+        <v>127</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>67.45999999999999</v>
+        <v>-4.19</v>
       </c>
       <c r="K61" t="n">
-        <v>37.9</v>
+        <v>-46.93</v>
       </c>
       <c r="L61" t="n">
-        <v>77.38</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:54:20</t>
+          <t>08:42:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.42</v>
+        <v>2.89</v>
       </c>
       <c r="F62" t="n">
-        <v>10.46</v>
+        <v>7.5</v>
       </c>
       <c r="G62" t="n">
-        <v>109.9</v>
+        <v>134.2</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>84.09999999999999</v>
+        <v>-12.74</v>
       </c>
       <c r="K62" t="n">
-        <v>-39.04</v>
+        <v>-70.39</v>
       </c>
       <c r="L62" t="n">
-        <v>92.72</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:55:33</t>
+          <t>08:44:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="F63" t="n">
-        <v>10.43</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>120.5</v>
+        <v>145.7</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>61.52</v>
+        <v>17.87</v>
       </c>
       <c r="K63" t="n">
-        <v>-22.88</v>
+        <v>-59.22</v>
       </c>
       <c r="L63" t="n">
-        <v>65.63</v>
+        <v>61.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:57:59</t>
+          <t>08:45:08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="F64" t="n">
-        <v>10.46</v>
+        <v>10.05</v>
       </c>
       <c r="G64" t="n">
-        <v>136.2</v>
+        <v>142.7</v>
       </c>
       <c r="H64" t="n">
-        <v>1.2</v>
+        <v>11.1</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-18.12</v>
+        <v>-41.54</v>
       </c>
       <c r="K64" t="n">
-        <v>60.61</v>
+        <v>-44.68</v>
       </c>
       <c r="L64" t="n">
-        <v>63.26</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:03:16</t>
+          <t>08:49:13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="F65" t="n">
-        <v>10.46</v>
+        <v>8.5</v>
       </c>
       <c r="G65" t="n">
-        <v>123.4</v>
+        <v>128.6</v>
       </c>
       <c r="H65" t="n">
-        <v>4.8</v>
+        <v>40.5</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>83.15000000000001</v>
+        <v>40.42</v>
       </c>
       <c r="K65" t="n">
-        <v>-96.44</v>
+        <v>-80.42</v>
       </c>
       <c r="L65" t="n">
-        <v>127.33</v>
+        <v>90.01000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:05:44</t>
+          <t>08:51:35</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="F66" t="n">
-        <v>9.66</v>
+        <v>10.37</v>
       </c>
       <c r="G66" t="n">
-        <v>124.6</v>
+        <v>136.5</v>
       </c>
       <c r="H66" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>114.61</v>
+        <v>39.27</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.11</v>
+        <v>-53.93</v>
       </c>
       <c r="L66" t="n">
-        <v>114.61</v>
+        <v>66.70999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:06:46</t>
+          <t>08:53:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.49</v>
+        <v>3.04</v>
       </c>
       <c r="F67" t="n">
-        <v>7.77</v>
+        <v>8.56</v>
       </c>
       <c r="G67" t="n">
-        <v>138.5</v>
+        <v>136.9</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>43.4</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-110.29</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>50.65</v>
+        <v>-21.25</v>
       </c>
       <c r="L67" t="n">
-        <v>121.37</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:12:02</t>
+          <t>08:58:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.16</v>
+        <v>3.33</v>
       </c>
       <c r="F68" t="n">
         <v>10.46</v>
       </c>
       <c r="G68" t="n">
-        <v>142.1</v>
+        <v>125.8</v>
       </c>
       <c r="H68" t="n">
-        <v>9.699999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>78.28</v>
+        <v>139.85</v>
       </c>
       <c r="K68" t="n">
-        <v>-106.65</v>
+        <v>75.45</v>
       </c>
       <c r="L68" t="n">
-        <v>132.3</v>
+        <v>158.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:13:02</t>
+          <t>08:59:36</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="F69" t="n">
-        <v>7.59</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>133.2</v>
+        <v>140.2</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="I69" t="n">
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-82.09</v>
+        <v>44.82</v>
       </c>
       <c r="K69" t="n">
-        <v>116.63</v>
+        <v>-129.48</v>
       </c>
       <c r="L69" t="n">
-        <v>142.62</v>
+        <v>137.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:13:53</t>
+          <t>09:01:28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="F70" t="n">
         <v>10.46</v>
       </c>
       <c r="G70" t="n">
-        <v>124.9</v>
+        <v>132</v>
       </c>
       <c r="H70" t="n">
-        <v>5.2</v>
+        <v>45.6</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-99.73</v>
+        <v>88.86</v>
       </c>
       <c r="K70" t="n">
-        <v>-63.77</v>
+        <v>101.54</v>
       </c>
       <c r="L70" t="n">
-        <v>118.37</v>
+        <v>134.93</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:18:21</t>
+          <t>09:05:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="F71" t="n">
         <v>10.46</v>
       </c>
       <c r="G71" t="n">
-        <v>134.4</v>
+        <v>124.4</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>148.84</v>
+        <v>182.63</v>
       </c>
       <c r="K71" t="n">
-        <v>-152.61</v>
+        <v>-132.27</v>
       </c>
       <c r="L71" t="n">
-        <v>213.18</v>
+        <v>225.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:20:10</t>
+          <t>09:07:34</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.21</v>
+        <v>2.65</v>
       </c>
       <c r="F72" t="n">
-        <v>10.27</v>
+        <v>10.17</v>
       </c>
       <c r="G72" t="n">
-        <v>121.2</v>
+        <v>126.5</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4</v>
+        <v>24.9</v>
       </c>
       <c r="I72" t="n">
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>70.64</v>
+        <v>23.34</v>
       </c>
       <c r="K72" t="n">
-        <v>-254.78</v>
+        <v>-192.82</v>
       </c>
       <c r="L72" t="n">
-        <v>264.39</v>
+        <v>194.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:21:46</t>
+          <t>09:10:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3109,28 +3109,28 @@
         <v>10.46</v>
       </c>
       <c r="G73" t="n">
-        <v>133.2</v>
+        <v>123.3</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>17.3</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>163.74</v>
+        <v>-51.17</v>
       </c>
       <c r="K73" t="n">
-        <v>-236.94</v>
+        <v>-125.79</v>
       </c>
       <c r="L73" t="n">
-        <v>288.01</v>
+        <v>135.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:31:22</t>
+          <t>09:21:50</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="F74" t="n">
         <v>10.46</v>
       </c>
       <c r="G74" t="n">
-        <v>106.5</v>
+        <v>139.2</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>33.7</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>32.22</v>
+        <v>20.09</v>
       </c>
       <c r="K74" t="n">
-        <v>68.34999999999999</v>
+        <v>24.38</v>
       </c>
       <c r="L74" t="n">
-        <v>75.56</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:32:25</t>
+          <t>09:24:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.18</v>
+        <v>3.03</v>
       </c>
       <c r="F75" t="n">
         <v>10.46</v>
       </c>
       <c r="G75" t="n">
-        <v>148.8</v>
+        <v>136</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-78.68000000000001</v>
+        <v>-42.01</v>
       </c>
       <c r="K75" t="n">
-        <v>-24.74</v>
+        <v>23.6</v>
       </c>
       <c r="L75" t="n">
-        <v>82.47</v>
+        <v>48.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:34:38</t>
+          <t>09:26:21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="F76" t="n">
-        <v>10.46</v>
+        <v>4.46</v>
       </c>
       <c r="G76" t="n">
-        <v>131.2</v>
+        <v>148.2</v>
       </c>
       <c r="H76" t="n">
-        <v>1.4</v>
+        <v>49.6</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-86.51000000000001</v>
+        <v>7.21</v>
       </c>
       <c r="K76" t="n">
-        <v>-58.24</v>
+        <v>-34.73</v>
       </c>
       <c r="L76" t="n">
-        <v>104.28</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:40:24</t>
+          <t>09:32:15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="F77" t="n">
-        <v>9.619999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="G77" t="n">
-        <v>120.7</v>
+        <v>139.9</v>
       </c>
       <c r="H77" t="n">
-        <v>1.2</v>
+        <v>46.5</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>87.3</v>
+        <v>43.52</v>
       </c>
       <c r="K77" t="n">
-        <v>73.67</v>
+        <v>57.06</v>
       </c>
       <c r="L77" t="n">
-        <v>114.23</v>
+        <v>71.76000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:41:39</t>
+          <t>09:33:41</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="F78" t="n">
-        <v>10.46</v>
+        <v>8.99</v>
       </c>
       <c r="G78" t="n">
-        <v>131.5</v>
+        <v>119.3</v>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>47.5</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-29.71</v>
+        <v>63.45</v>
       </c>
       <c r="K78" t="n">
-        <v>-67.75</v>
+        <v>-27.3</v>
       </c>
       <c r="L78" t="n">
-        <v>73.98</v>
+        <v>69.06999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:42:52</t>
+          <t>09:35:31</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="F79" t="n">
-        <v>10.46</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>134.4</v>
+        <v>133.4</v>
       </c>
       <c r="H79" t="n">
-        <v>2.9</v>
+        <v>41</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>59.57</v>
+        <v>32.06</v>
       </c>
       <c r="K79" t="n">
-        <v>51.04</v>
+        <v>38.4</v>
       </c>
       <c r="L79" t="n">
-        <v>78.45</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:47:54</t>
+          <t>09:39:49</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.78</v>
+        <v>3.02</v>
       </c>
       <c r="F80" t="n">
-        <v>10.46</v>
+        <v>9.9</v>
       </c>
       <c r="G80" t="n">
-        <v>134.9</v>
+        <v>133.3</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-119.76</v>
+        <v>-79.34999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-67.39</v>
+        <v>-54.56</v>
       </c>
       <c r="L80" t="n">
-        <v>137.42</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:50:33</t>
+          <t>09:42:20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="F81" t="n">
-        <v>7.43</v>
+        <v>10.46</v>
       </c>
       <c r="G81" t="n">
-        <v>135.6</v>
+        <v>134.4</v>
       </c>
       <c r="H81" t="n">
-        <v>3.5</v>
+        <v>29.7</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J81" t="n">
-        <v>33.03</v>
+        <v>-13.5</v>
       </c>
       <c r="K81" t="n">
-        <v>-77.81999999999999</v>
+        <v>107.9</v>
       </c>
       <c r="L81" t="n">
-        <v>84.54000000000001</v>
+        <v>108.74</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:51:45</t>
+          <t>09:44:13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.63</v>
+        <v>3.17</v>
       </c>
       <c r="F82" t="n">
         <v>10.46</v>
       </c>
       <c r="G82" t="n">
-        <v>133.4</v>
+        <v>115.3</v>
       </c>
       <c r="H82" t="n">
-        <v>4.5</v>
+        <v>29.1</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>116.63</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-3.01</v>
+        <v>-43.78</v>
       </c>
       <c r="L82" t="n">
-        <v>116.67</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:56:35</t>
+          <t>09:48:28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.42</v>
+        <v>2.67</v>
       </c>
       <c r="F83" t="n">
-        <v>10.46</v>
+        <v>6.02</v>
       </c>
       <c r="G83" t="n">
-        <v>123.2</v>
+        <v>143.5</v>
       </c>
       <c r="H83" t="n">
-        <v>4.7</v>
+        <v>28.4</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-196.45</v>
+        <v>102.49</v>
       </c>
       <c r="K83" t="n">
-        <v>50.22</v>
+        <v>20.05</v>
       </c>
       <c r="L83" t="n">
-        <v>202.76</v>
+        <v>104.43</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:58:12</t>
+          <t>09:50:52</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="F84" t="n">
         <v>10.46</v>
       </c>
       <c r="G84" t="n">
-        <v>136.9</v>
+        <v>137.4</v>
       </c>
       <c r="H84" t="n">
-        <v>4.9</v>
+        <v>21.5</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>127.25</v>
+        <v>-12.93</v>
       </c>
       <c r="K84" t="n">
-        <v>-126.32</v>
+        <v>-146.49</v>
       </c>
       <c r="L84" t="n">
-        <v>179.31</v>
+        <v>147.06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:00:01</t>
+          <t>09:52:19</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="F85" t="n">
         <v>10.46</v>
       </c>
       <c r="G85" t="n">
-        <v>138.5</v>
+        <v>123</v>
       </c>
       <c r="H85" t="n">
-        <v>2.4</v>
+        <v>63.8</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>235.64</v>
+        <v>-115.38</v>
       </c>
       <c r="K85" t="n">
-        <v>-94.83</v>
+        <v>99.67</v>
       </c>
       <c r="L85" t="n">
-        <v>254</v>
+        <v>152.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:04:21</t>
+          <t>09:57:48</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.16</v>
+        <v>3.49</v>
       </c>
       <c r="F86" t="n">
-        <v>10.46</v>
+        <v>7.8</v>
       </c>
       <c r="G86" t="n">
-        <v>139.9</v>
+        <v>118.4</v>
       </c>
       <c r="H86" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>254.22</v>
+        <v>52.67</v>
       </c>
       <c r="K86" t="n">
-        <v>129.35</v>
+        <v>130.1</v>
       </c>
       <c r="L86" t="n">
-        <v>285.23</v>
+        <v>140.35</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:05:25</t>
+          <t>09:59:35</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3694,31 +3694,31 @@
         <v>2.79</v>
       </c>
       <c r="F87" t="n">
-        <v>6.8</v>
+        <v>9.35</v>
       </c>
       <c r="G87" t="n">
-        <v>142.1</v>
+        <v>134.1</v>
       </c>
       <c r="H87" t="n">
-        <v>2.4</v>
+        <v>40.8</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-169.32</v>
+        <v>68.5</v>
       </c>
       <c r="K87" t="n">
-        <v>244.09</v>
+        <v>176.34</v>
       </c>
       <c r="L87" t="n">
-        <v>297.06</v>
+        <v>189.18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:07:21</t>
+          <t>10:01:04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="F88" t="n">
         <v>10.46</v>
       </c>
       <c r="G88" t="n">
-        <v>129.7</v>
+        <v>139.8</v>
       </c>
       <c r="H88" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>100.61</v>
+        <v>-187.48</v>
       </c>
       <c r="K88" t="n">
-        <v>-251.9</v>
+        <v>16.49</v>
       </c>
       <c r="L88" t="n">
-        <v>271.25</v>
+        <v>188.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="F14" t="n">
-        <v>5.98</v>
+        <v>6.24</v>
       </c>
       <c r="G14" t="n">
-        <v>110.3</v>
+        <v>127.7</v>
       </c>
       <c r="H14" t="n">
-        <v>44.8</v>
+        <v>41.5</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-32.79</v>
+        <v>60.93</v>
       </c>
       <c r="K14" t="n">
-        <v>8.449999999999999</v>
+        <v>-37.59</v>
       </c>
       <c r="L14" t="n">
-        <v>33.86</v>
+        <v>71.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:23:38</t>
+          <t>06:22:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="F15" t="n">
-        <v>2.81</v>
+        <v>8.26</v>
       </c>
       <c r="G15" t="n">
-        <v>139.1</v>
+        <v>124.3</v>
       </c>
       <c r="H15" t="n">
-        <v>29.4</v>
+        <v>60.5</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>-26.33</v>
+        <v>31.82</v>
       </c>
       <c r="K15" t="n">
-        <v>-18.75</v>
+        <v>10.11</v>
       </c>
       <c r="L15" t="n">
-        <v>32.33</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:25:01</t>
+          <t>06:25:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.11</v>
+        <v>2.77</v>
       </c>
       <c r="F16" t="n">
-        <v>9.68</v>
+        <v>8.6</v>
       </c>
       <c r="G16" t="n">
-        <v>126.9</v>
+        <v>132</v>
       </c>
       <c r="H16" t="n">
-        <v>71.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>18.21</v>
+        <v>34.68</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.69</v>
+        <v>29.52</v>
       </c>
       <c r="L16" t="n">
-        <v>31.49</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:30:25</t>
+          <t>06:28:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="F17" t="n">
-        <v>7.05</v>
+        <v>10.2</v>
       </c>
       <c r="G17" t="n">
-        <v>123.7</v>
+        <v>142.4</v>
       </c>
       <c r="H17" t="n">
-        <v>35.7</v>
+        <v>32</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
-        <v>64.20999999999999</v>
+        <v>-47.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-25.84</v>
+        <v>-89.28</v>
       </c>
       <c r="L17" t="n">
-        <v>69.22</v>
+        <v>101.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:31:47</t>
+          <t>06:31:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="F18" t="n">
-        <v>7.27</v>
+        <v>8.18</v>
       </c>
       <c r="G18" t="n">
-        <v>142.4</v>
+        <v>140.4</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>32.8</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J18" t="n">
-        <v>32.66</v>
+        <v>20.88</v>
       </c>
       <c r="K18" t="n">
-        <v>19.63</v>
+        <v>60.34</v>
       </c>
       <c r="L18" t="n">
-        <v>38.1</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:33:04</t>
+          <t>06:33:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="F19" t="n">
-        <v>7.74</v>
+        <v>7.47</v>
       </c>
       <c r="G19" t="n">
-        <v>129.7</v>
+        <v>123</v>
       </c>
       <c r="H19" t="n">
-        <v>31.1</v>
+        <v>75.3</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>32.83</v>
+        <v>-50.87</v>
       </c>
       <c r="K19" t="n">
-        <v>116.89</v>
+        <v>56.85</v>
       </c>
       <c r="L19" t="n">
-        <v>121.41</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:36:25</t>
+          <t>06:37:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="F20" t="n">
-        <v>9.06</v>
+        <v>7.31</v>
       </c>
       <c r="G20" t="n">
-        <v>141.5</v>
+        <v>133</v>
       </c>
       <c r="H20" t="n">
-        <v>29.8</v>
+        <v>17.4</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>50.5</v>
+        <v>88.05</v>
       </c>
       <c r="K20" t="n">
-        <v>34.89</v>
+        <v>-63.69</v>
       </c>
       <c r="L20" t="n">
-        <v>61.38</v>
+        <v>108.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:37:18</t>
+          <t>06:38:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="F21" t="n">
         <v>4.83</v>
       </c>
       <c r="G21" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="H21" t="n">
-        <v>8.800000000000001</v>
+        <v>48.6</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J21" t="n">
-        <v>76.51000000000001</v>
+        <v>-86.48</v>
       </c>
       <c r="K21" t="n">
-        <v>-35.12</v>
+        <v>-66.47</v>
       </c>
       <c r="L21" t="n">
-        <v>84.19</v>
+        <v>109.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:38:50</t>
+          <t>06:40:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="F22" t="n">
-        <v>7.86</v>
+        <v>8.17</v>
       </c>
       <c r="G22" t="n">
-        <v>131.2</v>
+        <v>126.6</v>
       </c>
       <c r="H22" t="n">
-        <v>32.3</v>
+        <v>51.6</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>38.36</v>
+        <v>-6.3</v>
       </c>
       <c r="K22" t="n">
-        <v>-87.08</v>
+        <v>-83.09</v>
       </c>
       <c r="L22" t="n">
-        <v>95.15000000000001</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:43:51</t>
+          <t>06:45:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="F23" t="n">
-        <v>8.94</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>119.5</v>
+        <v>117.9</v>
       </c>
       <c r="H23" t="n">
-        <v>22.8</v>
+        <v>16.2</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>126.42</v>
+        <v>179.21</v>
       </c>
       <c r="K23" t="n">
-        <v>28.66</v>
+        <v>30.78</v>
       </c>
       <c r="L23" t="n">
-        <v>129.63</v>
+        <v>181.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:44:53</t>
+          <t>06:47:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="F24" t="n">
-        <v>6.3</v>
+        <v>10.46</v>
       </c>
       <c r="G24" t="n">
-        <v>137.8</v>
+        <v>114.3</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3</v>
+        <v>13.4</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>48.02</v>
+        <v>194.36</v>
       </c>
       <c r="K24" t="n">
-        <v>-107.03</v>
+        <v>-7.49</v>
       </c>
       <c r="L24" t="n">
-        <v>117.31</v>
+        <v>194.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:46:40</t>
+          <t>06:49:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="F25" t="n">
-        <v>9.619999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="G25" t="n">
-        <v>125.2</v>
+        <v>124.5</v>
       </c>
       <c r="H25" t="n">
-        <v>29.3</v>
+        <v>52</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-171.53</v>
+        <v>-74.98999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-48.86</v>
+        <v>158.18</v>
       </c>
       <c r="L25" t="n">
-        <v>178.36</v>
+        <v>175.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:50:17</t>
+          <t>06:54:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="F26" t="n">
-        <v>8.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>132.1</v>
+        <v>131.2</v>
       </c>
       <c r="H26" t="n">
-        <v>49.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>122.25</v>
+        <v>142.09</v>
       </c>
       <c r="K26" t="n">
-        <v>-164.05</v>
+        <v>176.17</v>
       </c>
       <c r="L26" t="n">
-        <v>204.6</v>
+        <v>226.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:51:38</t>
+          <t>06:56:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="F27" t="n">
-        <v>8.890000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="G27" t="n">
-        <v>132.3</v>
+        <v>123.7</v>
       </c>
       <c r="H27" t="n">
-        <v>93.09999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-66.06999999999999</v>
+        <v>-40.29</v>
       </c>
       <c r="K27" t="n">
-        <v>177.8</v>
+        <v>-161.49</v>
       </c>
       <c r="L27" t="n">
-        <v>189.68</v>
+        <v>166.44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:53:00</t>
+          <t>06:57:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.06</v>
+        <v>2.69</v>
       </c>
       <c r="F28" t="n">
-        <v>8.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>137.8</v>
+        <v>128.1</v>
       </c>
       <c r="H28" t="n">
-        <v>25.6</v>
+        <v>44.2</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>161.03</v>
+        <v>-137.92</v>
       </c>
       <c r="K28" t="n">
-        <v>112.42</v>
+        <v>41.33</v>
       </c>
       <c r="L28" t="n">
-        <v>196.39</v>
+        <v>143.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:03:12</t>
+          <t>07:06:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.51</v>
+        <v>1.83</v>
       </c>
       <c r="F29" t="n">
-        <v>10.46</v>
+        <v>6.96</v>
       </c>
       <c r="G29" t="n">
-        <v>154.5</v>
+        <v>130.9</v>
       </c>
       <c r="H29" t="n">
-        <v>63.1</v>
+        <v>20.8</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>5.23</v>
+        <v>-7.84</v>
       </c>
       <c r="K29" t="n">
-        <v>30.7</v>
+        <v>25.54</v>
       </c>
       <c r="L29" t="n">
-        <v>31.15</v>
+        <v>26.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:05:18</t>
+          <t>07:07:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="F30" t="n">
-        <v>6.23</v>
+        <v>9.93</v>
       </c>
       <c r="G30" t="n">
-        <v>136.2</v>
+        <v>131.7</v>
       </c>
       <c r="H30" t="n">
-        <v>20.5</v>
+        <v>35.4</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.47</v>
+        <v>41.33</v>
       </c>
       <c r="K30" t="n">
-        <v>-34.29</v>
+        <v>-4.42</v>
       </c>
       <c r="L30" t="n">
-        <v>38.48</v>
+        <v>41.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:06:43</t>
+          <t>07:10:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="F31" t="n">
-        <v>7.89</v>
+        <v>6.73</v>
       </c>
       <c r="G31" t="n">
-        <v>128.1</v>
+        <v>123.3</v>
       </c>
       <c r="H31" t="n">
-        <v>27</v>
+        <v>36.8</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>14.1</v>
+        <v>17.95</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.98</v>
+        <v>-8.08</v>
       </c>
       <c r="L31" t="n">
-        <v>40.51</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:10:01</t>
+          <t>07:14:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="F32" t="n">
-        <v>3.23</v>
+        <v>10.46</v>
       </c>
       <c r="G32" t="n">
-        <v>137</v>
+        <v>122.2</v>
       </c>
       <c r="H32" t="n">
-        <v>36.3</v>
+        <v>30.9</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-44.63</v>
+        <v>39.3</v>
       </c>
       <c r="K32" t="n">
-        <v>30.21</v>
+        <v>42.1</v>
       </c>
       <c r="L32" t="n">
-        <v>53.89</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:11:16</t>
+          <t>07:15:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.95</v>
+        <v>2.11</v>
       </c>
       <c r="F33" t="n">
-        <v>9.369999999999999</v>
+        <v>2.99</v>
       </c>
       <c r="G33" t="n">
-        <v>124.3</v>
+        <v>135.9</v>
       </c>
       <c r="H33" t="n">
-        <v>31.9</v>
+        <v>34.7</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J33" t="n">
-        <v>52.04</v>
+        <v>54.49</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.67</v>
+        <v>-18.62</v>
       </c>
       <c r="L33" t="n">
-        <v>59.42</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:13:28</t>
+          <t>07:16:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="F34" t="n">
-        <v>7.04</v>
+        <v>10.46</v>
       </c>
       <c r="G34" t="n">
-        <v>136</v>
+        <v>130.2</v>
       </c>
       <c r="H34" t="n">
-        <v>32.9</v>
+        <v>2.3</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>41.88</v>
+        <v>17.37</v>
       </c>
       <c r="K34" t="n">
-        <v>44.11</v>
+        <v>-68.63</v>
       </c>
       <c r="L34" t="n">
-        <v>60.82</v>
+        <v>70.79000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:18:28</t>
+          <t>07:21:18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="F35" t="n">
-        <v>8.720000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="G35" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H35" t="n">
-        <v>53.3</v>
+        <v>16.8</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>87.61</v>
+        <v>-31.42</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.87</v>
+        <v>105.95</v>
       </c>
       <c r="L35" t="n">
-        <v>87.63</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:20:34</t>
+          <t>07:22:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.29</v>
+        <v>2.64</v>
       </c>
       <c r="F36" t="n">
-        <v>9.56</v>
+        <v>6.78</v>
       </c>
       <c r="G36" t="n">
-        <v>149.5</v>
+        <v>134.6</v>
       </c>
       <c r="H36" t="n">
-        <v>62.7</v>
+        <v>23.2</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>82.98999999999999</v>
+        <v>100.41</v>
       </c>
       <c r="K36" t="n">
-        <v>-51.24</v>
+        <v>11.8</v>
       </c>
       <c r="L36" t="n">
-        <v>97.54000000000001</v>
+        <v>101.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:22:53</t>
+          <t>07:24:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.83</v>
+        <v>2.14</v>
       </c>
       <c r="F37" t="n">
-        <v>7.66</v>
+        <v>5.13</v>
       </c>
       <c r="G37" t="n">
-        <v>130.9</v>
+        <v>123.1</v>
       </c>
       <c r="H37" t="n">
-        <v>45.3</v>
+        <v>56.3</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-58.22</v>
+        <v>-49.76</v>
       </c>
       <c r="K37" t="n">
-        <v>54.28</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>79.59999999999999</v>
+        <v>93.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:28:39</t>
+          <t>07:29:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="F38" t="n">
-        <v>7.4</v>
+        <v>7.96</v>
       </c>
       <c r="G38" t="n">
-        <v>141.9</v>
+        <v>127</v>
       </c>
       <c r="H38" t="n">
-        <v>27</v>
+        <v>56.9</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>-2.39</v>
+        <v>-59.87</v>
       </c>
       <c r="K38" t="n">
-        <v>-106.28</v>
+        <v>130.96</v>
       </c>
       <c r="L38" t="n">
-        <v>106.31</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:30:48</t>
+          <t>07:30:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="F39" t="n">
-        <v>8.24</v>
+        <v>10.46</v>
       </c>
       <c r="G39" t="n">
-        <v>138</v>
+        <v>126.2</v>
       </c>
       <c r="H39" t="n">
-        <v>58.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-63.07</v>
+        <v>-141.2</v>
       </c>
       <c r="K39" t="n">
-        <v>-92.38</v>
+        <v>-55.22</v>
       </c>
       <c r="L39" t="n">
-        <v>111.86</v>
+        <v>151.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:32:45</t>
+          <t>07:33:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="F40" t="n">
-        <v>9.23</v>
+        <v>10.46</v>
       </c>
       <c r="G40" t="n">
-        <v>124.8</v>
+        <v>134.2</v>
       </c>
       <c r="H40" t="n">
-        <v>31.8</v>
+        <v>58.4</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>23.77</v>
+        <v>-198.59</v>
       </c>
       <c r="K40" t="n">
-        <v>-129.01</v>
+        <v>68.63</v>
       </c>
       <c r="L40" t="n">
-        <v>131.18</v>
+        <v>210.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:37:06</t>
+          <t>07:37:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="F41" t="n">
         <v>10.46</v>
       </c>
       <c r="G41" t="n">
-        <v>130.9</v>
+        <v>122.2</v>
       </c>
       <c r="H41" t="n">
-        <v>45.9</v>
+        <v>41.1</v>
       </c>
       <c r="I41" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>113.37</v>
+        <v>537.5</v>
       </c>
       <c r="K41" t="n">
-        <v>152.32</v>
+        <v>5.03</v>
       </c>
       <c r="L41" t="n">
-        <v>189.88</v>
+        <v>537.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:39:40</t>
+          <t>07:39:28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="F42" t="n">
         <v>10.46</v>
       </c>
       <c r="G42" t="n">
-        <v>124.5</v>
+        <v>133.5</v>
       </c>
       <c r="H42" t="n">
-        <v>20.9</v>
+        <v>42.4</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J42" t="n">
-        <v>127.32</v>
+        <v>130.56</v>
       </c>
       <c r="K42" t="n">
-        <v>-126.69</v>
+        <v>-198.2</v>
       </c>
       <c r="L42" t="n">
-        <v>179.62</v>
+        <v>237.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:40:59</t>
+          <t>07:41:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="F43" t="n">
-        <v>8.130000000000001</v>
+        <v>10.28</v>
       </c>
       <c r="G43" t="n">
-        <v>131.9</v>
+        <v>124.9</v>
       </c>
       <c r="H43" t="n">
-        <v>21.1</v>
+        <v>46.6</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>183.31</v>
+        <v>262.4</v>
       </c>
       <c r="K43" t="n">
-        <v>-47.15</v>
+        <v>-49.2</v>
       </c>
       <c r="L43" t="n">
-        <v>189.28</v>
+        <v>266.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:48:48</t>
+          <t>07:52:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.18</v>
+        <v>2.74</v>
       </c>
       <c r="F44" t="n">
-        <v>10.46</v>
+        <v>7.63</v>
       </c>
       <c r="G44" t="n">
-        <v>119.4</v>
+        <v>124.8</v>
       </c>
       <c r="H44" t="n">
-        <v>29.4</v>
+        <v>63</v>
       </c>
       <c r="I44" t="n">
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>4.42</v>
+        <v>50.65</v>
       </c>
       <c r="K44" t="n">
-        <v>51.46</v>
+        <v>-16.3</v>
       </c>
       <c r="L44" t="n">
-        <v>51.65</v>
+        <v>53.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:50:03</t>
+          <t>07:54:18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="F45" t="n">
-        <v>8.630000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>132.2</v>
+        <v>135.5</v>
       </c>
       <c r="H45" t="n">
-        <v>31.4</v>
+        <v>41.4</v>
       </c>
       <c r="I45" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>47.35</v>
+        <v>41.73</v>
       </c>
       <c r="K45" t="n">
-        <v>18.38</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>50.79</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:52:04</t>
+          <t>07:55:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="F46" t="n">
-        <v>6.71</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>130.3</v>
+        <v>122.7</v>
       </c>
       <c r="H46" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>31.38</v>
+        <v>-15.66</v>
       </c>
       <c r="K46" t="n">
-        <v>-27.44</v>
+        <v>24.48</v>
       </c>
       <c r="L46" t="n">
-        <v>41.69</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:56:04</t>
+          <t>08:00:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="F47" t="n">
-        <v>7.94</v>
+        <v>10.46</v>
       </c>
       <c r="G47" t="n">
-        <v>132.7</v>
+        <v>140.5</v>
       </c>
       <c r="H47" t="n">
-        <v>68.7</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>37.41</v>
+        <v>-36.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-38.92</v>
+        <v>-34.9</v>
       </c>
       <c r="L47" t="n">
-        <v>53.98</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:58:04</t>
+          <t>08:02:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="F48" t="n">
-        <v>10.46</v>
+        <v>8.09</v>
       </c>
       <c r="G48" t="n">
-        <v>142.8</v>
+        <v>133.3</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>52.7</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>41.46</v>
+        <v>70.45</v>
       </c>
       <c r="K48" t="n">
-        <v>-53.67</v>
+        <v>1.35</v>
       </c>
       <c r="L48" t="n">
-        <v>67.81999999999999</v>
+        <v>70.45999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:59:46</t>
+          <t>08:03:41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.46</v>
+        <v>3.19</v>
       </c>
       <c r="F49" t="n">
-        <v>5.27</v>
+        <v>5.15</v>
       </c>
       <c r="G49" t="n">
-        <v>123.1</v>
+        <v>134.4</v>
       </c>
       <c r="H49" t="n">
-        <v>46.2</v>
+        <v>58.7</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>33.26</v>
+        <v>-88.29000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>49.18</v>
+        <v>-2.42</v>
       </c>
       <c r="L49" t="n">
-        <v>59.37</v>
+        <v>88.31999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:05:48</t>
+          <t>08:08:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="F50" t="n">
-        <v>9.85</v>
+        <v>10.46</v>
       </c>
       <c r="G50" t="n">
-        <v>129.9</v>
+        <v>127.4</v>
       </c>
       <c r="H50" t="n">
-        <v>52.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J50" t="n">
-        <v>-42.46</v>
+        <v>22.42</v>
       </c>
       <c r="K50" t="n">
-        <v>95.59</v>
+        <v>139.04</v>
       </c>
       <c r="L50" t="n">
-        <v>104.6</v>
+        <v>140.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:08:07</t>
+          <t>08:09:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.29</v>
+        <v>2.92</v>
       </c>
       <c r="F51" t="n">
-        <v>7.2</v>
+        <v>4.75</v>
       </c>
       <c r="G51" t="n">
-        <v>124.8</v>
+        <v>136.4</v>
       </c>
       <c r="H51" t="n">
-        <v>45</v>
+        <v>14.8</v>
       </c>
       <c r="I51" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J51" t="n">
-        <v>-77.09999999999999</v>
+        <v>-2.2</v>
       </c>
       <c r="K51" t="n">
-        <v>-20.71</v>
+        <v>116.21</v>
       </c>
       <c r="L51" t="n">
-        <v>79.84</v>
+        <v>116.23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:09:07</t>
+          <t>08:11:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.78</v>
+        <v>3.24</v>
       </c>
       <c r="F52" t="n">
         <v>10.46</v>
       </c>
       <c r="G52" t="n">
-        <v>130.6</v>
+        <v>130.3</v>
       </c>
       <c r="H52" t="n">
-        <v>35.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-65.34999999999999</v>
+        <v>97.69</v>
       </c>
       <c r="K52" t="n">
-        <v>71.97</v>
+        <v>47.44</v>
       </c>
       <c r="L52" t="n">
-        <v>97.20999999999999</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:15:11</t>
+          <t>08:15:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="F53" t="n">
-        <v>9.34</v>
+        <v>7.29</v>
       </c>
       <c r="G53" t="n">
-        <v>127.1</v>
+        <v>124.4</v>
       </c>
       <c r="H53" t="n">
-        <v>23.7</v>
+        <v>56.1</v>
       </c>
       <c r="I53" t="n">
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>89.51000000000001</v>
+        <v>-58.3</v>
       </c>
       <c r="K53" t="n">
-        <v>74.5</v>
+        <v>155.69</v>
       </c>
       <c r="L53" t="n">
-        <v>116.46</v>
+        <v>166.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:17:05</t>
+          <t>08:16:42</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="F54" t="n">
-        <v>8.210000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="G54" t="n">
-        <v>135.8</v>
+        <v>131.8</v>
       </c>
       <c r="H54" t="n">
-        <v>78.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>73.29000000000001</v>
+        <v>-130.41</v>
       </c>
       <c r="K54" t="n">
-        <v>78.36</v>
+        <v>61.85</v>
       </c>
       <c r="L54" t="n">
-        <v>107.29</v>
+        <v>144.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:19:01</t>
+          <t>08:18:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="F55" t="n">
-        <v>6.92</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>141.3</v>
+        <v>148.9</v>
       </c>
       <c r="H55" t="n">
-        <v>43.7</v>
+        <v>59.3</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>48.58</v>
+        <v>-184.8</v>
       </c>
       <c r="K55" t="n">
-        <v>165.19</v>
+        <v>-35.45</v>
       </c>
       <c r="L55" t="n">
-        <v>172.19</v>
+        <v>188.17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:22:32</t>
+          <t>08:23:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.99</v>
+        <v>3.16</v>
       </c>
       <c r="F56" t="n">
-        <v>10.46</v>
+        <v>9.66</v>
       </c>
       <c r="G56" t="n">
-        <v>124.5</v>
+        <v>129.1</v>
       </c>
       <c r="H56" t="n">
-        <v>55.2</v>
+        <v>72.2</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>232.55</v>
+        <v>86.38</v>
       </c>
       <c r="K56" t="n">
-        <v>-158.35</v>
+        <v>288.9</v>
       </c>
       <c r="L56" t="n">
-        <v>281.34</v>
+        <v>301.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:23:46</t>
+          <t>08:24:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="F57" t="n">
         <v>10.46</v>
       </c>
       <c r="G57" t="n">
-        <v>138.4</v>
+        <v>141</v>
       </c>
       <c r="H57" t="n">
-        <v>4.3</v>
+        <v>45.9</v>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-101.52</v>
+        <v>-14.33</v>
       </c>
       <c r="K57" t="n">
-        <v>151.88</v>
+        <v>196.16</v>
       </c>
       <c r="L57" t="n">
-        <v>182.68</v>
+        <v>196.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:24:52</t>
+          <t>08:26:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.84</v>
+        <v>2.67</v>
       </c>
       <c r="F58" t="n">
-        <v>10.44</v>
+        <v>10.46</v>
       </c>
       <c r="G58" t="n">
-        <v>134.6</v>
+        <v>142</v>
       </c>
       <c r="H58" t="n">
-        <v>59.1</v>
+        <v>44.4</v>
       </c>
       <c r="I58" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>94.06999999999999</v>
+        <v>221.38</v>
       </c>
       <c r="K58" t="n">
-        <v>-115.77</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>149.17</v>
+        <v>221.57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:33:51</t>
+          <t>08:33:26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.95</v>
+        <v>2.53</v>
       </c>
       <c r="F59" t="n">
-        <v>10.46</v>
+        <v>5.46</v>
       </c>
       <c r="G59" t="n">
-        <v>129.1</v>
+        <v>136.7</v>
       </c>
       <c r="H59" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
       <c r="I59" t="n">
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>42.2</v>
+        <v>48.34</v>
       </c>
       <c r="K59" t="n">
-        <v>2.99</v>
+        <v>-4.33</v>
       </c>
       <c r="L59" t="n">
-        <v>42.31</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:35:20</t>
+          <t>08:34:59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.12</v>
+        <v>2.99</v>
       </c>
       <c r="F60" t="n">
-        <v>6.98</v>
+        <v>10.46</v>
       </c>
       <c r="G60" t="n">
-        <v>130.4</v>
+        <v>141</v>
       </c>
       <c r="H60" t="n">
-        <v>57.2</v>
+        <v>28.5</v>
       </c>
       <c r="I60" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-33.74</v>
+        <v>40.24</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.95</v>
+        <v>-30.89</v>
       </c>
       <c r="L60" t="n">
-        <v>34.26</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:37:14</t>
+          <t>08:37:09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.38</v>
+        <v>2.83</v>
       </c>
       <c r="F61" t="n">
-        <v>8.460000000000001</v>
+        <v>10.46</v>
       </c>
       <c r="G61" t="n">
-        <v>127</v>
+        <v>129.9</v>
       </c>
       <c r="H61" t="n">
-        <v>29.9</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.19</v>
+        <v>45.75</v>
       </c>
       <c r="K61" t="n">
-        <v>-46.93</v>
+        <v>-19.69</v>
       </c>
       <c r="L61" t="n">
-        <v>47.12</v>
+        <v>49.81</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:42:38</t>
+          <t>08:43:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="F62" t="n">
-        <v>7.5</v>
+        <v>10.46</v>
       </c>
       <c r="G62" t="n">
-        <v>134.2</v>
+        <v>139.8</v>
       </c>
       <c r="H62" t="n">
-        <v>1.9</v>
+        <v>51.4</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-12.74</v>
+        <v>-7.5</v>
       </c>
       <c r="K62" t="n">
-        <v>-70.39</v>
+        <v>95.05</v>
       </c>
       <c r="L62" t="n">
-        <v>71.53</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:44:02</t>
+          <t>08:44:57</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="F63" t="n">
-        <v>8.449999999999999</v>
+        <v>5.95</v>
       </c>
       <c r="G63" t="n">
-        <v>145.7</v>
+        <v>119.7</v>
       </c>
       <c r="H63" t="n">
-        <v>49</v>
+        <v>54.4</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>17.87</v>
+        <v>-3.16</v>
       </c>
       <c r="K63" t="n">
-        <v>-59.22</v>
+        <v>-63.96</v>
       </c>
       <c r="L63" t="n">
-        <v>61.86</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:45:08</t>
+          <t>08:47:23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="F64" t="n">
-        <v>10.05</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>142.7</v>
+        <v>133</v>
       </c>
       <c r="H64" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="I64" t="n">
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-41.54</v>
+        <v>-44.71</v>
       </c>
       <c r="K64" t="n">
-        <v>-44.68</v>
+        <v>-61.93</v>
       </c>
       <c r="L64" t="n">
-        <v>61.01</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:49:13</t>
+          <t>08:51:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="F65" t="n">
-        <v>8.5</v>
+        <v>10.46</v>
       </c>
       <c r="G65" t="n">
-        <v>128.6</v>
+        <v>125</v>
       </c>
       <c r="H65" t="n">
-        <v>40.5</v>
+        <v>4.5</v>
       </c>
       <c r="I65" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>40.42</v>
+        <v>-69.47</v>
       </c>
       <c r="K65" t="n">
-        <v>-80.42</v>
+        <v>95.98</v>
       </c>
       <c r="L65" t="n">
-        <v>90.01000000000001</v>
+        <v>118.49</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:51:35</t>
+          <t>08:52:53</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="F66" t="n">
-        <v>10.37</v>
+        <v>7.85</v>
       </c>
       <c r="G66" t="n">
-        <v>136.5</v>
+        <v>131.5</v>
       </c>
       <c r="H66" t="n">
-        <v>4.8</v>
+        <v>35.3</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>39.27</v>
+        <v>44.26</v>
       </c>
       <c r="K66" t="n">
-        <v>-53.93</v>
+        <v>95.09</v>
       </c>
       <c r="L66" t="n">
-        <v>66.70999999999999</v>
+        <v>104.89</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:53:47</t>
+          <t>08:54:41</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="F67" t="n">
-        <v>8.56</v>
+        <v>7.91</v>
       </c>
       <c r="G67" t="n">
-        <v>136.9</v>
+        <v>124.8</v>
       </c>
       <c r="H67" t="n">
-        <v>43.4</v>
+        <v>33.2</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>82.43000000000001</v>
+        <v>50.92</v>
       </c>
       <c r="K67" t="n">
-        <v>-21.25</v>
+        <v>-84.79000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>85.13</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:58:02</t>
+          <t>08:59:28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="F68" t="n">
-        <v>10.46</v>
+        <v>9.32</v>
       </c>
       <c r="G68" t="n">
-        <v>125.8</v>
+        <v>124.1</v>
       </c>
       <c r="H68" t="n">
-        <v>66.7</v>
+        <v>28.3</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>139.85</v>
+        <v>206.51</v>
       </c>
       <c r="K68" t="n">
-        <v>75.45</v>
+        <v>-38.64</v>
       </c>
       <c r="L68" t="n">
-        <v>158.91</v>
+        <v>210.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:59:36</t>
+          <t>09:01:52</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="F69" t="n">
-        <v>8.550000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="G69" t="n">
-        <v>140.2</v>
+        <v>133.8</v>
       </c>
       <c r="H69" t="n">
-        <v>31.8</v>
+        <v>15.2</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>44.82</v>
+        <v>-10.98</v>
       </c>
       <c r="K69" t="n">
-        <v>-129.48</v>
+        <v>-165.85</v>
       </c>
       <c r="L69" t="n">
-        <v>137.02</v>
+        <v>166.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:01:28</t>
+          <t>09:03:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="F70" t="n">
         <v>10.46</v>
       </c>
       <c r="G70" t="n">
-        <v>132</v>
+        <v>136.3</v>
       </c>
       <c r="H70" t="n">
-        <v>45.6</v>
+        <v>42</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>88.86</v>
+        <v>217.23</v>
       </c>
       <c r="K70" t="n">
-        <v>101.54</v>
+        <v>-154.64</v>
       </c>
       <c r="L70" t="n">
-        <v>134.93</v>
+        <v>266.65</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:05:28</t>
+          <t>09:09:47</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="F71" t="n">
         <v>10.46</v>
       </c>
       <c r="G71" t="n">
-        <v>124.4</v>
+        <v>129.7</v>
       </c>
       <c r="H71" t="n">
-        <v>64.09999999999999</v>
+        <v>31.4</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>182.63</v>
+        <v>169.52</v>
       </c>
       <c r="K71" t="n">
-        <v>-132.27</v>
+        <v>-247.17</v>
       </c>
       <c r="L71" t="n">
-        <v>225.49</v>
+        <v>299.71</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:07:34</t>
+          <t>09:12:02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="F72" t="n">
-        <v>10.17</v>
+        <v>6.45</v>
       </c>
       <c r="G72" t="n">
-        <v>126.5</v>
+        <v>131.9</v>
       </c>
       <c r="H72" t="n">
-        <v>24.9</v>
+        <v>37.7</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>23.34</v>
+        <v>-33.24</v>
       </c>
       <c r="K72" t="n">
-        <v>-192.82</v>
+        <v>226.7</v>
       </c>
       <c r="L72" t="n">
-        <v>194.23</v>
+        <v>229.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:10:00</t>
+          <t>09:12:57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.84</v>
+        <v>3.71</v>
       </c>
       <c r="F73" t="n">
         <v>10.46</v>
       </c>
       <c r="G73" t="n">
-        <v>123.3</v>
+        <v>134.4</v>
       </c>
       <c r="H73" t="n">
-        <v>17.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-51.17</v>
+        <v>220.69</v>
       </c>
       <c r="K73" t="n">
-        <v>-125.79</v>
+        <v>-77.39</v>
       </c>
       <c r="L73" t="n">
-        <v>135.79</v>
+        <v>233.86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:21:50</t>
+          <t>09:25:36</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="F74" t="n">
         <v>10.46</v>
       </c>
       <c r="G74" t="n">
-        <v>139.2</v>
+        <v>120.9</v>
       </c>
       <c r="H74" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>20.09</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>24.38</v>
+        <v>-49.7</v>
       </c>
       <c r="L74" t="n">
-        <v>31.59</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:24:14</t>
+          <t>09:28:26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="F75" t="n">
         <v>10.46</v>
       </c>
       <c r="G75" t="n">
-        <v>136</v>
+        <v>118.3</v>
       </c>
       <c r="H75" t="n">
-        <v>24.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-42.01</v>
+        <v>-7.1</v>
       </c>
       <c r="K75" t="n">
-        <v>23.6</v>
+        <v>-49.34</v>
       </c>
       <c r="L75" t="n">
-        <v>48.19</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:26:21</t>
+          <t>09:29:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="F76" t="n">
-        <v>4.46</v>
+        <v>10.46</v>
       </c>
       <c r="G76" t="n">
-        <v>148.2</v>
+        <v>135.7</v>
       </c>
       <c r="H76" t="n">
-        <v>49.6</v>
+        <v>32.1</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>7.21</v>
+        <v>7.82</v>
       </c>
       <c r="K76" t="n">
-        <v>-34.73</v>
+        <v>-40.19</v>
       </c>
       <c r="L76" t="n">
-        <v>35.47</v>
+        <v>40.95</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:32:15</t>
+          <t>09:34:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="F77" t="n">
         <v>10.46</v>
       </c>
       <c r="G77" t="n">
-        <v>139.9</v>
+        <v>141.8</v>
       </c>
       <c r="H77" t="n">
-        <v>46.5</v>
+        <v>43.5</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>43.52</v>
+        <v>-5.76</v>
       </c>
       <c r="K77" t="n">
-        <v>57.06</v>
+        <v>-73.39</v>
       </c>
       <c r="L77" t="n">
-        <v>71.76000000000001</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:33:41</t>
+          <t>09:36:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="F78" t="n">
-        <v>8.99</v>
+        <v>10.46</v>
       </c>
       <c r="G78" t="n">
-        <v>119.3</v>
+        <v>129.4</v>
       </c>
       <c r="H78" t="n">
-        <v>47.5</v>
+        <v>49.6</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>63.45</v>
+        <v>44.8</v>
       </c>
       <c r="K78" t="n">
-        <v>-27.3</v>
+        <v>-61.76</v>
       </c>
       <c r="L78" t="n">
-        <v>69.06999999999999</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:35:31</t>
+          <t>09:37:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="F79" t="n">
-        <v>8.699999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="G79" t="n">
-        <v>133.4</v>
+        <v>147.6</v>
       </c>
       <c r="H79" t="n">
-        <v>41</v>
+        <v>57.6</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>32.06</v>
+        <v>16.2</v>
       </c>
       <c r="K79" t="n">
-        <v>38.4</v>
+        <v>69.47</v>
       </c>
       <c r="L79" t="n">
-        <v>50.02</v>
+        <v>71.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:39:49</t>
+          <t>09:43:23</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="F80" t="n">
-        <v>9.9</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>133.3</v>
+        <v>123.7</v>
       </c>
       <c r="H80" t="n">
-        <v>45.5</v>
+        <v>34.5</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-79.34999999999999</v>
+        <v>105.55</v>
       </c>
       <c r="K80" t="n">
-        <v>-54.56</v>
+        <v>15.14</v>
       </c>
       <c r="L80" t="n">
-        <v>96.3</v>
+        <v>106.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:42:20</t>
+          <t>09:46:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="F81" t="n">
         <v>10.46</v>
       </c>
       <c r="G81" t="n">
-        <v>134.4</v>
+        <v>128.2</v>
       </c>
       <c r="H81" t="n">
-        <v>29.7</v>
+        <v>13</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.5</v>
+        <v>-112.23</v>
       </c>
       <c r="K81" t="n">
-        <v>107.9</v>
+        <v>17.79</v>
       </c>
       <c r="L81" t="n">
-        <v>108.74</v>
+        <v>113.63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:44:13</t>
+          <t>09:48:07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="F82" t="n">
         <v>10.46</v>
       </c>
       <c r="G82" t="n">
-        <v>115.3</v>
+        <v>132.7</v>
       </c>
       <c r="H82" t="n">
-        <v>29.1</v>
+        <v>24.2</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>69.90000000000001</v>
+        <v>-105.33</v>
       </c>
       <c r="K82" t="n">
-        <v>-43.78</v>
+        <v>85.34</v>
       </c>
       <c r="L82" t="n">
-        <v>82.48</v>
+        <v>135.57</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:48:28</t>
+          <t>09:54:02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.67</v>
+        <v>3.45</v>
       </c>
       <c r="F83" t="n">
-        <v>6.02</v>
+        <v>10.46</v>
       </c>
       <c r="G83" t="n">
-        <v>143.5</v>
+        <v>136.1</v>
       </c>
       <c r="H83" t="n">
-        <v>28.4</v>
+        <v>2.4</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>102.49</v>
+        <v>50.72</v>
       </c>
       <c r="K83" t="n">
-        <v>20.05</v>
+        <v>-163.94</v>
       </c>
       <c r="L83" t="n">
-        <v>104.43</v>
+        <v>171.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:50:52</t>
+          <t>09:54:43</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.24</v>
+        <v>3.11</v>
       </c>
       <c r="F84" t="n">
         <v>10.46</v>
       </c>
       <c r="G84" t="n">
-        <v>137.4</v>
+        <v>137.7</v>
       </c>
       <c r="H84" t="n">
-        <v>21.5</v>
+        <v>43.7</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-12.93</v>
+        <v>-3.39</v>
       </c>
       <c r="K84" t="n">
-        <v>-146.49</v>
+        <v>209.39</v>
       </c>
       <c r="L84" t="n">
-        <v>147.06</v>
+        <v>209.42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:52:19</t>
+          <t>09:55:36</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="F85" t="n">
         <v>10.46</v>
       </c>
       <c r="G85" t="n">
-        <v>123</v>
+        <v>133.1</v>
       </c>
       <c r="H85" t="n">
-        <v>63.8</v>
+        <v>70.2</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-115.38</v>
+        <v>-109.7</v>
       </c>
       <c r="K85" t="n">
-        <v>99.67</v>
+        <v>-158.96</v>
       </c>
       <c r="L85" t="n">
-        <v>152.47</v>
+        <v>193.14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:57:48</t>
+          <t>10:01:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.49</v>
+        <v>2.9</v>
       </c>
       <c r="F86" t="n">
-        <v>7.8</v>
+        <v>10.46</v>
       </c>
       <c r="G86" t="n">
-        <v>118.4</v>
+        <v>126.9</v>
       </c>
       <c r="H86" t="n">
-        <v>0.7</v>
+        <v>34.1</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>52.67</v>
+        <v>150.49</v>
       </c>
       <c r="K86" t="n">
-        <v>130.1</v>
+        <v>167.93</v>
       </c>
       <c r="L86" t="n">
-        <v>140.35</v>
+        <v>225.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:59:35</t>
+          <t>10:02:34</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.79</v>
+        <v>3.57</v>
       </c>
       <c r="F87" t="n">
-        <v>9.35</v>
+        <v>10.46</v>
       </c>
       <c r="G87" t="n">
-        <v>134.1</v>
+        <v>149</v>
       </c>
       <c r="H87" t="n">
-        <v>40.8</v>
+        <v>73.3</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>68.5</v>
+        <v>285.52</v>
       </c>
       <c r="K87" t="n">
-        <v>176.34</v>
+        <v>158.63</v>
       </c>
       <c r="L87" t="n">
-        <v>189.18</v>
+        <v>326.63</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:01:04</t>
+          <t>10:03:59</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.26</v>
+        <v>2.99</v>
       </c>
       <c r="F88" t="n">
-        <v>10.46</v>
+        <v>7.72</v>
       </c>
       <c r="G88" t="n">
-        <v>139.8</v>
+        <v>121.7</v>
       </c>
       <c r="H88" t="n">
-        <v>13.5</v>
+        <v>25.4</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-187.48</v>
+        <v>18.31</v>
       </c>
       <c r="K88" t="n">
-        <v>16.49</v>
+        <v>-230.28</v>
       </c>
       <c r="L88" t="n">
-        <v>188.2</v>
+        <v>231.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-36.35</v>
+        <v>-36.66</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.77</v>
+        <v>-8.84</v>
       </c>
       <c r="L14" t="n">
-        <v>37.4</v>
+        <v>37.71</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.85</v>
+        <v>-13.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-49.2</v>
+        <v>-48.67</v>
       </c>
       <c r="L15" t="n">
-        <v>51.11</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.28</v>
+        <v>-54.17</v>
       </c>
       <c r="K16" t="n">
-        <v>15.25</v>
+        <v>14.94</v>
       </c>
       <c r="L16" t="n">
-        <v>57.34</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-55.33</v>
+        <v>-52.58</v>
       </c>
       <c r="K17" t="n">
-        <v>-55.62</v>
+        <v>-52.85</v>
       </c>
       <c r="L17" t="n">
-        <v>78.45999999999999</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>23.43</v>
+        <v>25.27</v>
       </c>
       <c r="K18" t="n">
-        <v>56.41</v>
+        <v>60.84</v>
       </c>
       <c r="L18" t="n">
-        <v>61.08</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-60.97</v>
+        <v>-61.07</v>
       </c>
       <c r="K19" t="n">
-        <v>-51.23</v>
+        <v>-51.32</v>
       </c>
       <c r="L19" t="n">
-        <v>79.63</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-83.16</v>
+        <v>-91.2</v>
       </c>
       <c r="K20" t="n">
-        <v>-42.39</v>
+        <v>-46.49</v>
       </c>
       <c r="L20" t="n">
-        <v>93.34</v>
+        <v>102.37</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-86.13</v>
+        <v>-88.42</v>
       </c>
       <c r="K21" t="n">
-        <v>79.40000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>117.15</v>
+        <v>120.26</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-19.13</v>
+        <v>-22.1</v>
       </c>
       <c r="K22" t="n">
-        <v>-21.84</v>
+        <v>-25.23</v>
       </c>
       <c r="L22" t="n">
-        <v>29.03</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-53.32</v>
+        <v>-54.24</v>
       </c>
       <c r="K23" t="n">
-        <v>170.08</v>
+        <v>173.01</v>
       </c>
       <c r="L23" t="n">
-        <v>178.24</v>
+        <v>181.31</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>120.98</v>
+        <v>140.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.77</v>
+        <v>-10.16</v>
       </c>
       <c r="L24" t="n">
-        <v>121.3</v>
+        <v>140.57</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-155.91</v>
+        <v>-166.54</v>
       </c>
       <c r="K25" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="L25" t="n">
-        <v>155.93</v>
+        <v>166.56</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-86.45</v>
+        <v>-102.81</v>
       </c>
       <c r="K26" t="n">
-        <v>125.84</v>
+        <v>149.64</v>
       </c>
       <c r="L26" t="n">
-        <v>152.67</v>
+        <v>181.55</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>157.54</v>
+        <v>171.61</v>
       </c>
       <c r="K27" t="n">
-        <v>132.49</v>
+        <v>144.32</v>
       </c>
       <c r="L27" t="n">
-        <v>205.85</v>
+        <v>224.23</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>128.46</v>
+        <v>152.35</v>
       </c>
       <c r="K28" t="n">
-        <v>-114.67</v>
+        <v>-136</v>
       </c>
       <c r="L28" t="n">
-        <v>172.19</v>
+        <v>204.22</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>55.65</v>
+        <v>56.47</v>
       </c>
       <c r="K29" t="n">
-        <v>6.66</v>
+        <v>6.75</v>
       </c>
       <c r="L29" t="n">
-        <v>56.05</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>11.21</v>
+        <v>10.03</v>
       </c>
       <c r="K30" t="n">
-        <v>62.58</v>
+        <v>55.99</v>
       </c>
       <c r="L30" t="n">
-        <v>63.57</v>
+        <v>56.88</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>50.93</v>
+        <v>47.86</v>
       </c>
       <c r="K31" t="n">
-        <v>42.29</v>
+        <v>39.74</v>
       </c>
       <c r="L31" t="n">
-        <v>66.2</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="K32" t="n">
-        <v>-44.81</v>
+        <v>-46.98</v>
       </c>
       <c r="L32" t="n">
-        <v>44.83</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.14</v>
+        <v>-11.47</v>
       </c>
       <c r="K33" t="n">
-        <v>65.62</v>
+        <v>67.56</v>
       </c>
       <c r="L33" t="n">
-        <v>66.56</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>46.75</v>
+        <v>47.72</v>
       </c>
       <c r="K34" t="n">
-        <v>46.31</v>
+        <v>47.26</v>
       </c>
       <c r="L34" t="n">
-        <v>65.8</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-100.32</v>
+        <v>-102.97</v>
       </c>
       <c r="K35" t="n">
-        <v>-26.27</v>
+        <v>-26.97</v>
       </c>
       <c r="L35" t="n">
-        <v>103.71</v>
+        <v>106.44</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-85.06999999999999</v>
+        <v>-89.70999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-77.48</v>
+        <v>-81.70999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>115.06</v>
+        <v>121.34</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-36.81</v>
+        <v>-38.08</v>
       </c>
       <c r="K37" t="n">
-        <v>102.49</v>
+        <v>106</v>
       </c>
       <c r="L37" t="n">
-        <v>108.9</v>
+        <v>112.64</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>132.03</v>
+        <v>136.33</v>
       </c>
       <c r="K38" t="n">
-        <v>-102.01</v>
+        <v>-105.33</v>
       </c>
       <c r="L38" t="n">
-        <v>166.85</v>
+        <v>172.28</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-162.19</v>
+        <v>-163.44</v>
       </c>
       <c r="K39" t="n">
-        <v>-15.37</v>
+        <v>-15.48</v>
       </c>
       <c r="L39" t="n">
-        <v>162.91</v>
+        <v>164.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>156.2</v>
+        <v>159.78</v>
       </c>
       <c r="K40" t="n">
-        <v>34.62</v>
+        <v>35.41</v>
       </c>
       <c r="L40" t="n">
-        <v>159.99</v>
+        <v>163.66</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>162.88</v>
+        <v>186.2</v>
       </c>
       <c r="K41" t="n">
-        <v>-85.7</v>
+        <v>-97.97</v>
       </c>
       <c r="L41" t="n">
-        <v>184.05</v>
+        <v>210.4</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-145.64</v>
+        <v>-170.69</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.93</v>
+        <v>-55</v>
       </c>
       <c r="L42" t="n">
-        <v>153.01</v>
+        <v>179.33</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-199.17</v>
+        <v>-220.2</v>
       </c>
       <c r="K43" t="n">
-        <v>-21.17</v>
+        <v>-23.41</v>
       </c>
       <c r="L43" t="n">
-        <v>200.29</v>
+        <v>221.44</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>80.19</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>9.1</v>
+        <v>8.51</v>
       </c>
       <c r="L44" t="n">
-        <v>80.7</v>
+        <v>75.53</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>31.46</v>
+        <v>30.77</v>
       </c>
       <c r="K45" t="n">
-        <v>51.79</v>
+        <v>50.66</v>
       </c>
       <c r="L45" t="n">
-        <v>60.6</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>14.18</v>
+        <v>15.01</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.72</v>
+        <v>-60.05</v>
       </c>
       <c r="L46" t="n">
-        <v>58.46</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-51.63</v>
+        <v>-53.72</v>
       </c>
       <c r="K47" t="n">
-        <v>-52.97</v>
+        <v>-55.11</v>
       </c>
       <c r="L47" t="n">
-        <v>73.97</v>
+        <v>76.95999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>38.74</v>
+        <v>42.57</v>
       </c>
       <c r="K48" t="n">
-        <v>42.31</v>
+        <v>46.5</v>
       </c>
       <c r="L48" t="n">
-        <v>57.37</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>15.21</v>
+        <v>15.43</v>
       </c>
       <c r="K49" t="n">
-        <v>85.03</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>86.38</v>
+        <v>87.61</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-64.47</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>125.89</v>
+        <v>128.36</v>
       </c>
       <c r="L50" t="n">
-        <v>141.44</v>
+        <v>144.21</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>25.93</v>
+        <v>29.88</v>
       </c>
       <c r="K51" t="n">
-        <v>80.88</v>
+        <v>93.19</v>
       </c>
       <c r="L51" t="n">
-        <v>84.94</v>
+        <v>97.86</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>60.79</v>
+        <v>64.13</v>
       </c>
       <c r="K52" t="n">
-        <v>-74.93000000000001</v>
+        <v>-79.05</v>
       </c>
       <c r="L52" t="n">
-        <v>96.48999999999999</v>
+        <v>101.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>182.76</v>
+        <v>187.38</v>
       </c>
       <c r="K53" t="n">
-        <v>5.4</v>
+        <v>5.54</v>
       </c>
       <c r="L53" t="n">
-        <v>182.84</v>
+        <v>187.46</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>171.71</v>
+        <v>185.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.88</v>
+        <v>-5.28</v>
       </c>
       <c r="L54" t="n">
-        <v>171.78</v>
+        <v>185.71</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>108.7</v>
+        <v>127.28</v>
       </c>
       <c r="K55" t="n">
-        <v>-34.03</v>
+        <v>-39.85</v>
       </c>
       <c r="L55" t="n">
-        <v>113.91</v>
+        <v>133.37</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>127.14</v>
+        <v>141.79</v>
       </c>
       <c r="K56" t="n">
-        <v>169.76</v>
+        <v>189.32</v>
       </c>
       <c r="L56" t="n">
-        <v>212.1</v>
+        <v>236.54</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>236.13</v>
+        <v>256.22</v>
       </c>
       <c r="K57" t="n">
-        <v>65.54000000000001</v>
+        <v>71.12</v>
       </c>
       <c r="L57" t="n">
-        <v>245.05</v>
+        <v>265.91</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-208.43</v>
+        <v>-235.2</v>
       </c>
       <c r="K58" t="n">
-        <v>-55.29</v>
+        <v>-62.39</v>
       </c>
       <c r="L58" t="n">
-        <v>215.64</v>
+        <v>243.34</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-47.27</v>
+        <v>-47.7</v>
       </c>
       <c r="K59" t="n">
-        <v>-18.48</v>
+        <v>-18.65</v>
       </c>
       <c r="L59" t="n">
-        <v>50.75</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-46</v>
+        <v>-48.78</v>
       </c>
       <c r="K60" t="n">
-        <v>12.95</v>
+        <v>13.73</v>
       </c>
       <c r="L60" t="n">
-        <v>47.79</v>
+        <v>50.68</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>25.57</v>
+        <v>26.61</v>
       </c>
       <c r="K61" t="n">
-        <v>42.1</v>
+        <v>43.81</v>
       </c>
       <c r="L61" t="n">
-        <v>49.25</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-63.04</v>
+        <v>-59.06</v>
       </c>
       <c r="K62" t="n">
-        <v>71.67</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>95.45</v>
+        <v>89.42</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>86.47</v>
+        <v>83.64</v>
       </c>
       <c r="K63" t="n">
-        <v>-40.88</v>
+        <v>-39.54</v>
       </c>
       <c r="L63" t="n">
-        <v>95.65000000000001</v>
+        <v>92.51000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>77.48</v>
+        <v>76.28</v>
       </c>
       <c r="K64" t="n">
-        <v>36.25</v>
+        <v>35.69</v>
       </c>
       <c r="L64" t="n">
-        <v>85.54000000000001</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-24.98</v>
+        <v>-27.87</v>
       </c>
       <c r="K65" t="n">
-        <v>83.09</v>
+        <v>92.69</v>
       </c>
       <c r="L65" t="n">
-        <v>86.76000000000001</v>
+        <v>96.79000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>14.64</v>
+        <v>16.5</v>
       </c>
       <c r="K66" t="n">
-        <v>79.56</v>
+        <v>89.66</v>
       </c>
       <c r="L66" t="n">
-        <v>80.90000000000001</v>
+        <v>91.16</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>95.36</v>
+        <v>101.32</v>
       </c>
       <c r="K67" t="n">
-        <v>5.29</v>
+        <v>5.63</v>
       </c>
       <c r="L67" t="n">
-        <v>95.5</v>
+        <v>101.47</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-76.73</v>
+        <v>-80.88</v>
       </c>
       <c r="K68" t="n">
-        <v>-126.97</v>
+        <v>-133.85</v>
       </c>
       <c r="L68" t="n">
-        <v>148.35</v>
+        <v>156.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>66.84999999999999</v>
+        <v>77.92</v>
       </c>
       <c r="K69" t="n">
-        <v>-96.28</v>
+        <v>-112.23</v>
       </c>
       <c r="L69" t="n">
-        <v>117.21</v>
+        <v>136.63</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>27.18</v>
+        <v>30.98</v>
       </c>
       <c r="K70" t="n">
-        <v>-113.26</v>
+        <v>-129.1</v>
       </c>
       <c r="L70" t="n">
-        <v>116.47</v>
+        <v>132.76</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-144.42</v>
+        <v>-172.03</v>
       </c>
       <c r="K71" t="n">
-        <v>-67.45</v>
+        <v>-80.34999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>159.4</v>
+        <v>189.87</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>130.98</v>
+        <v>153.77</v>
       </c>
       <c r="K72" t="n">
-        <v>116.87</v>
+        <v>137.2</v>
       </c>
       <c r="L72" t="n">
-        <v>175.54</v>
+        <v>206.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>39.88</v>
+        <v>42.83</v>
       </c>
       <c r="K73" t="n">
-        <v>-233.38</v>
+        <v>-250.68</v>
       </c>
       <c r="L73" t="n">
-        <v>236.76</v>
+        <v>254.32</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>29.81</v>
+        <v>30</v>
       </c>
       <c r="K74" t="n">
-        <v>46.34</v>
+        <v>46.62</v>
       </c>
       <c r="L74" t="n">
-        <v>55.1</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>22.41</v>
+        <v>21.72</v>
       </c>
       <c r="K75" t="n">
-        <v>49.97</v>
+        <v>48.43</v>
       </c>
       <c r="L75" t="n">
-        <v>54.76</v>
+        <v>53.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-46.91</v>
+        <v>-45.86</v>
       </c>
       <c r="K76" t="n">
-        <v>-64.66</v>
+        <v>-63.22</v>
       </c>
       <c r="L76" t="n">
-        <v>79.89</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-89.38</v>
+        <v>-83.34999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-60.16</v>
+        <v>-56.1</v>
       </c>
       <c r="L77" t="n">
-        <v>107.74</v>
+        <v>100.47</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-37.82</v>
+        <v>-36.8</v>
       </c>
       <c r="K78" t="n">
-        <v>82.48999999999999</v>
+        <v>80.25</v>
       </c>
       <c r="L78" t="n">
-        <v>90.75</v>
+        <v>88.28</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-27.49</v>
+        <v>-29.36</v>
       </c>
       <c r="K79" t="n">
-        <v>-55.38</v>
+        <v>-59.15</v>
       </c>
       <c r="L79" t="n">
-        <v>61.83</v>
+        <v>66.04000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>130.24</v>
+        <v>127.17</v>
       </c>
       <c r="K80" t="n">
-        <v>45.21</v>
+        <v>44.14</v>
       </c>
       <c r="L80" t="n">
-        <v>137.86</v>
+        <v>134.61</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-131.83</v>
+        <v>-132.84</v>
       </c>
       <c r="K81" t="n">
-        <v>-63.36</v>
+        <v>-63.85</v>
       </c>
       <c r="L81" t="n">
-        <v>146.27</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>117.63</v>
+        <v>120.76</v>
       </c>
       <c r="K82" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="L82" t="n">
-        <v>117.65</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>155.24</v>
+        <v>169.49</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.46</v>
+        <v>-0.5</v>
       </c>
       <c r="L83" t="n">
-        <v>155.25</v>
+        <v>169.49</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-19.95</v>
+        <v>-20.91</v>
       </c>
       <c r="K84" t="n">
-        <v>-174.6</v>
+        <v>-182.98</v>
       </c>
       <c r="L84" t="n">
-        <v>175.74</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>95.53</v>
+        <v>106.84</v>
       </c>
       <c r="K85" t="n">
-        <v>-93.70999999999999</v>
+        <v>-104.8</v>
       </c>
       <c r="L85" t="n">
-        <v>133.82</v>
+        <v>149.66</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>23.48</v>
+        <v>25.49</v>
       </c>
       <c r="K86" t="n">
-        <v>334.93</v>
+        <v>363.65</v>
       </c>
       <c r="L86" t="n">
-        <v>335.75</v>
+        <v>364.54</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>193.19</v>
+        <v>206.21</v>
       </c>
       <c r="K87" t="n">
-        <v>130.17</v>
+        <v>138.94</v>
       </c>
       <c r="L87" t="n">
-        <v>232.95</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.15</v>
+        <v>-3.37</v>
       </c>
       <c r="K88" t="n">
-        <v>-226.67</v>
+        <v>-242.37</v>
       </c>
       <c r="L88" t="n">
-        <v>226.7</v>
+        <v>242.39</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-02.xlsx
+++ b/output/2024-09-02.xlsx
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>56.47</v>
+        <v>56.58</v>
       </c>
       <c r="K29" t="n">
-        <v>6.75</v>
+        <v>6.77</v>
       </c>
       <c r="L29" t="n">
-        <v>56.87</v>
+        <v>56.98</v>
       </c>
     </row>
     <row r="30">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.47</v>
+        <v>-11.54</v>
       </c>
       <c r="K33" t="n">
-        <v>67.56</v>
+        <v>67.97</v>
       </c>
       <c r="L33" t="n">
-        <v>68.53</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="34">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>15.01</v>
+        <v>15.38</v>
       </c>
       <c r="K46" t="n">
-        <v>-60.05</v>
+        <v>-61.52</v>
       </c>
       <c r="L46" t="n">
-        <v>61.9</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-53.72</v>
+        <v>-53.94</v>
       </c>
       <c r="K47" t="n">
-        <v>-55.11</v>
+        <v>-55.34</v>
       </c>
       <c r="L47" t="n">
-        <v>76.95999999999999</v>
+        <v>77.27</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>42.57</v>
+        <v>42.66</v>
       </c>
       <c r="K48" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="L48" t="n">
-        <v>63.04</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>15.43</v>
+        <v>15.52</v>
       </c>
       <c r="K49" t="n">
-        <v>86.23999999999999</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>87.61</v>
+        <v>88.14</v>
       </c>
     </row>
     <row r="50">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>26.61</v>
+        <v>26.76</v>
       </c>
       <c r="K61" t="n">
-        <v>43.81</v>
+        <v>44.06</v>
       </c>
       <c r="L61" t="n">
-        <v>51.25</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="62">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>83.64</v>
+        <v>85.42</v>
       </c>
       <c r="K63" t="n">
-        <v>-39.54</v>
+        <v>-40.38</v>
       </c>
       <c r="L63" t="n">
-        <v>92.51000000000001</v>
+        <v>94.48999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.86</v>
+        <v>-47.23</v>
       </c>
       <c r="K76" t="n">
-        <v>-63.22</v>
+        <v>-65.11</v>
       </c>
       <c r="L76" t="n">
-        <v>78.09999999999999</v>
+        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-29.36</v>
+        <v>-31.02</v>
       </c>
       <c r="K79" t="n">
-        <v>-59.15</v>
+        <v>-62.49</v>
       </c>
       <c r="L79" t="n">
-        <v>66.04000000000001</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="80">
